--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J874"/>
+  <dimension ref="A1:J876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/1/23，2026/3/1，2026/3/22，2026/3/27</t>
+          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/1/23，2026/3/1，2026/3/22，2026/3/27，2026/6/28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -510,12 +510,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BV1dmXNBgE3x，BV1Z1u9z9E4q，BV15MPuzCEEd</t>
+          <t>BV1n4TM6GEnu，BV1dmXNBgE3x，BV1Z1u9z9E4q，BV15MPuzCEEd</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/1/9，2026/2/12，2026/3/9，2026/3/15，2026/5/1，2026/5/16，2026/5/23</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/1/9，2026/2/12，2026/3/9，2026/3/15，2026/5/1，2026/5/16，2026/5/23，2026/7/5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/9，2025/12/16，2026/2/14，2026/3/7，2026/3/17，2026/3/21，2026/5/1</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/9，2025/12/16，2026/2/14，2026/3/7，2026/3/17，2026/3/21，2026/5/1，2026/7/4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BV1oco7YsEGk</t>
+          <t>BV1P6MK6UE3G，BV1oco7YsEGk</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/9，2025/12/30，2026/2/20，2026/2/23，2026/3/4，2026/4/11，2026/4/16，2026/4/23，2026/6/14</t>
+          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/9，2025/12/30，2026/2/20，2026/2/23，2026/3/4，2026/4/11，2026/4/16，2026/4/23，2026/6/14，2026/7/4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/7，2025/11/9，2025/12/2，2026/1/21，2026/3/5，2026/4/16，2026/6/23</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/7，2025/11/9，2025/12/2，2026/1/21，2026/3/5，2026/4/16，2026/6/23，2026/7/5</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/7，2025/12/16，2025/12/28，2026/1/10，2026/1/15，2026/2/19，2026/3/7，2026/3/17，2026/3/21，2026/5/6</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/7，2025/12/16，2025/12/28，2026/1/10，2026/1/15，2026/2/19，2026/3/7，2026/3/17，2026/3/21，2026/5/6，2026/7/5</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BV1zmEmzhE1a</t>
+          <t>BV1XNTy6AE2b，BV1zmEmzhE1a</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/7，2025/11/19，2025/11/26，2025/12/30，2026/1/28，2026/2/14，2026/3/13，2026/4/10，2026/5/23，2026/6/18</t>
+          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/7，2025/11/19，2025/11/26，2025/12/30，2026/1/28，2026/2/14，2026/3/13，2026/4/10，2026/5/23，2026/6/18，2026/6/29</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/1，2025/11/9，2025/12/4，2025/12/16，2025/12/31，2026/1/9，2026/1/15，2026/1/21，2026/1/23，2026/1/29，2026/2/2，2026/2/7，2026/2/10，2026/2/14，2026/2/19，2026/2/24，2026/2/25，2026/2/27，2026/3/1，2026/3/4，2026/3/5，2026/3/7，2026/3/8，2026/3/9，2026/3/12，2026/3/13，2026/3/14，2026/3/15，2026/3/17，2026/3/18，2026/3/19，2026/3/22，2026/3/24，2026/3/27，2026/3/28，2026/3/31，2026/4/8，2026/4/14，2026/4/18，2026/4/25，2026/5/1，2026/5/15，2026/5/25，2026/6/12，2026/6/23，2026/6/26</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/1，2025/11/9，2025/12/4，2025/12/16，2025/12/31，2026/1/9，2026/1/15，2026/1/21，2026/1/23，2026/1/29，2026/2/2，2026/2/7，2026/2/10，2026/2/14，2026/2/19，2026/2/24，2026/2/25，2026/2/27，2026/3/1，2026/3/4，2026/3/5，2026/3/7，2026/3/8，2026/3/9，2026/3/12，2026/3/13，2026/3/14，2026/3/15，2026/3/17，2026/3/18，2026/3/19，2026/3/22，2026/3/24，2026/3/27，2026/3/28，2026/3/31，2026/4/8，2026/4/14，2026/4/18，2026/4/25，2026/5/1，2026/5/15，2026/5/25，2026/6/12，2026/6/23，2026/6/26，2026/7/4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/2，2025/12/26，2026/5/4</t>
+          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/2，2025/12/26，2026/5/4，2026/6/28</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BV1PNMgzuEWm，BV1JdBCBEEPS</t>
+          <t>BV1HATu6mEcq，BV1PNMgzuEWm，BV1JdBCBEEPS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/21，2025/05/15，2025/07/28，2025/09/10，2026/1/14</t>
+          <t>2025/03/13，2025/04/21，2025/05/15，2025/07/28，2025/09/10，2026/1/14，2026/6/28</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BV1weQuYAEWL</t>
+          <t>BV1VzTM6PEye，BV1weQuYAEWL</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/05/12，2025/05/22，2025/06/16，2025/06/30，2025/08/01，2025/08/16，2025/09/19，2025/10/05，2025/11/18，2025/12/23，2026/1/9，2026/2/27，2026/4/29</t>
+          <t>2025/03/13，2025/05/12，2025/05/22，2025/06/16，2025/06/30，2025/08/01，2025/08/16，2025/09/19，2025/10/05，2025/11/18，2025/12/23，2026/1/9，2026/2/27，2026/4/29，2026/7/5</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/1，2026/2/14</t>
+          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/1，2026/2/14，2026/6/28</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/7，2025/12/23，2026/1/5，2026/1/21，2026/1/29，2026/2/9，2026/2/20，2026/2/23，2026/3/4，2026/3/6，2026/3/7，2026/4/11，2026/4/14，2026/4/29，2026/5/23</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/7，2025/12/23，2026/1/5，2026/1/21，2026/1/29，2026/2/9，2026/2/20，2026/2/23，2026/3/4，2026/3/6，2026/3/7，2026/4/11，2026/4/14，2026/4/29，2026/5/23，2026/7/3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/2，2025/12/17，2026/1/9，2026/1/15，2026/2/2，2026/2/14，2026/3/13，2026/3/25，2026/4/24，2026/5/23，2026/6/17</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/2，2025/12/17，2026/1/9，2026/1/15，2026/2/2，2026/2/14，2026/3/13，2026/3/25，2026/4/24，2026/5/23，2026/6/17，2026/7/5</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/1/3，2026/1/5，2026/1/30，2026/3/14，2026/3/31，2026/4/20，2026/5/1，2026/6/19</t>
+          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/1/3，2026/1/5，2026/1/30，2026/3/14，2026/3/31，2026/4/20，2026/5/1，2026/6/19，2026/6/30</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/1/22，2026/1/25，2026/2/19，2026/5/20</t>
+          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/1/22，2026/1/25，2026/2/19，2026/5/20，2026/7/2</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/8，2026/1/23，2026/1/26，2026/2/7，2026/2/10，2026/2/23，2026/2/25，2026/2/27，2026/3/1，2026/3/4，2026/3/13，2026/3/24，2026/3/28，2026/3/29，2026/4/27，2026/5/2，2026/6/18</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/8，2026/1/23，2026/1/26，2026/2/7，2026/2/10，2026/2/23，2026/2/25，2026/2/27，2026/3/1，2026/3/4，2026/3/13，2026/3/24，2026/3/28，2026/3/29，2026/4/27，2026/5/2，2026/6/18，2026/7/4</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7611,7 +7611,11 @@
           <t>囍帖街</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>喜帖街</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>谢安琪</t>
@@ -7619,7 +7623,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/8，2026/2/18，2026/3/6，2026/3/13，2026/3/14，2026/3/31，2026/5/1</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/8，2026/2/18，2026/3/6，2026/3/13，2026/3/14，2026/3/31，2026/5/1，2026/6/28</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7630,7 +7634,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8143,7 +8147,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/12，2025/09/11，2025/10/31，2026/1/9</t>
+          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/12，2025/09/11，2025/10/31，2026/1/9，2026/7/5</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -8154,7 +8158,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8303,7 +8307,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/7，2026/1/17，2026/2/14，2026/4/9，2026/5/20，2026/6/19</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/7，2026/1/17，2026/2/14，2026/4/9，2026/5/20，2026/6/19，2026/6/28</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8314,7 +8318,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8903,7 +8907,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/1/14</t>
+          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/1/14，2026/6/28</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -8914,7 +8918,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10031,7 +10035,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/6/28</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10042,7 +10046,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10755,7 +10759,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/2/7</t>
+          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/2/7，2026/6/28</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -10766,7 +10770,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12431,7 +12435,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/17，2025/05/04，2025/05/24，2025/05/30，2025/09/19，2025/10/22，2025/11/13</t>
+          <t>2025/04/06，2025/04/17，2025/05/04，2025/05/24，2025/05/30，2025/09/19，2025/10/22，2025/11/13，2026/6/28</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -12442,7 +12446,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -14823,7 +14827,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/2/18，2026/5/20</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/2/18，2026/5/20，2026/7/5</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14834,7 +14838,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -15163,7 +15167,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>365</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15203,7 +15207,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>366</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15243,7 +15247,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15283,7 +15287,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>368</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15323,7 +15327,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15339,7 +15343,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/2，2026/1/26</t>
+          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/2，2026/1/26，2026/6/28</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -15350,7 +15354,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -15363,7 +15367,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15403,7 +15407,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15443,7 +15447,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15483,7 +15487,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>373</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15531,7 +15535,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>374</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15571,7 +15575,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>375</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15611,7 +15615,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>376</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15651,7 +15655,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15691,7 +15695,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15727,7 +15731,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>379</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15767,7 +15771,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>380</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15803,7 +15807,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15843,7 +15847,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>382</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15883,7 +15887,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>383</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15919,7 +15923,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>384</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15955,7 +15959,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>385</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15991,7 +15995,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>386</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -16031,7 +16035,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>387</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -16071,7 +16075,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>388</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -16111,7 +16115,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>389</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -16147,7 +16151,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>390</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -16187,7 +16191,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>391</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -16227,7 +16231,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>392</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -16263,7 +16267,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>393</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -16299,7 +16303,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>394</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -16339,7 +16343,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>395</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -16379,7 +16383,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>396</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -16415,7 +16419,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>397</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -16455,7 +16459,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -16495,7 +16499,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>399</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -16535,7 +16539,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>400</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -16575,7 +16579,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -16611,7 +16615,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -16651,7 +16655,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>403</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -16691,7 +16695,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>404</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -16735,7 +16739,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>405</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -16775,7 +16779,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>406</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -16815,7 +16819,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>407</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -16855,7 +16859,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>408</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -16891,7 +16895,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>409</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -16927,7 +16931,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>410</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -16967,7 +16971,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>411</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -17003,7 +17007,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>412</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -17043,7 +17047,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>413</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -17083,7 +17087,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>414</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -17119,7 +17123,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -17159,7 +17163,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>416</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -17199,7 +17203,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>417</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -17239,7 +17243,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>418</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -17279,7 +17283,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -17319,7 +17323,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>420</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -17359,7 +17363,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>421</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -17399,7 +17403,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>422</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -17439,7 +17443,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>423</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -17479,7 +17483,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -17519,7 +17523,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>425</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -17559,7 +17563,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -17595,7 +17599,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>427</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -17635,7 +17639,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -17671,7 +17675,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>429</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -17711,7 +17715,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>430</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -17751,7 +17755,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>431</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -17791,7 +17795,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>432</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -17831,7 +17835,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>433</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -17871,7 +17875,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>434</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -17911,7 +17915,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>435</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -17951,7 +17955,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>436</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -17991,7 +17995,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>437</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -18031,7 +18035,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>438</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -18071,7 +18075,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>439</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -18111,7 +18115,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -18127,7 +18131,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/1/1，2026/2/10，2026/2/22，2026/3/12，2026/4/5，2026/5/3，2026/5/24</t>
+          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/1/1，2026/2/10，2026/2/22，2026/3/12，2026/4/5，2026/5/3，2026/5/24，2026/7/3</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -18138,7 +18142,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -18151,7 +18155,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>441</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -18191,7 +18195,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>442</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -18227,7 +18231,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>443</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -18267,7 +18271,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>444</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -18307,7 +18311,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>445</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -18347,7 +18351,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -18387,7 +18391,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>447</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -18427,7 +18431,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>448</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -18467,7 +18471,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>449</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -18507,7 +18511,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>450</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -18543,7 +18547,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>451</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -18587,7 +18591,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>452</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -18627,7 +18631,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>453</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -18667,7 +18671,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>454</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -18707,7 +18711,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>455</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -18751,7 +18755,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>456</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -18791,7 +18795,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>457</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -18831,7 +18835,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>458</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -18875,7 +18879,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>459</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -18915,7 +18919,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>460</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -18935,7 +18939,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/06/17，2025/07/21，2025/08/16，2025/10/16，2025/12/2，2026/4/22，2026/6/23</t>
+          <t>2025/05/22，2025/06/17，2025/07/21，2025/08/16，2025/10/16，2025/12/2，2026/4/22，2026/6/23，2026/7/5</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -18946,7 +18950,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -18959,7 +18963,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -18999,7 +19003,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>462</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -19035,7 +19039,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>463</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -19071,7 +19075,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>464</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -19111,7 +19115,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>465</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -19151,7 +19155,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>466</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -19191,7 +19195,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>467</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -19231,7 +19235,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>468</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -19271,7 +19275,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>469</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -19307,7 +19311,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -19343,7 +19347,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -19383,7 +19387,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>472</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -19423,7 +19427,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>473</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -19459,7 +19463,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -19499,7 +19503,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>475</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -19535,7 +19539,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -19575,7 +19579,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>477</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -19615,7 +19619,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -19655,7 +19659,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>479</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -19671,7 +19675,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/1/10，2026/1/22，2026/3/25</t>
+          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/1/10，2026/1/22，2026/3/25，2026/6/28</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -19682,7 +19686,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -19695,7 +19699,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>480</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -19735,7 +19739,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>481</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -19771,7 +19775,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>482</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -19807,7 +19811,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>483</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -19847,7 +19851,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>484</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -19891,7 +19895,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -19935,7 +19939,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>486</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -19975,7 +19979,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -20019,7 +20023,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -20059,7 +20063,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -20095,7 +20099,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>490</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -20131,7 +20135,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -20167,7 +20171,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>492</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -20203,7 +20207,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>493</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -20243,7 +20247,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>494</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -20279,7 +20283,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>495</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -20319,7 +20323,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>496</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -20359,7 +20363,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>497</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -20395,7 +20399,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>498</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -20431,7 +20435,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -20467,7 +20471,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -20507,7 +20511,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>501</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -20547,7 +20551,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>502</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -20583,7 +20587,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>503</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -20623,7 +20627,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -20663,7 +20667,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>505</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -20695,7 +20699,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>506</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -20731,7 +20735,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -20767,7 +20771,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -20807,7 +20811,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>509</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -20847,7 +20851,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -20887,7 +20891,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>511</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -20927,7 +20931,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>512</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -20967,7 +20971,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>513</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -21011,7 +21015,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>514</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -21051,7 +21055,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>515</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -21091,7 +21095,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -21131,7 +21135,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>517</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -21171,7 +21175,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>518</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -21207,7 +21211,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>519</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -21247,7 +21251,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>520</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -21287,7 +21291,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -21327,7 +21331,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -21363,7 +21367,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -21403,7 +21407,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>524</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -21443,7 +21447,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>525</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -21483,7 +21487,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>526</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -21523,7 +21527,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>527</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -21563,7 +21567,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>528</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -21599,7 +21603,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>529</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -21615,7 +21619,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/7，2025/11/21，2025/12/2，2025/12/17，2026/1/1，2026/1/5，2026/1/14，2026/1/22，2026/1/24，2026/2/2，2026/3/5，2026/3/15，2026/4/1，2026/5/4，2026/5/25，2026/6/20</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/7，2025/11/21，2025/12/2，2025/12/17，2026/1/1，2026/1/5，2026/1/14，2026/1/22，2026/1/24，2026/2/2，2026/3/5，2026/3/15，2026/4/1，2026/5/4，2026/5/25，2026/6/20，2026/7/5</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21626,7 +21630,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21639,7 +21643,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>530</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -21679,7 +21683,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>531</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -21719,7 +21723,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>532</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -21759,7 +21763,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>533</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -21799,7 +21803,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>534</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -21843,7 +21847,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>535</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -21883,7 +21887,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>536</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -21919,7 +21923,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>537</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -21955,7 +21959,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>538</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -21991,7 +21995,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>539</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -22031,7 +22035,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>540</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -22071,7 +22075,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -22111,7 +22115,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>542</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -22147,7 +22151,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>543</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -22183,7 +22187,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>544</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -22231,7 +22235,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>545</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -22271,7 +22275,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>546</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -22319,7 +22323,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>547</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -22363,7 +22367,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>548</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -22399,7 +22403,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>549</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -22439,7 +22443,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>550</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -22475,7 +22479,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -22515,7 +22519,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>552</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -22555,7 +22559,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>553</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -22591,7 +22595,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>554</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -22627,7 +22631,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>555</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -22663,7 +22667,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>556</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -22699,7 +22703,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -22735,7 +22739,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>558</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -22771,7 +22775,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>559</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -22811,7 +22815,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>560</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -22847,7 +22851,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -22883,7 +22887,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>562</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -22923,7 +22927,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -22959,7 +22963,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>564</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -22999,7 +23003,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>565</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -23035,7 +23039,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>566</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -23075,7 +23079,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>567</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -23115,7 +23119,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>568</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -23155,7 +23159,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>569</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -23195,7 +23199,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>570</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -23235,7 +23239,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>571</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -23275,7 +23279,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>572</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -23315,7 +23319,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>573</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -23355,7 +23359,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>574</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -23395,7 +23399,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>575</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -23435,7 +23439,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>576</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -23471,7 +23475,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>577</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -23511,7 +23515,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>578</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -23527,7 +23531,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>2025/07/11，2025/09/30，2025/10/31，2025/12/4，2026/1/23，2026/2/12，2026/3/17，2026/4/9</t>
+          <t>2025/07/11，2025/09/30，2025/10/31，2025/12/4，2026/1/23，2026/2/12，2026/3/17，2026/4/9，2026/6/28</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -23538,7 +23542,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -23551,7 +23555,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>579</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -23587,7 +23591,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>580</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -23623,7 +23627,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>581</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -23663,7 +23667,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>582</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -23703,7 +23707,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>583</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -23743,7 +23747,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>584</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -23783,7 +23787,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -23819,7 +23823,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>586</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -23859,7 +23863,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>587</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -23899,7 +23903,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -23935,7 +23939,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>589</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -23975,7 +23979,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>590</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -24011,7 +24015,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -24047,7 +24051,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -24083,7 +24087,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>593</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -24119,7 +24123,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>594</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -24155,7 +24159,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>595</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -24195,7 +24199,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -24235,7 +24239,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>597</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -24279,7 +24283,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>598</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -24315,7 +24319,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>599</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -24355,7 +24359,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>600</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -24391,7 +24395,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -24427,7 +24431,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>602</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -24463,7 +24467,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>603</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -24503,7 +24507,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>604</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -24539,7 +24543,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>605</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -24575,7 +24579,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -24615,7 +24619,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>607</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -24655,7 +24659,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>608</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -24695,7 +24699,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>609</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -24731,7 +24735,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>610</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -24771,7 +24775,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>611</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -24815,7 +24819,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -24851,7 +24855,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>613</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -24891,7 +24895,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>614</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -24931,7 +24935,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>615</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -24967,7 +24971,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -25015,7 +25019,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>617</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -25055,7 +25059,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>618</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -25091,7 +25095,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>619</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -25131,7 +25135,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>620</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -25171,7 +25175,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>621</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -25211,7 +25215,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -25247,7 +25251,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>623</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -25287,7 +25291,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -25323,7 +25327,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>625</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -25363,7 +25367,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>626</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -25403,7 +25407,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>627</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -25443,7 +25447,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -25483,7 +25487,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>629</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -25523,7 +25527,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>630</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -25559,7 +25563,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -25599,7 +25603,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>632</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -25635,7 +25639,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>633</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -25671,7 +25675,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>634</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -25707,7 +25711,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>635</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -25743,7 +25747,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -25779,7 +25783,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>637</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -25819,7 +25823,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>638</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -25859,7 +25863,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>639</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -25899,7 +25903,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>640</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -25939,7 +25943,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -25979,7 +25983,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -26019,7 +26023,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -26059,7 +26063,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -26095,7 +26099,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -26135,7 +26139,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -26175,7 +26179,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>647</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -26211,7 +26215,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -26251,7 +26255,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>649</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -26267,7 +26271,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>2025/09/15，2025/10/19，2025/10/20，2025/10/26，2025/11/1，2025/11/14，2026/1/15，2026/1/23，2026/4/19，2026/4/24</t>
+          <t>2025/09/15，2025/10/19，2025/10/20，2025/10/26，2025/11/1，2025/11/14，2026/1/15，2026/1/23，2026/4/19，2026/4/24，2026/7/5</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -26278,7 +26282,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -26291,7 +26295,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>650</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -26331,7 +26335,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>651</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -26367,7 +26371,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>652</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -26407,7 +26411,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>653</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -26447,7 +26451,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>654</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -26487,7 +26491,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>655</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -26523,7 +26527,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -26563,7 +26567,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>657</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -26579,7 +26583,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>2025/09/20，2025/09/21，2025/09/22，2025/09/24，2025/09/27，2025/10/05，2025/10/12，2025/10/22，2025/11/1，2025/12/6，2025/12/12，2026/1/19，2026/4/8，2026/5/20，2026/6/6</t>
+          <t>2025/09/20，2025/09/21，2025/09/22，2025/09/24，2025/09/27，2025/10/05，2025/10/12，2025/10/22，2025/11/1，2025/12/6，2025/12/12，2026/1/19，2026/4/8，2026/5/20，2026/6/6，2026/6/28</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -26590,7 +26594,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -26603,7 +26607,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>658</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -26619,7 +26623,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/1，2025/11/9，2025/11/19，2025/11/22，2025/11/28，2025/12/8，2025/12/22，2026/1/5，2026/1/14，2026/1/22，2026/2/7，2026/2/10，2026/3/8，2026/3/22，2026/4/18，2026/5/1，2026/5/20，2026/6/10，2026/6/25</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/1，2025/11/9，2025/11/19，2025/11/22，2025/11/28，2025/12/8，2025/12/22，2026/1/5，2026/1/14，2026/1/22，2026/2/7，2026/2/10，2026/3/8，2026/3/22，2026/4/18，2026/5/1，2026/5/20，2026/6/10，2026/6/25，2026/7/5</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26630,7 +26634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -26643,7 +26647,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>659</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -26683,7 +26687,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>660</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -26719,7 +26723,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -26755,7 +26759,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>662</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -26791,7 +26795,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>663</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -26827,7 +26831,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>664</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -26863,7 +26867,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>665</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -26903,7 +26907,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>666</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -26939,7 +26943,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -26975,7 +26979,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>668</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -27015,7 +27019,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>669</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -27055,7 +27059,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>670</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -27095,7 +27099,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>671</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -27135,7 +27139,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -27171,7 +27175,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>673</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -27211,7 +27215,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>674</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -27247,7 +27251,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>675</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -27287,7 +27291,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>676</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -27327,7 +27331,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>677</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -27363,7 +27367,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>678</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -27399,7 +27403,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -27439,7 +27443,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>680</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -27475,7 +27479,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>681</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -27511,7 +27515,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>682</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -27551,7 +27555,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -27587,7 +27591,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>684</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -27623,7 +27627,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>685</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -27659,7 +27663,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>686</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -27699,7 +27703,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>687</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -27739,7 +27743,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>688</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -27787,7 +27791,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>689</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -27827,7 +27831,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>690</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -27875,7 +27879,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>691</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -27911,7 +27915,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>692</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -27955,7 +27959,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>693</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -27995,7 +27999,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>694</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -28035,7 +28039,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>695</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -28075,7 +28079,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>696</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -28115,7 +28119,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>697</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -28155,7 +28159,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>698</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -28195,7 +28199,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>699</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -28235,7 +28239,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>700</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -28271,7 +28275,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>701</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -28307,7 +28311,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>702</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -28347,7 +28351,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>703</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -28383,7 +28387,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>704</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -28419,7 +28423,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>705</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -28455,7 +28459,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>706</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -28491,7 +28495,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>707</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -28527,7 +28531,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>708</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -28563,7 +28567,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>709</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -28603,7 +28607,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>710</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -28639,7 +28643,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>711</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -28679,7 +28683,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>712</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -28723,7 +28727,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>713</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -28763,7 +28767,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>714</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -28799,7 +28803,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>715</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -28839,7 +28843,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>716</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -28875,7 +28879,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>717</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -28915,7 +28919,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>718</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -28955,7 +28959,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -28991,7 +28995,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>720</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -29027,7 +29031,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>721</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -29063,7 +29067,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>722</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -29099,7 +29103,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>723</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -29135,7 +29139,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>724</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -29179,7 +29183,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>725</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -29215,7 +29219,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>726</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -29251,7 +29255,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>727</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -29287,7 +29291,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>728</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -29323,7 +29327,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>729</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -29355,7 +29359,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>730</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -29391,7 +29395,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>731</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -29427,7 +29431,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>732</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -29467,7 +29471,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>733</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -29503,7 +29507,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>734</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -29543,7 +29547,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>735</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -29579,7 +29583,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>736</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -29615,7 +29619,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>737</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -29655,7 +29659,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>738</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -29699,7 +29703,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>739</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -29739,7 +29743,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>740</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -29775,7 +29779,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>741</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -29811,7 +29815,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>742</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -29847,7 +29851,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>743</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -29887,7 +29891,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>744</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -29927,7 +29931,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>745</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -29963,7 +29967,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>746</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -29999,7 +30003,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>747</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -30047,7 +30051,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>748</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -30087,7 +30091,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>749</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -30103,7 +30107,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>2025/12/11，2025/12/12，2025/12/17，2026/1/2，2026/1/5，2026/1/11，2026/1/17，2026/1/29，2026/2/9，2026/3/28，2026/4/29</t>
+          <t>2025/12/11，2025/12/12，2025/12/17，2026/1/2，2026/1/5，2026/1/11，2026/1/17，2026/1/29，2026/2/9，2026/3/28，2026/4/29，2026/7/5</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -30114,7 +30118,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -30127,7 +30131,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>750</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -30163,7 +30167,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>751</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -30199,7 +30203,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>752</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -30235,7 +30239,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>753</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -30271,7 +30275,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>754</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -30307,7 +30311,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>755</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -30343,7 +30347,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>756</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -30379,7 +30383,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>757</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -30419,7 +30423,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>758</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -30459,7 +30463,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>759</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -30495,7 +30499,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>760</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -30535,7 +30539,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>761</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -30575,7 +30579,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>762</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -30619,7 +30623,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>763</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -30659,7 +30663,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>764</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -30699,7 +30703,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>765</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -30735,7 +30739,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>766</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -30771,7 +30775,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>767</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -30811,7 +30815,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>768</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -30851,7 +30855,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -30891,7 +30895,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>770</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -30927,7 +30931,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>771</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -30963,7 +30967,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>772</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -30979,7 +30983,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>2026/1/23</t>
+          <t>2026/1/23，2026/6/28</t>
         </is>
       </c>
       <c r="F773" t="inlineStr"/>
@@ -30990,7 +30994,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -31003,7 +31007,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>773</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -31039,7 +31043,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>774</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -31079,7 +31083,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>775</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -31095,7 +31099,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2026/1/24，2026/1/25，2026/1/26，2026/2/2，2026/2/7，2026/2/10，2026/2/14，2026/2/19，2026/3/4，2026/3/12，2026/3/31，2026/4/1，2026/4/14，2026/4/18，2026/5/10，2026/5/23，2026/6/12</t>
+          <t>2026/1/24，2026/1/25，2026/1/26，2026/2/2，2026/2/7，2026/2/10，2026/2/14，2026/2/19，2026/3/4，2026/3/12，2026/3/31，2026/4/1，2026/4/14，2026/4/18，2026/5/10，2026/5/23，2026/6/12，2026/7/3</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
@@ -31106,7 +31110,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -31119,7 +31123,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>776</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -31159,7 +31163,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>777</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -31203,7 +31207,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -31243,7 +31247,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>779</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -31287,7 +31291,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -31327,7 +31331,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -31363,7 +31367,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>782</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -31403,7 +31407,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>783</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -31443,7 +31447,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>784</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -31483,7 +31487,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>785</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -31523,7 +31527,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>786</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -31539,7 +31543,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/2/8，2026/2/9，2026/2/14，2026/2/20，2026/2/28，2026/5/25，2026/6/13</t>
+          <t>2026/2/8，2026/2/9，2026/2/14，2026/2/20，2026/2/28，2026/5/25，2026/6/13，2026/7/5</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31550,7 +31554,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -31563,7 +31567,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>787</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -31607,7 +31611,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>788</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -31647,7 +31651,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>789</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -31687,7 +31691,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>790</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -31735,7 +31739,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>791</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -31775,7 +31779,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>792</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -31811,7 +31815,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>793</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -31851,7 +31855,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>794</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -31891,7 +31895,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>795</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -31931,7 +31935,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>796</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -31971,7 +31975,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>797</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -32015,7 +32019,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>798</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -32055,7 +32059,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>799</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -32095,7 +32099,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>800</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -32139,7 +32143,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>801</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -32179,7 +32183,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>802</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -32223,7 +32227,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>803</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -32263,7 +32267,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>804</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -32303,7 +32307,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>805</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -32347,7 +32351,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>806</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -32363,7 +32367,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>2025/12/8，2026/1/9，2026/3/4</t>
+          <t>2025/12/8，2026/1/9，2026/3/4，2026/7/5</t>
         </is>
       </c>
       <c r="F807" t="inlineStr"/>
@@ -32374,7 +32378,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -32391,7 +32395,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>807</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -32427,7 +32431,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>808</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -32471,7 +32475,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>809</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -32511,7 +32515,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>810</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -32551,7 +32555,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>811</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -32567,7 +32571,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>2026/3/13，2026/3/25，2026/3/28，2026/4/11，2026/4/20，2026/5/26</t>
+          <t>2026/3/13，2026/3/25，2026/3/28，2026/4/11，2026/4/20，2026/5/26，2026/7/5</t>
         </is>
       </c>
       <c r="F812" t="inlineStr"/>
@@ -32578,7 +32582,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -32595,7 +32599,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>812</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -32639,7 +32643,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>813</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -32655,7 +32659,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/3/13，2026/3/14，2026/3/28，2026/4/29，2026/5/25，2026/6/3，2026/6/13</t>
+          <t>2026/3/13，2026/3/14，2026/3/28，2026/4/29，2026/5/25，2026/6/3，2026/6/13，2026/7/2</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -32666,7 +32670,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -32679,7 +32683,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>814</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -32715,7 +32719,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>815</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -32751,7 +32755,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>816</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -32799,7 +32803,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>817</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -32835,7 +32839,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>818</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -32871,7 +32875,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>819</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -32911,7 +32915,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>820</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -32951,7 +32955,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>821</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -32991,7 +32995,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>822</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -33035,7 +33039,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>823</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -33083,7 +33087,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>824</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -33127,7 +33131,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>825</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -33167,7 +33171,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>826</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -33207,7 +33211,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>827</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -33247,7 +33251,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>828</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -33287,7 +33291,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>829</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -33331,7 +33335,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>830</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -33371,7 +33375,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>831</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -33415,7 +33419,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>832</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -33455,7 +33459,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>833</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -33495,7 +33499,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>834</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -33535,7 +33539,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>835</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -33575,7 +33579,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>836</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -33615,7 +33619,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>837</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -33655,7 +33659,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>838</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -33695,7 +33699,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>839</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -33735,7 +33739,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>840</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -33775,7 +33779,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>841</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -33811,7 +33815,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>842</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -33851,7 +33855,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>843</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -33891,7 +33895,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>844</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -33935,7 +33939,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>845</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -33979,7 +33983,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>846</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -34015,7 +34019,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>847</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -34059,7 +34063,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>848</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -34099,7 +34103,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>849</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -34143,7 +34147,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>850</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -34183,7 +34187,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>851</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -34223,7 +34227,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>852</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -34263,7 +34267,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>853</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -34303,7 +34307,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>854</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -34343,7 +34347,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>855</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -34391,7 +34395,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>856</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -34431,7 +34435,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>857</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -34475,7 +34479,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>858</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -34523,7 +34527,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>859</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -34563,7 +34567,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>860</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -34603,7 +34607,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>861</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -34643,7 +34647,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>862</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -34683,7 +34687,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>863</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -34723,7 +34727,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>864</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -34763,7 +34767,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>865</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -34807,7 +34811,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>866</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -34847,7 +34851,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>867</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -34887,7 +34891,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>868</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -34927,7 +34931,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>869</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -34971,7 +34975,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>870</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -35007,7 +35011,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>871</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -35023,7 +35027,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>2026/6/20</t>
+          <t>2026/6/20，2026/6/30</t>
         </is>
       </c>
       <c r="F872" t="inlineStr"/>
@@ -35034,7 +35038,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -35047,7 +35051,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>872</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -35087,7 +35091,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>873</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -35123,6 +35127,90 @@
         </is>
       </c>
       <c r="J874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>눈,코,입</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>眼，鼻，嘴</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>TAEYANG</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>2026/6/29</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>韩语</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>BV1mAKX6kEg8</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>海屿你</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr"/>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>马也_Crabbit</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>2026/7/5</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>BV1ZoTC6BELe</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J876"/>
+  <dimension ref="A1:J883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/1/23，2026/3/1，2026/3/22，2026/3/27，2026/6/28</t>
+          <t>2025/03/01，2025/04/01，2025/04/17，2025/04/29，2025/05/30，2025/08/02，2025/08/21，2025/09/18，2025/09/19，2025/09/28，2025/10/16，2025/11/14，2025/12/12，2026/01/23，2026/03/01，2026/03/22，2026/03/27，2026/06/28，2026/07/22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/17，2025/09/02，2025/09/07，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/9，2025/11/14，2025/12/24，2025/12/26，2026/1/16，2026/1/24，2026/1/28，2026/1/30，2026/2/10，2026/2/14，2026/3/9，2026/3/27，2026/4/1，2026/4/14，2026/4/24，2026/6/12</t>
+          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/17，2025/09/02，2025/09/07，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/7，2026/1/14，2026/1/24，2026/2/19，2026/3/7，2026/3/15，2026/6/6，2026/6/23</t>
+          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -631,7 +631,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/25，2025/03/28，2025/04/17，2025/05/03，2025/05/09，2025/05/16，2025/05/30，2025/06/14，2025/06/19，2025/07/05，2025/07/18，2025/08/21，2025/08/25，2025/09/05，2025/09/22，2025/09/26，2026/1/19，2026/1/21，2026/3/4，2026/4/16，2026/6/6，2026/6/18，2026/6/23</t>
+          <t>2025/03/02，2025/03/25，2025/03/28，2025/04/17，2025/05/03，2025/05/09，2025/05/16，2025/05/30，2025/06/14，2025/06/19，2025/07/05，2025/07/18，2025/08/21，2025/08/25，2025/09/05，2025/09/22，2025/09/26，2026/01/19，2026/01/21，2026/03/04，2026/04/16，2026/06/06，2026/06/18，2026/06/23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/9，2025/12/11，2026/1/15，2026/2/12，2026/4/19</t>
+          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/1，2025/11/17，2025/12/2，2025/12/31，2026/2/2，2026/2/14，2026/3/6，2026/4/1，2026/4/20，2026/5/15，2026/6/10</t>
+          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/9，2025/11/19，2025/12/16，2026/1/16，2026/1/28，2026/2/7，2026/2/10，2026/3/17，2026/4/19，2026/5/23，2026/6/19</t>
+          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/7，2025/12/4，2026/1/28，2026/4/29，2026/6/25</t>
+          <t>2025/03/03，2025/04/20，2025/06/16，2025/06/27，2025/07/31，2025/10/05，2025/11/07，2025/12/04，2026/01/28，2026/04/29，2026/06/25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -839,7 +839,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/8，2025/12/30，2026/4/26</t>
+          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/17，2025/06/02，2025/07/07，2025/07/14，2025/08/07，2025/09/04，2025/09/29，2025/11/7，2025/12/5，2026/5/21</t>
+          <t>2025/03/03，2025/04/17，2025/06/02，2025/07/07，2025/07/14，2025/08/07，2025/09/04，2025/09/29，2025/11/07，2025/12/05，2026/05/21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/7，2025/12/31，2026/1/14，2026/1/19，2026/3/29，2026/4/12，2026/4/27，2026/5/1，2026/6/3，2026/6/18，2026/6/25</t>
+          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/4，2026/1/24，2026/1/24，2026/2/19，2026/2/25，2026/3/13，2026/4/8，2026/6/10</t>
+          <t>2025/03/04，2025/03/12，2025/03/17，2025/03/28，2025/04/07，2025/04/19，2025/04/26，2025/05/06，2025/05/16，2025/05/22，2025/05/30，2025/06/21，2025/07/06，2025/08/22，2025/09/06，2025/09/21，2025/10/23，2025/11/10，2025/11/13，2025/12/04，2026/01/24，2026/01/24，2026/02/19，2026/02/25，2026/03/13，2026/04/08，2026/06/10，2026/07/27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/7，2025/12/17，2026/1/19，2026/1/29，2026/2/10，2026/2/12，2026/3/22，2026/4/18，2026/5/10，2026/6/6，2026/6/25</t>
+          <t>2025/03/04，2025/03/19，2025/04/14，2025/04/22，2025/05/01，2025/05/13，2025/05/19，2025/05/27，2025/06/03，2025/06/12，2025/06/19，2025/06/27，2025/07/08，2025/07/14，2025/07/18，2025/07/20，2025/08/02，2025/08/08，2025/08/12，2025/09/02，2025/09/18，2025/10/01，2025/10/03，2025/10/11，2025/10/24，2025/11/13，2025/11/14，2025/11/28，2025/12/07，2025/12/17，2026/01/19，2026/01/29，2026/02/10，2026/02/12，2026/03/22，2026/04/18，2026/05/10，2026/06/06，2026/06/25，2026/07/17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/1/10，2026/1/24，2026/4/9，2026/5/21</t>
+          <t>2025/03/04，2025/04/04，2025/04/18，2025/05/25，2025/05/26，2025/06/06，2025/06/13，2025/09/04，2025/09/17，2025/10/09，2025/10/28，2026/01/10，2026/01/24，2026/04/09，2026/05/21，2026/07/17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/03，2025/04/17，2025/05/22，2025/06/03，2025/07/24，2025/08/12，2025/09/03，2025/10/10，2025/11/9，2025/11/10，2026/3/13，2026/6/3</t>
+          <t>2025/03/04，2025/04/03，2025/04/17，2025/05/22，2025/06/03，2025/07/24，2025/08/12，2025/09/03，2025/10/10，2025/11/09，2025/11/10，2026/03/13，2026/06/03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/1/9，2026/2/12，2026/3/9，2026/3/15，2026/5/1，2026/5/16，2026/5/23，2026/7/5</t>
+          <t>2025/03/04，2025/04/02，2025/04/17，2025/04/29，2025/05/12，2025/05/27，2025/06/10，2025/07/05，2025/08/10，2025/08/28，2025/09/05，2025/09/18，2025/11/12，2025/11/28，2026/01/09，2026/02/12，2026/03/09，2026/03/15，2026/05/01，2026/05/16，2026/05/23，2026/07/05，2026/07/28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/29，2025/05/20，2025/07/13，2025/07/25，2025/07/31，2025/10/09，2025/12/2，2026/1/9，2026/3/21</t>
+          <t>2025/03/04，2025/04/29，2025/05/20，2025/07/13，2025/07/25，2025/07/31，2025/10/09，2025/12/02，2026/01/09，2026/03/21，2026/07/19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/3/9，2026/4/18，2026/5/23</t>
+          <t>2025/03/04，2025/04/18，2025/05/23，2025/07/24，2025/08/28，2025/09/05，2026/03/09，2026/04/18，2026/05/23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/9，2025/12/16，2026/2/14，2026/3/7，2026/3/17，2026/3/21，2026/5/1，2026/7/4</t>
+          <t>2025/03/04，2025/04/14，2025/04/24，2025/05/19，2025/08/21，2025/09/06，2025/09/17，2025/09/26，2025/10/01，2025/11/09，2025/12/16，2026/02/14，2026/03/07，2026/03/17，2026/03/21，2026/05/01，2026/07/04，2026/07/26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/1/15，2026/2/14，2026/3/4，2026/4/9</t>
+          <t>2025/03/04，2025/05/09，2025/05/29，2025/06/28，2025/08/08，2025/08/21，2025/09/15，2025/10/24，2025/12/17，2026/01/15，2026/02/14，2026/03/04，2026/04/09</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/9，2025/11/12，2025/11/27，2025/12/4，2025/12/28，2026/1/22，2026/2/2，2026/2/23，2026/3/25，2026/4/16，2026/5/6，2026/5/21</t>
+          <t>2025/03/04，2025/05/01，2025/05/08，2025/05/26，2025/06/05，2025/06/23，2025/06/26，2025/07/03，2025/07/20，2025/07/26，2025/08/03，2025/08/12，2025/08/30，2025/09/21，2025/09/29，2025/11/09，2025/11/12，2025/11/27，2025/12/04，2025/12/28，2026/01/22，2026/02/02，2026/02/23，2026/03/25，2026/04/16，2026/05/06，2026/05/21，2026/07/10，2026/07/15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/14，2025/05/09，2025/06/13，2025/06/19，2025/06/27，2025/07/10，2025/09/10，2025/09/19，2025/11/14，2025/12/31，2026/2/23，2026/4/16</t>
+          <t>2025/03/04，2025/04/14，2025/05/09，2025/06/13，2025/06/19，2025/06/27，2025/07/10，2025/09/10，2025/09/19，2025/11/14，2025/12/31，2026/02/23，2026/04/16，2026/07/22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/1/3，2026/3/25，2026/5/10，2026/6/20</t>
+          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/07，2025/05/29，2025/06/06，2025/06/19，2025/06/26，2025/07/10，2025/07/11，2025/07/14，2025/08/02，2025/09/03，2025/09/26，2025/10/03，2025/11/9，2025/11/24，2025/11/26，2026/1/5，2026/1/30，2026/3/4，2026/6/17</t>
+          <t>2025/03/04，2025/04/07，2025/05/29，2025/06/06，2025/06/19，2025/06/26，2025/07/10，2025/07/11，2025/07/14，2025/08/02，2025/09/03，2025/09/26，2025/10/03，2025/11/09，2025/11/24，2025/11/26，2026/01/05，2026/01/30，2026/03/04，2026/06/17</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/9，2025/12/30，2026/2/20，2026/2/23，2026/3/4，2026/4/11，2026/4/16，2026/4/23，2026/6/14，2026/7/4</t>
+          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/1，2025/11/9，2025/11/21，2025/12/8，2026/1/15，2026/1/24，2026/3/4，2026/3/14，2026/5/6，2026/5/16，2026/5/20，2026/6/12</t>
+          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/13，2025/05/06，2025/05/15，2025/05/25，2025/06/06，2025/06/23，2025/07/15，2025/07/26，2025/09/15，2025/09/24，2025/10/03，2025/11/26，2025/12/26，2026/1/10，2026/3/22，2026/6/17</t>
+          <t>2025/03/04，2025/04/13，2025/05/06，2025/05/15，2025/05/25，2025/06/06，2025/06/23，2025/07/15，2025/07/26，2025/09/15，2025/09/24，2025/10/03，2025/11/26，2025/12/26，2026/01/10，2026/03/22，2026/06/17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/12，2025/09/17，2025/09/02，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/5，2025/11/14，2025/11/21，2025/11/28，2025/12/8，2025/12/17，2026/1/10，2026/1/22，2026/2/10，2026/2/14，2026/2/14，2026/2/27，2026/3/28，2026/4/9，2026/4/14，2026/5/6，2026/5/23，2026/6/6，2026/6/25</t>
+          <t>2025/03/04，2025/03/25，2025/04/29，2025/05/09，2025/05/13，2025/05/22，2025/05/26，2025/05/30，2025/06/08，2025/06/13，2025/06/20，2025/07/05，2025/07/14，2025/07/20，2025/08/01，2025/08/30，2025/09/12，2025/09/17，2025/09/02，2025/09/22，2025/09/24，2025/10/03，2025/10/12，2025/11/05，2025/11/14，2025/11/21，2025/11/28，2025/12/08，2025/12/17，2026/01/10，2026/01/22，2026/02/10，2026/02/14，2026/02/14，2026/02/27，2026/03/28，2026/04/09，2026/04/14，2026/05/06，2026/05/23，2026/06/06，2026/06/25，2026/07/09，2026/07/16，2026/07/27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/1，2025/11/28，2025/12/12，2026/1/5，2026/1/22，2026/3/4，2026/3/8，2026/3/22，2026/4/22，2026/4/24，2026/5/10，2026/5/23，2026/6/10，2026/6/15</t>
+          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/7，2025/12/24，2026/1/1，2026/1/16，2026/3/14，2026/5/1，2026/5/20</t>
+          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/3/15，2026/6/23</t>
+          <t>2025/03/04，2025/04/22，2025/05/18，2025/09/04，2025/09/10，2025/11/28，2026/03/15，2026/06/23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/25，2026/1/29，2026/2/9</t>
+          <t>2025/03/04，2025/05/25，2026/01/29，2026/02/09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/21，2025/04/05，2025/04/14，2025/04/24，2025/05/20，2025/06/05，2025/06/17，2025/06/23，2025/06/26，2025/08/12，2025/08/21，2025/09/14，2025/09/24，2025/10/16，2025/10/24，2025/12/17，2026/2/14，2026/3/8，2026/4/25，2026/5/21</t>
+          <t>2025/03/04，2025/03/21，2025/04/05，2025/04/14，2025/04/24，2025/05/20，2025/06/05，2025/06/17，2025/06/23，2025/06/26，2025/08/12，2025/08/21，2025/09/14，2025/09/24，2025/10/16，2025/10/24，2025/12/17，2026/02/14，2026/03/08，2026/04/25，2026/05/21，2026/07/18，2026/07/28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/9，2025/11/14，2025/11/26，2026/1/25</t>
+          <t>2025/03/04，2025/04/18，2025/04/28，2025/08/22，2025/09/17，2025/10/30，2025/11/09，2025/11/14，2025/11/26，2026/01/25，2026/07/17</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/24，2025/05/25，2025/06/19，2025/06/20，2025/07/14，2026/4/17，2026/5/1，2026/6/10，2026/6/15</t>
+          <t>2025/03/04，2025/04/24，2025/05/25，2025/06/19，2025/06/20，2025/07/14，2026/04/17，2026/05/01，2026/06/10，2026/06/15，2026/07/22</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/2/19，2026/3/4</t>
+          <t>2025/03/04，2025/05/18，2025/07/26，2025/08/12，2025/11/28，2026/02/19，2026/03/04，2026/07/17</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/1/9，2026/1/28，2026/2/25，2026/3/12，2026/3/21，2026/4/26，2026/5/10，2026/6/26</t>
+          <t>2025/03/04，2025/03/17，2025/03/21，2025/04/04，2025/04/14，2025/04/19，2025/04/25，2025/05/08，2025/05/09，2025/05/19，2025/05/27，2025/05/29，2025/06/08，2025/06/09，2025/07/11，2025/07/14，2025/08/04，2025/08/08，2025/08/12，2025/09/18，2025/10/03，2025/10/10，2025/10/23，2025/11/13，2025/11/28，2025/12/13，2025/12/28，2026/01/09，2026/01/28，2026/02/25，2026/03/12，2026/03/21，2026/04/26，2026/05/10，2026/06/26</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/1/14，2026/2/19，2026/3/14，2026/4/16，2026/6/17</t>
+          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/21，2025/04/19，2025/05/11，2025/06/03，2026/1/19，2026/1/25，2026/2/25，2026/4/1</t>
+          <t>2025/03/06，2025/03/21，2025/04/19，2025/05/11，2025/06/03，2026/01/19，2026/01/25，2026/02/25，2026/04/01，2026/07/27</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/03，2025/04/14，2025/05/05，2025/05/15，2025/05/29，2025/06/20，2025/06/27，2025/08/07，2025/08/24，2025/09/17，2025/10/16，2025/11/10，2025/12/9，2025/12/17，2026/1/21，2026/2/12，2026/2/25</t>
+          <t>2025/03/06，2025/04/03，2025/04/14，2025/05/05，2025/05/15，2025/05/29，2025/06/20，2025/06/27，2025/08/07，2025/08/24，2025/09/17，2025/10/16，2025/11/10，2025/12/09，2025/12/17，2026/01/21，2026/02/12，2026/02/25，2026/07/27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/7，2025/11/9，2025/12/2，2026/1/21，2026/3/5，2026/4/16，2026/6/23，2026/7/5</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/28，2025/04/19，2025/04/24，2025/05/03，2025/05/15，2025/05/16，2025/05/22，2025/05/30，2025/06/14，2025/06/19，2025/06/26，2025/07/18，2025/08/04，2025/09/10，2025/09/18，2025/10/03，2026/2/7，2026/2/9，2026/2/27，2026/4/18，2026/6/6，2026/6/16，2026/6/17，2026/6/23</t>
+          <t>2025/03/06，2025/03/28，2025/04/19，2025/04/24，2025/05/03，2025/05/15，2025/05/16，2025/05/22，2025/05/30，2025/06/14，2025/06/19，2025/06/26，2025/07/18，2025/08/04，2025/09/10，2025/09/18，2025/10/03，2026/02/07，2026/02/09，2026/02/27，2026/04/18，2026/06/06，2026/06/16，2026/06/17，2026/06/23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/17，2025/05/18，2025/05/30，2025/06/06，2025/06/21，2025/06/27，2025/07/24，2025/08/24，2025/09/10，2025/09/30，2025/10/23，2025/11/10，2026/1/15，2026/2/14，2026/3/22，2026/5/20</t>
+          <t>2025/03/06，2025/04/17，2025/05/18，2025/05/30，2025/06/06，2025/06/21，2025/06/27，2025/07/24，2025/08/24，2025/09/10，2025/09/30，2025/10/23，2025/11/10，2026/01/15，2026/02/14，2026/03/22，2026/05/20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/06，2025/04/13，2025/04/22，2025/05/08，2025/05/09，2025/05/30，2025/06/08，2025/08/04，2025/09/18，2025/10/12，2025/11/21，2026/1/24，2026/2/14，2026/2/25，2026/4/10，2026/4/25</t>
+          <t>2025/03/06，2025/04/06，2025/04/13，2025/04/22，2025/05/08，2025/05/09，2025/05/30，2025/06/08，2025/08/04，2025/09/18，2025/10/12，2025/11/21，2026/01/24，2026/02/14，2026/02/25，2026/04/10，2026/04/25</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/13，2025/05/01，2025/06/15，2025/07/24，2025/08/30，2025/09/05，2025/10/09，2025/11/3，2025/12/12，2026/2/4，2026/4/18，2026/5/20，2026/6/20</t>
+          <t>2025/03/06，2025/04/13，2025/05/01，2025/06/15，2025/07/24，2025/08/30，2025/09/05，2025/10/09，2025/11/03，2025/12/12，2026/02/04，2026/04/18，2026/05/20，2026/06/20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/04，2025/04/19，2025/06/02，2025/06/17，2025/06/23，2025/07/20，2025/09/24，2025/10/09，2026/2/17，2026/3/7，2026/5/24</t>
+          <t>2025/03/07，2025/04/04，2025/04/19，2025/06/02，2025/06/17，2025/06/23，2025/07/20，2025/09/24，2025/10/09，2026/02/17，2026/03/07，2026/05/24</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/27，2025/04/07，2025/04/12，2025/04/22，2025/04/26，2025/05/05，2025/05/19，2025/06/03，2025/06/09，2025/07/18，2025/07/22，2025/09/10，2025/09/19，2025/10/16，2025/12/24，2026/6/20</t>
+          <t>2025/03/07，2025/03/27，2025/04/07，2025/04/12，2025/04/22，2025/04/26，2025/05/05，2025/05/19，2025/06/03，2025/06/09，2025/07/18，2025/07/22，2025/09/10，2025/09/19，2025/10/16，2025/12/24，2026/06/20</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025/03/07，2026/3/8</t>
+          <t>2025/03/07，2026/03/08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/25，2026/6/10</t>
+          <t>2025/03/07，2025/05/25，2026/06/10</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/05/04，2025/05/18，2025/06/09，2025/08/04，2025/08/16，2025/09/18，2025/10/17，2025/11/21，2025/11/28，2026/5/10</t>
+          <t>2025/03/07，2025/03/28，2025/05/04，2025/05/18，2025/06/09，2025/08/04，2025/08/16，2025/09/18，2025/10/17，2025/11/21，2025/11/28，2026/05/10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/7，2025/12/16，2025/12/28，2026/1/10，2026/1/15，2026/2/19，2026/3/7，2026/3/17，2026/3/21，2026/5/6，2026/7/5</t>
+          <t>2025/03/07，2025/04/20，2025/04/25，2025/05/18，2025/05/26，2025/06/02，2025/06/27，2025/07/07，2025/08/03，2025/09/14，2025/09/17，2025/10/03，2025/10/07，2025/12/07，2025/12/16，2025/12/28，2026/01/10，2026/01/15，2026/02/19，2026/03/07，2026/03/17，2026/03/21，2026/05/06，2026/07/05，2026/07/20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/7，2025/11/19，2025/11/26，2025/12/30，2026/1/28，2026/2/14，2026/3/13，2026/4/10，2026/5/23，2026/6/18，2026/6/29</t>
+          <t>2025/03/07，2025/04/06，2025/04/11，2025/04/18，2025/05/08，2025/05/25，2025/06/12，2025/07/03，2025/07/09，2025/07/29，2025/08/23，2025/09/13，2025/09/22，2025/09/26，2025/09/30，2025/10/23，2025/10/31，2025/11/07，2025/11/19，2025/11/26，2025/12/30，2026/01/28，2026/02/14，2026/03/13，2026/04/10，2026/05/23，2026/06/18，2026/06/29，2026/07/25</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/1，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/1/9，2026/1/22，2026/2/14，2026/3/22，2026/4/19，2026/5/1，2026/5/23，2026/6/25</t>
+          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/4，2025/12/24，2026/1/15，2026/2/23，2026/3/8，2026/4/14，2026/5/4，2026/5/23，2026/6/14</t>
+          <t>2025/03/07，2025/03/17，2025/03/28，2025/03/29，2025/04/13，2025/04/15，2025/04/18，2025/04/28，2025/05/22，2025/06/02，2025/06/03，2025/06/10，2025/06/12，2025/06/20，2025/06/20，2025/06/27，2025/07/05，2025/07/09，2025/07/13，2025/08/04，2025/08/08，2025/08/12，2025/08/24，2025/09/06，2025/10/07，2025/10/24，2025/11/24，2025/12/04，2025/12/24，2026/01/15，2026/02/23，2026/03/08，2026/04/14，2026/05/04，2026/05/23，2026/06/14，2026/07/27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/04，2025/04/12，2025/04/18，2025/04/24，2025/06/17，2025/06/19，2025/07/11，2025/07/18，2025/08/28，2025/09/05，2025/09/08，2025/09/27，2025/10/03，2025/12/11，2025/12/30，2026/1/21，2026/1/25，2026/2/10，2026/2/23，2026/3/6，2026/3/22，2026/4/24</t>
+          <t>2025/03/07，2025/04/04，2025/04/12，2025/04/18，2025/04/24，2025/06/17，2025/06/19，2025/07/11，2025/07/18，2025/08/28，2025/09/05，2025/09/08，2025/09/27，2025/10/03，2025/12/11，2025/12/30，2026/01/21，2026/01/25，2026/02/10，2026/02/23，2026/03/06，2026/03/22，2026/04/24</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/1，2025/11/9，2025/12/4，2025/12/16，2025/12/31，2026/1/9，2026/1/15，2026/1/21，2026/1/23，2026/1/29，2026/2/2，2026/2/7，2026/2/10，2026/2/14，2026/2/19，2026/2/24，2026/2/25，2026/2/27，2026/3/1，2026/3/4，2026/3/5，2026/3/7，2026/3/8，2026/3/9，2026/3/12，2026/3/13，2026/3/14，2026/3/15，2026/3/17，2026/3/18，2026/3/19，2026/3/22，2026/3/24，2026/3/27，2026/3/28，2026/3/31，2026/4/8，2026/4/14，2026/4/18，2026/4/25，2026/5/1，2026/5/15，2026/5/25，2026/6/12，2026/6/23，2026/6/26，2026/7/4</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/2，2025/12/26，2026/5/4，2026/6/28</t>
+          <t>2025/03/07，2025/04/14，2025/05/05，2025/05/19，2025/05/23，2025/06/13，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/12/02，2025/12/26，2026/05/04，2026/06/28</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/11，2025/04/29，2025/08/01，2025/10/26，2026/2/19，2026/2/23，2026/3/6</t>
+          <t>2025/03/07，2025/04/11，2025/04/29，2025/08/01，2025/10/26，2026/02/19，2026/02/23，2026/03/06</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/8，2026/1/12，2026/1/30，2026/2/7，2026/4/18，2026/5/23</t>
+          <t>2025/03/07，2025/05/01，2025/05/09，2025/05/26，2025/06/17，2025/06/20，2025/07/13，2025/09/12，2025/09/26，2025/10/11，2025/12/08，2026/01/12，2026/01/30，2026/02/07，2026/04/18，2026/05/23，2026/07/18</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/2/14，2026/5/4</t>
+          <t>2025/03/08，2025/04/06，2025/05/15，2025/05/26，2025/07/22，2025/09/17，2025/12/30，2026/02/14，2026/05/04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/4/9，2026/5/10，2026/6/12</t>
+          <t>2025/03/09，2025/03/21，2025/04/11，2025/04/15，2025/04/29，2025/05/08，2025/05/16，2025/05/22，2025/05/30，2025/06/06，2025/06/13，2025/06/30，2025/07/21，2025/09/19，2025/11/14，2025/11/22，2026/04/09，2026/05/10，2026/06/12，2026/07/27</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/2/2，2026/2/12，2026/4/14，2026/4/22，2026/6/10</t>
+          <t>2025/03/09，2025/03/24，2025/04/06，2025/04/21，2025/04/28，2025/05/08，2025/05/20，2025/06/08，2025/07/08，2025/07/28，2025/09/24，2025/09/30，2025/11/18，2025/12/24，2026/02/02，2026/02/12，2026/04/14，2026/04/22，2026/06/10</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/11，2025/05/20，2025/06/16，2025/06/24，2025/08/29，2025/09/12，2025/10/12，2026/1/9，2026/5/20</t>
+          <t>2025/03/09，2025/04/04，2025/04/11，2025/05/20，2025/06/16，2025/06/24，2025/08/29，2025/09/12，2025/10/12，2026/01/09，2026/05/20</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/06，2025/05/08，2025/05/24，2025/06/06，2025/07/05，2025/07/24，2025/08/04，2025/09/08，2025/09/19，2025/10/16，2025/10/28，2025/11/13，2025/12/16，2025/12/30，2026/2/19，2026/4/14，2026/6/12，2026/6/14</t>
+          <t>2025/03/09，2025/04/06，2025/05/08，2025/05/24，2025/06/06，2025/07/05，2025/07/24，2025/08/04，2025/09/08，2025/09/19，2025/10/16，2025/10/28，2025/11/13，2025/12/16，2025/12/30，2026/02/19，2026/04/14，2026/06/12，2026/06/14</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/1，2026/1/16，2026/2/2，2026/2/23，2026/3/8，2026/3/19，2026/3/21，2026/4/16，2026/5/10，2026/6/14</t>
+          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/01，2025/04/12，2025/04/28，2025/04/29，2025/05/09，2025/08/13，2025/08/24，2025/10/07，2025/11/12，2026/3/4</t>
+          <t>2025/03/09，2025/04/01，2025/04/12，2025/04/28，2025/04/29，2025/05/09，2025/08/13，2025/08/24，2025/10/07，2025/11/12，2026/03/04，2026/07/26</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/9，2026/1/1，2026/6/20</t>
+          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/1/15，2026/3/1，2026/5/5</t>
+          <t>2025/03/09，2025/05/12，2025/06/12，2025/07/21，2025/12/11，2026/01/15，2026/03/01，2026/05/05，2026/07/16</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/2/9，2026/4/8</t>
+          <t>2025/03/09，2025/04/04，2025/04/28，2025/07/08，2025/07/21，2025/08/18，2026/02/09，2026/04/08</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/3/27，2026/4/1，2026/6/23</t>
+          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/4/26</t>
+          <t>2025/03/10，2025/06/05，2025/07/05，2025/08/22，2026/04/26</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/05/03，2025/06/19，2026/1/19，2026/6/23</t>
+          <t>2025/03/12，2025/05/03，2025/06/19，2026/01/19，2026/06/23</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/1/1，2026/2/14，2026/5/6，2026/5/23</t>
+          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/04，2025/05/03，2025/06/15，2025/07/28，2025/09/04，2025/10/22，2026/3/4</t>
+          <t>2025/03/12，2025/04/04，2025/05/03，2025/06/15，2025/07/28，2025/09/04，2025/10/22，2026/03/04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/2，2026/2/9</t>
+          <t>2025/03/12，2025/04/11，2025/05/04，2025/05/18，2025/06/06，2025/06/27，2025/07/15，2025/08/16，2025/09/11，2025/09/18，2025/10/05，2025/12/02，2026/02/09</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/03/21，2025/04/04，2025/05/03，2025/06/21，2025/09/30，2025/10/22，2026/2/17</t>
+          <t>2025/03/12，2025/03/21，2025/04/04，2025/05/03，2025/06/21，2025/09/30，2025/10/22，2026/02/17</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/4，2025/11/7，2025/11/9，2025/12/4，2026/1/9，2026/1/19，2026/1/21，2026/1/25，2026/3/4，2026/3/7，2026/3/14，2026/6/6，2026/6/19</t>
+          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/3，2025/12/2，2025/12/4，2025/12/12，2026/1/5，2026/1/14，2026/2/19，2026/3/4，2026/3/31，2026/4/12，2026/4/29，2026/5/15，2026/6/12，2026/6/23</t>
+          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/19，2025/08/16，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/1/14，2026/2/4，2026/5/20</t>
+          <t>2025/03/12，2025/04/13，2025/05/01，2025/05/06，2025/05/24，2025/06/09，2025/06/24，2025/07/08，2025/08/19，2025/08/16，2025/09/08，2025/10/07，2025/10/28，2025/11/18，2025/12/11，2026/01/14，2026/02/04，2026/05/20，2026/07/09</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/11，2025/04/26，2025/04/29，2025/05/18，2025/06/02，2025/06/27，2025/07/05，2025/07/15，2025/08/02，2025/09/10</t>
+          <t>2025/03/13，2025/04/11，2025/04/26，2025/04/29，2025/05/18，2025/06/02，2025/06/27，2025/07/05，2025/07/15，2025/08/02，2025/09/10，2026/07/16</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/03，2025/05/26，2025/06/01，2025/06/06，2025/09/08，2025/09/12，2026/4/9，2026/6/20</t>
+          <t>2025/03/13，2025/04/03，2025/05/26，2025/06/01，2025/06/06，2025/09/08，2025/09/12，2026/04/09，2026/06/20，2026/07/22</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/12，2025/05/19，2025/05/25，2025/07/05，2025/08/12，2025/09/03，2025/09/10，2025/11/14，2025/12/31，2026/2/18，2026/6/6</t>
+          <t>2025/03/13，2025/04/12，2025/05/19，2025/05/25，2025/07/05，2025/08/12，2025/09/03，2025/09/10，2025/11/14，2025/12/31，2026/02/18，2026/06/06</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/05/10，2025/05/24，2025/06/20，2025/07/13，2025/08/23，2025/09/05，2025/09/18，2025/09/30，2025/11/27，2026/2/7</t>
+          <t>2025/03/13，2025/05/10，2025/05/24，2025/06/20，2025/07/13，2025/08/23，2025/09/05，2025/09/18，2025/09/30，2025/11/27，2026/02/07</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/30，2025/04/17，2025/04/21，2025/05/05，2025/05/13，2025/05/20，2025/06/06，2025/06/20，2025/06/27，2025/07/05，2025/07/31，2025/08/24，2025/08/29，2025/09/20，2025/09/30，2025/10/22，2025/11/26，2026/1/15，2026/2/14，2026/4/8，2026/5/20</t>
+          <t>2025/03/13，2025/03/30，2025/04/17，2025/04/21，2025/05/05，2025/05/13，2025/05/20，2025/06/06，2025/06/20，2025/06/27，2025/07/05，2025/07/31，2025/08/24，2025/08/29，2025/09/20，2025/09/30，2025/10/22，2025/11/26，2026/01/15，2026/02/14，2026/04/08，2026/05/20</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/21，2025/05/15，2025/07/28，2025/09/10，2026/1/14，2026/6/28</t>
+          <t>2025/03/13，2025/04/21，2025/05/15，2025/07/28，2025/09/10，2026/01/14，2026/06/28</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/17，2025/05/04，2025/05/13，2025/07/22，2025/09/05，2025/09/28，2026/6/3</t>
+          <t>2025/03/13，2025/04/17，2025/05/04，2025/05/13，2025/07/22，2025/09/05，2025/09/28，2026/06/03</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/9，2026/1/23，2026/2/18，2026/4/9，2026/6/15</t>
+          <t>2025/03/13，2025/03/28，2025/04/11，2025/04/25，2025/05/15，2025/05/29，2025/06/20，2025/07/13，2025/09/19，2025/10/05，2025/10/23，2025/11/09，2026/01/23，2026/02/18，2026/04/09，2026/06/15，2026/07/22</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/13，2025/04/19，2025/05/06，2025/06/03，2025/08/28，2025/09/17，2025/10/10，2025/11/17，2025/11/22，2025/12/24，2026/1/15，2026/1/29，2026/3/19，2026/5/15</t>
+          <t>2025/03/13，2025/04/13，2025/04/19，2025/05/06，2025/06/03，2025/08/28，2025/09/17，2025/10/10，2025/11/17，2025/11/22，2025/12/24，2026/01/15，2026/01/29，2026/03/19，2026/05/15</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/2/10，2026/2/24，2026/3/18，2026/5/20，2026/6/19</t>
+          <t>2025/03/13，2025/03/14，2025/03/29，2025/04/19，2025/04/26，2025/05/09，2025/05/19，2025/05/22，2025/05/25，2025/07/03，2025/07/05，2025/07/28，2025/08/04，2025/08/21，2025/09/30，2025/11/14，2025/11/17，2026/02/10，2026/02/24，2026/03/18，2026/05/20，2026/06/19</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/05/12，2025/05/22，2025/06/16，2025/06/30，2025/08/01，2025/08/16，2025/09/19，2025/10/05，2025/11/18，2025/12/23，2026/1/9，2026/2/27，2026/4/29，2026/7/5</t>
+          <t>2025/03/13，2025/05/12，2025/05/22，2025/06/16，2025/06/30，2025/08/01，2025/08/16，2025/09/19，2025/10/05，2025/11/18，2025/12/23，2026/01/09，2026/02/27，2026/04/29，2026/07/05，2026/07/22</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/19，2025/05/20，2025/07/26，2025/08/16，2025/12/11，2026/4/9，2026/4/18</t>
+          <t>2025/03/14，2025/05/19，2025/05/20，2025/07/26，2025/08/16，2025/12/11，2026/04/09，2026/04/18，2026/07/22</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/15，2025/06/06，2025/07/31，2025/09/12，2026/4/9</t>
+          <t>2025/03/14，2025/05/15，2025/06/06，2025/07/31，2025/09/12，2026/04/09</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/05/15，2025/06/07，2025/07/18，2025/09/12，2025/11/9，2025/11/22，2026/3/9，2026/4/14，2026/5/20</t>
+          <t>2025/03/14，2025/03/28，2025/05/15，2025/06/07，2025/07/18，2025/09/12，2025/11/09，2025/11/22，2026/03/09，2026/04/14，2026/05/20</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/14，2025/04/14，2025/05/26，2025/06/02，2025/06/12，2025/06/23，2025/07/06，2025/07/10，2025/07/25，2025/08/23，2025/09/20，2025/11/9，2026/3/25，2026/4/26，2026/6/15</t>
+          <t>2025/03/14，2025/03/14，2025/04/14，2025/05/26，2025/06/02，2025/06/12，2025/06/23，2025/07/06，2025/07/10，2025/07/25，2025/08/23，2025/09/20，2025/11/09，2026/03/25，2026/04/26，2026/06/15</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/02，2025/05/12，2025/05/23，2025/06/26，2025/07/08，2025/07/31，2025/08/22，2025/09/02，2025/09/15，2025/10/10，2025/11/3，2026/2/2，2026/4/1，2026/5/20</t>
+          <t>2025/03/14，2025/04/02，2025/05/12，2025/05/23，2025/06/26，2025/07/08，2025/07/31，2025/08/22，2025/09/02，2025/09/15，2025/10/10，2025/11/03，2026/02/02，2026/04/01，2026/05/20，2026/07/26</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/1，2026/2/14，2026/6/28</t>
+          <t>2025/03/14，2025/03/20，2025/04/07，2025/05/06，2025/05/18，2025/05/30，2025/06/16，2025/06/27，2025/08/13，2025/08/24，2025/09/18，2025/09/19，2025/11/01，2026/02/14，2026/06/28，2026/07/22</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/2/8，2026/4/9</t>
+          <t>2025/03/14，2025/04/17，2025/04/25，2025/06/23，2025/08/30，2025/09/12，2025/09/15，2025/11/19，2026/02/08，2026/04/09，2026/07/16</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/1/12，2026/2/7，2026/3/15，2026/4/19，2026/6/26</t>
+          <t>2025/03/14，2025/04/14，2025/05/06，2025/05/30，2025/07/22，2025/08/26，2025/09/03，2025/10/10，2025/11/13，2025/12/19，2026/01/12，2026/02/07，2026/03/15，2026/04/19，2026/06/26</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/15，2025/06/30，2025/08/13，2025/10/25，2026/3/13，2026/6/12</t>
+          <t>2025/03/14，2025/05/15，2025/06/30，2025/08/13，2025/10/25，2026/03/13，2026/06/12，2026/07/17</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/19，2025/07/21，2025/10/20，2025/11/9，2026/1/14，2026/2/19，2026/4/19，2026/6/3</t>
+          <t>2025/03/14，2025/05/19，2025/07/21，2025/10/20，2025/11/09，2026/01/14，2026/02/19，2026/04/19，2026/06/03</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/06/06，2025/06/27，2025/08/01，2025/11/9，2025/11/14，2026/6/12</t>
+          <t>2025/03/14，2025/06/06，2025/06/27，2025/08/01，2025/11/09，2025/11/14，2026/06/12</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/11，2025/04/25，2025/06/05，2025/06/15，2025/07/07，2025/09/11，2025/10/10，2025/11/14，2025/12/9，2026/4/8</t>
+          <t>2025/03/14，2025/04/11，2025/04/25，2025/06/05，2025/06/15，2025/07/07，2025/09/11，2025/10/10，2025/11/14，2025/12/09，2026/04/08，2026/07/27</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/9</t>
+          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/9，2026/1/15，2026/2/19，2026/3/13，2026/3/15，2026/3/21，2026/6/14，2026/6/17</t>
+          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/1/19，2026/4/18，2026/5/1，2026/5/23</t>
+          <t>2025/03/14，2025/04/24，2025/05/03，2025/06/23，2025/08/21，2025/10/07，2025/10/31，2026/01/19，2026/04/18，2026/05/01，2026/05/23，2026/07/17</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/05，2025/07/22，2026/2/27，2026/4/9，2026/4/14，2026/4/22，2026/6/10，2026/6/19</t>
+          <t>2025/03/14，2025/04/05，2025/07/22，2026/02/27，2026/04/09，2026/04/14，2026/04/22，2026/06/10，2026/06/19</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/1/2，2026/1/30，2026/4/9</t>
+          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/3，2025/11/24，2026/4/9，2026/4/14，2026/4/24，2026/5/23</t>
+          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/12，2025/05/20，2025/05/30，2025/06/27，2025/08/13，2025/09/11，2025/10/28，2025/12/20，2026/1/16，2026/4/17</t>
+          <t>2025/03/14，2025/04/12，2025/05/20，2025/05/30，2025/06/27，2025/08/13，2025/09/11，2025/10/28，2025/12/20，2026/01/16，2026/04/17</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/06，2025/04/11，2025/04/29，2025/06/09，2025/09/26，2025/11/22，2026/3/8</t>
+          <t>2025/03/14，2025/04/06，2025/04/11，2025/04/29，2025/06/09，2025/09/26，2025/11/22，2026/03/08</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/06/19，2025/07/10，2025/09/07，2025/09/21，2025/12/1，2026/2/14，2026/3/6</t>
+          <t>2025/03/21，2025/06/19，2025/07/10，2025/09/07，2025/09/21，2025/12/01，2026/02/14，2026/03/06</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/23，2025/07/22，2026/4/9</t>
+          <t>2025/03/14，2025/05/23，2025/07/22，2026/04/09</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2025/3/14</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/05，2025/05/15，2025/08/12，2026/3/28</t>
+          <t>2025/03/15，2025/04/05，2025/05/15，2025/08/12，2026/03/28</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/3/5</t>
+          <t>2025/03/15，2025/06/26，2025/08/04，2025/09/18，2025/10/25，2026/03/05，2026/07/28</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/05/22，2025/06/10，2025/11/9，2025/11/14，2026/3/19，2026/6/15</t>
+          <t>2025/03/15，2025/05/22，2025/06/10，2025/11/09，2025/11/14，2026/03/19，2026/06/15</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/8，2025/12/12，2026/2/14，2026/3/12，2026/4/9，2026/5/10，2026/5/23，2026/6/6，2026/6/25</t>
+          <t>2025/03/15，2025/04/03，2025/04/11，2025/04/29，2025/05/18，2025/05/26，2025/06/02，2025/07/03，2025/08/21，2025/09/12，2025/11/19，2025/12/08，2025/12/12，2026/02/14，2026/03/12，2026/04/09，2026/05/10，2026/05/23，2026/06/06，2026/06/25，2026/07/18</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/05/12，2025/06/23，2025/09/04，2025/12/23，2026/5/5</t>
+          <t>2025/03/15，2025/05/12，2025/06/23，2025/09/04，2025/12/23，2026/05/05，2026/07/16</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/2/7，2026/6/23</t>
+          <t>2025/03/16，2025/04/17，2025/05/08，2025/09/11，2025/10/03，2025/10/16，2025/11/19，2026/02/07，2026/06/23</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/7，2025/12/23，2026/1/5，2026/1/21，2026/1/29，2026/2/9，2026/2/20，2026/2/23，2026/3/4，2026/3/6，2026/3/7，2026/4/11，2026/4/14，2026/4/29，2026/5/23，2026/7/3</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/7，2026/3/6，2026/4/2，2026/6/20</t>
+          <t>2025/03/17，2025/04/14，2025/04/29，2025/07/15，2025/07/25，2025/08/04，2025/08/22，2025/09/11，2025/09/30，2025/10/25，2025/11/07，2026/03/06，2026/04/02，2026/06/20，2026/07/22</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/27，2025/04/25，2025/05/01，2025/05/15，2025/06/10，2025/07/03，2025/09/11，2025/12/11，2026/1/9</t>
+          <t>2025/03/17，2025/03/27，2025/04/25，2025/05/01，2025/05/15，2025/06/10，2025/07/03，2025/09/11，2025/12/11，2026/01/09</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/07，2025/04/17，2025/04/28，2025/05/20，2025/06/03，2025/07/11，2025/08/04，2025/09/11，2025/09/24，2025/10/07，2025/11/26，2025/12/24，2026/2/7</t>
+          <t>2025/03/17，2025/04/07，2025/04/17，2025/04/28，2025/05/20，2025/06/03，2025/07/11，2025/08/04，2025/09/11，2025/09/24，2025/10/07，2025/11/26，2025/12/24，2026/02/07，2026/07/16</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/9，2026/1/12，2026/4/26</t>
+          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/05/17，2025/6/1，2025/09/21，2025/10/09，2025/11/26</t>
+          <t>2025/03/17，2025/05/17，2025/06/01，2025/09/21，2025/10/09，2025/11/26</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2025/3/17</t>
+          <t>2025/03/17</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/9，2026/4/26</t>
+          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/12，2025/09/02，2025/11/9，2025/12/4，2026/1/1，2026/1/29，2026/4/9，2026/6/15</t>
+          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/12，2025/09/02，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/2，2025/12/17，2026/1/9，2026/1/15，2026/2/2，2026/2/14，2026/3/13，2026/3/25，2026/4/24，2026/5/23，2026/6/17，2026/7/5</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/1，2026/1/15，2026/4/8</t>
+          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/1/3，2026/1/5，2026/1/30，2026/3/14，2026/3/31，2026/4/20，2026/5/1，2026/6/19，2026/6/30</t>
+          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/07/07，2025/08/12，2025/08/26，2025/09/13，2025/09/17，2025/10/10，2025/11/21，2025/12/11，2026/1/2，2026/1/15，2026/1/28，2026/2/19，2026/3/5，2026/4/9，2026/6/6，2026/6/20</t>
+          <t>2025/03/19，2025/07/07，2025/08/12，2025/08/26，2025/09/13，2025/09/17，2025/10/10，2025/11/21，2025/12/11，2026/01/02，2026/01/15，2026/01/28，2026/02/19，2026/03/05，2026/04/09，2026/06/06，2026/06/20</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/05，2025/04/24，2025/05/12，2025/06/19，2025/07/11，2025/07/31，2025/09/03，2025/09/20，2025/10/17，2025/11/9，2025/11/21，2026/1/15</t>
+          <t>2025/03/19，2025/04/05，2025/04/24，2025/05/12，2025/06/19，2025/07/11，2025/07/31，2025/09/03，2025/09/20，2025/10/17，2025/11/09，2025/11/21，2026/01/15</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/1/10，2026/4/9</t>
+          <t>2025/03/19，2025/04/07，2025/05/13，2025/06/10，2025/08/21，2025/11/19，2026/01/10，2026/04/09</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/08，2025/04/18，2025/05/12，2025/05/23，2025/06/27，2025/07/24，2025/08/28，2025/10/11，2025/10/31，2025/11/24，2025/12/19，2026/2/2，2026/4/19</t>
+          <t>2025/03/19，2025/04/08，2025/04/18，2025/05/12，2025/05/23，2025/06/27，2025/07/24，2025/08/28，2025/10/11，2025/10/31，2025/11/24，2025/12/19，2026/02/02，2026/04/19，2026/07/25</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/04/11，2025/05/19，2025/05/23，2025/06/12，2025/06/23，2025/07/20，2025/08/19，2025/09/21，2025/10/07，2025/10/20，2025/10/28，2025/11/9，2025/11/24，2025/12/16，2025/12/24，2025/12/26，2026/5/23</t>
+          <t>2025/03/19，2025/03/28，2025/04/11，2025/05/19，2025/05/23，2025/06/12，2025/06/23，2025/07/20，2025/08/19，2025/09/21，2025/10/07，2025/10/20，2025/10/28，2025/11/09，2025/11/24，2025/12/16，2025/12/24，2025/12/26，2026/05/23</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/4，2026/1/3，2026/2/10，2026/3/13，2026/3/22，2026/4/14，2026/6/17</t>
+          <t>2025/03/19，2025/04/07，2025/04/17，2025/04/22，2025/05/22，2025/06/23，2025/07/09，2025/08/26，2025/09/28，2025/11/21，2025/12/04，2026/01/03，2026/02/10，2026/03/13，2026/03/22，2026/04/14，2026/06/17</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/05/18，2025/06/13，2025/09/12，2025/10/01，2026/4/20，2026/6/10</t>
+          <t>2025/03/19，2025/04/07，2025/05/18，2025/06/13，2025/09/12，2025/10/01，2026/04/20，2026/06/10</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/1/1，2026/1/9，2026/3/22，2026/4/9，2026/4/20，2026/5/25，2026/6/10，2026/6/19</t>
+          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/4/26，2026/6/19，2026/6/20</t>
+          <t>2025/03/19，2025/04/17，2025/05/20，2025/05/31，2025/09/15，2025/10/13，2025/10/22，2025/12/24，2026/04/26，2026/06/19，2026/06/20</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/04/17，2025/04/21，2025/04/29，2025/05/08，2025/05/30，2025/06/13，2025/06/26，2025/07/08，2025/07/18，2025/08/22，2025/09/05，2025/09/28，2025/10/25，2025/11/10，2025/11/27，2025/12/8，2025/12/24，2026/1/28，2026/4/22，2026/5/5，2026/6/14</t>
+          <t>2025/03/20，2025/04/04，2025/04/17，2025/04/21，2025/04/29，2025/05/08，2025/05/30，2025/06/13，2025/06/26，2025/07/08，2025/07/18，2025/08/22，2025/09/05，2025/09/28，2025/10/25，2025/11/10，2025/11/27，2025/12/08，2025/12/24，2026/01/28，2026/04/22，2026/05/05，2026/06/14，2026/07/22</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/2，2026/1/16，2026/2/2，2026/2/23，2026/2/25，2026/3/17，2026/4/8，2026/5/6，2026/5/21，2026/6/25</t>
+          <t>2025/03/20，2025/05/19，2025/06/12，2025/06/19，2025/06/23，2025/07/11，2025/08/03，2025/08/12，2025/08/21，2025/09/15，2025/10/07，2025/12/02，2026/01/16，2026/02/02，2026/02/23，2026/02/25，2026/03/17，2026/04/08，2026/05/06，2026/05/21，2026/06/25，2026/07/18</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/1/22，2026/1/25，2026/2/19，2026/5/20，2026/7/2</t>
+          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/23，2025/07/21，2025/08/08，2025/09/05，2026/1/29</t>
+          <t>2025/03/20，2025/05/23，2025/07/21，2025/08/08，2025/09/05，2026/01/29</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/05/22，2025/05/29，2025/06/03，2025/08/28，2025/09/11，2025/10/18，2025/10/30，2025/11/28，2025/12/28，2026/3/15，2026/5/19</t>
+          <t>2025/03/20，2025/05/22，2025/05/29，2025/06/03，2025/08/28，2025/09/11，2025/10/18，2025/10/30，2025/11/28，2025/12/28，2026/03/15，2026/05/19，2026/07/13</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/8，2026/1/23，2026/1/26，2026/2/7，2026/2/10，2026/2/23，2026/2/25，2026/2/27，2026/3/1，2026/3/4，2026/3/13，2026/3/24，2026/3/28，2026/3/29，2026/4/27，2026/5/2，2026/6/18，2026/7/4</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/11，2025/04/22，2025/05/08，2025/06/12，2025/08/22，2025/08/29，2025/09/05，2025/11/19，2025/12/31，2026/2/14，2026/4/24</t>
+          <t>2025/03/20，2025/04/11，2025/04/22，2025/05/08，2025/06/12，2025/08/22，2025/08/29，2025/09/05，2025/11/19，2025/12/31，2026/02/14，2026/04/24</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/13，2025/05/30，2025/06/06，2025/07/08，2025/08/07，2025/08/22，2025/09/30，2025/11/9，2025/11/13，2025/12/31，2026/4/16，2026/6/20</t>
+          <t>2025/03/20，2025/04/17，2025/05/13，2025/05/30，2025/06/06，2025/07/08，2025/08/07，2025/08/22，2025/09/30，2025/11/09，2025/11/13，2025/12/31，2026/04/16，2026/06/20</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/06/26，2026/4/14，2026/6/10</t>
+          <t>2025/03/20，2025/06/26，2026/04/14，2026/06/10</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/1/16，2026/2/7，2026/3/28</t>
+          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/8，2025/12/26，2026/1/5，2026/1/24，2026/2/5，2026/2/14，2026/3/9，2026/3/28，2026/4/26，2026/5/5，2026/5/23，2026/6/12</t>
+          <t>2025/03/20，2025/03/29，2025/05/09，2025/05/18，2025/05/22，2025/05/26，2025/06/13，2025/06/23，2025/07/07，2025/07/14，2025/07/18，2025/08/07，2025/08/19，2025/08/28，2025/09/12，2025/09/28，2025/10/09，2025/12/08，2025/12/26，2026/01/05，2026/01/24，2026/02/05，2026/02/14，2026/03/09，2026/03/28，2026/04/26，2026/05/05，2026/05/23，2026/06/12</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/06/28，2025/08/04，2026/1/19，2026/4/8</t>
+          <t>2025/03/21，2025/06/28，2025/08/04，2026/01/19，2026/04/08</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/12，2025/12/7，2026/4/24</t>
+          <t>2025/03/21，2025/05/12，2025/12/07，2026/04/24</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2025/3/21，2026/6/12</t>
+          <t>2025/03/21，2026/06/12</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2025/3/21</t>
+          <t>2025/03/21</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/2/9，2026/3/4，2026/3/25，2026/3/29，2026/5/23</t>
+          <t>2025/03/21，2025/05/19，2025/06/13，2025/07/22，2025/07/23，2025/08/25，2025/09/12，2025/10/26，2025/12/17，2026/02/09，2026/03/04，2026/03/25，2026/03/29，2026/05/23</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/24，2025/06/05，2025/07/26，2025/09/21，2025/10/16，2025/10/30，2025/11/9，2026/1/9，2026/4/24，2026/5/23，2026/6/20</t>
+          <t>2025/03/21，2025/04/24，2025/06/05，2025/07/26，2025/09/21，2025/10/16，2025/10/30，2025/11/09，2026/01/09，2026/04/24，2026/05/23，2026/06/20，2026/07/19</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/6，2026/2/7，2026/3/24，2026/4/26，2026/5/4，2026/5/23</t>
+          <t>2025/03/21，2025/04/13，2025/06/07，2025/06/16，2025/09/14，2025/10/05，2025/10/31，2025/11/12，2025/12/06，2026/02/07，2026/03/24，2026/04/26，2026/05/04，2026/05/23，2026/07/09，2026/07/27</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/9，2026/1/9，2026/5/4</t>
+          <t>2025/03/21，2025/04/14，2025/05/12，2025/06/07，2025/07/06，2025/07/21，2025/09/14，2025/10/31，2025/11/09，2026/01/09，2026/05/04，2026/07/27</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/03/29，2025/04/25，2025/05/30，2025/06/22，2025/07/18，2025/09/03，2025/09/13，2026/4/16</t>
+          <t>2025/03/21，2025/03/29，2025/04/25，2025/05/30，2025/06/22，2025/07/18，2025/09/03，2025/09/13，2026/04/16</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2025/3/21</t>
+          <t>2025/03/21</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/3，2025/11/22，2026/1/22，2026/2/19，2026/3/15，2026/4/2，2026/5/1，2026/5/23</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/06/26，2025/10/24，2026/4/1</t>
+          <t>2025/03/21，2025/06/26，2025/10/24，2026/04/01</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/8，2026/2/18，2026/3/6，2026/3/13，2026/3/14，2026/3/31，2026/5/1，2026/6/28</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/04，2025/04/19，2025/05/26，2025/06/02，2025/07/27，2025/09/06，2025/09/08，2025/10/11，2026/4/2</t>
+          <t>2025/03/21，2025/04/04，2025/04/19，2025/05/26，2025/06/02，2025/07/27，2025/09/06，2025/09/08，2025/10/11，2026/04/02</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/04，2025/04/18，2025/04/25，2025/05/01，2025/05/25，2025/06/02，2025/06/06，2025/12/26，2026/1/21，2026/3/12</t>
+          <t>2025/03/21，2025/04/04，2025/04/18，2025/04/25，2025/05/01，2025/05/25，2025/06/02，2025/06/06，2025/12/26，2026/01/21，2026/03/12</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/1/19，2026/3/9，2026/4/18，2026/4/20，2026/5/10，2026/6/19，2026/6/26</t>
+          <t>2025/03/21，2025/05/01，2025/05/24，2025/06/05，2025/06/26，2025/07/24，2025/09/11，2025/10/17，2025/10/23，2025/11/19，2026/01/19，2026/03/09，2026/04/18，2026/04/20，2026/05/10，2026/06/19，2026/06/26，2026/07/27</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/07，2025/04/18，2025/05/08，2025/10/24，2025/12/12，2026/4/26</t>
+          <t>2025/03/21，2025/04/07，2025/04/18，2025/05/08，2025/10/24，2025/12/12，2026/04/26</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/3/25</t>
+          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/1，2025/11/26，2025/12/2，2026/2/14</t>
+          <t>2025/03/21，2025/04/05，2025/05/18，2025/06/12，2025/07/14，2025/07/15，2025/08/02，2025/08/30，2025/10/03，2025/11/01，2025/11/26，2025/12/02，2026/02/14，2026/07/09</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/2，2025/12/5，2025/12/30，2026/1/23，2026/1/29，2026/2/23，2026/3/17，2026/3/22，2026/4/19，2026/5/10，2026/6/12</t>
+          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/06/24，2026/5/20</t>
+          <t>2025/03/22，2025/06/24，2026/05/20</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/1/1，2026/5/10</t>
+          <t>2025/03/22，2025/04/03，2025/04/19，2025/05/26，2025/09/18，2025/10/17，2026/01/01，2026/05/10</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/01，2025/05/12，2025/05/31，2025/07/11，2025/08/16，2025/09/19，2025/09/24，2025/11/18，2026/1/9，2026/2/14</t>
+          <t>2025/03/23，2025/04/01，2025/05/12，2025/05/31，2025/07/11，2025/08/16，2025/09/19，2025/09/24，2025/11/18，2026/01/09，2026/02/14</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/1/29，2026/2/9，2026/3/25，2026/4/19，2026/5/23，2026/6/12</t>
+          <t>2025/03/23，2025/03/28，2025/04/06，2025/05/15，2025/05/22，2025/05/29，2025/06/07，2025/06/09，2025/07/06，2025/07/15，2025/09/06，2025/09/14，2025/09/30，2025/11/13，2026/01/29，2026/02/09，2026/03/25，2026/04/19，2026/05/23，2026/06/12，2026/07/22，2026/07/27</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/17，2025/05/25，2025/12/2，2026/1/14，2026/6/6</t>
+          <t>2025/03/23，2025/04/17，2025/05/25，2025/12/02，2026/01/14，2026/06/06</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/12，2025/09/11，2025/10/31，2026/1/9，2026/7/5</t>
+          <t>2025/03/23，2025/04/10，2025/05/01，2025/05/19，2025/06/08，2025/07/14，2025/09/12，2025/09/11，2025/10/31，2026/01/09，2026/07/05</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/02，2025/05/18，2025/06/19，2025/07/07，2025/09/04，2025/09/12，2026/1/19，2026/4/9</t>
+          <t>2025/03/24，2025/04/02，2025/05/18，2025/06/19，2025/07/07，2025/09/04，2025/09/12，2026/01/19，2026/04/09</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/7，2026/1/17，2026/2/14，2026/4/9，2026/5/20，2026/6/19，2026/6/28</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/06/23，2026/1/9，2026/4/9</t>
+          <t>2025/03/24，2025/06/23，2026/01/09，2026/04/09</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/11，2025/04/20，2025/05/17，2025/05/22，2025/06/07，2025/06/21，2025/07/06，2025/07/28，2025/09/03，2025/09/14，2025/11/9，2026/1/1，2026/2/7，2026/3/25，2026/4/26，2026/6/23</t>
+          <t>2025/03/25，2025/04/11，2025/04/20，2025/05/17，2025/05/22，2025/06/07，2025/06/21，2025/07/06，2025/07/28，2025/09/03，2025/09/14，2025/11/09，2026/01/01，2026/02/07，2026/03/25，2026/04/26，2026/06/23</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/05，2025/06/23，2025/09/15，2025/12/7，2026/6/12</t>
+          <t>2025/03/25，2025/05/05，2025/06/23，2025/09/15，2025/12/07，2026/06/12</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/22，2025/06/19，2026/1/19</t>
+          <t>2025/03/25，2025/04/22，2025/06/19，2026/01/19</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/07/24，2025/07/29，2025/07/31，2025/09/04，2025/09/24，2025/10/03，2025/10/16，2025/11/18，2025/11/21，2026/3/5，2026/6/6</t>
+          <t>2025/03/25，2025/07/24，2025/07/29，2025/07/31，2025/09/04，2025/09/24，2025/10/03，2025/10/16，2025/11/18，2025/11/21，2026/03/05，2026/06/06</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/3/25，2026/6/23</t>
+          <t>2025/03/25，2025/05/13，2025/05/29，2025/06/17，2025/08/22，2025/09/04，2026/03/25，2026/06/23</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/24，2025/11/27，2026/4/14，2026/6/10</t>
+          <t>2025/03/25，2025/09/24，2025/11/27，2026/04/14，2026/06/10</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/18，2025/06/02，2026/2/19，2026/5/23</t>
+          <t>2025/03/25，2025/04/18，2025/06/02，2026/02/19，2026/05/23</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/05/20，2025/06/01，2025/07/15，2025/09/27，2025/10/03，2026/3/9，2026/6/26</t>
+          <t>2025/03/25，2025/05/20，2025/06/01，2025/07/15，2025/09/27，2025/10/03，2026/03/09，2026/06/26</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/18，2025/04/24，2025/06/23，2025/09/29，2025/12/17，2026/4/8，2026/5/21</t>
+          <t>2025/03/25，2025/04/18，2025/04/24，2025/06/23，2025/09/29，2025/12/17，2026/04/08，2026/05/21</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/9</t>
+          <t>2025/03/25，2025/09/19，2025/10/10，2025/11/09</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/06，2025/05/01，2025/06/23，2025/07/09，2025/09/05，2025/09/15，2025/10/16，2025/11/19，2025/12/17，2026/4/9</t>
+          <t>2025/03/25，2025/04/06，2025/05/01，2025/06/23，2025/07/09，2025/09/05，2025/09/15，2025/10/16，2025/11/19，2025/12/17，2026/04/09，2026/07/16</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/2/14，2026/2/23，2026/2/25，2026/3/9，2026/3/15</t>
+          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/24，2025/05/13，2025/06/02，2025/06/27，2025/07/14，2025/08/26，2025/09/02，2025/10/03，2025/10/17，2025/11/21，2026/02/14，2026/02/23，2026/02/25，2026/03/09，2026/03/15</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/1/14，2026/6/28</t>
+          <t>2025/03/27，2025/04/17，2025/05/15，2025/05/27，2025/11/27，2025/12/24，2026/01/14，2026/06/28</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/28，2025/04/29，2025/05/12，2025/06/06，2025/06/16，2025/07/24，2025/08/01，2025/09/05，2025/09/26，2025/10/28，2025/12/5，2026/1/9，2026/2/19，2026/3/22，2026/4/16</t>
+          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/28，2025/04/29，2025/05/12，2025/06/06，2025/06/16，2025/07/24，2025/08/01，2025/09/05，2025/09/26，2025/10/28，2025/12/05，2026/01/09，2026/02/19，2026/03/22，2026/04/16</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/06/08，2025/07/13，2025/07/21，2025/07/24，2025/07/28，2025/08/01，2025/08/16，2025/09/26，2025/10/28，2025/11/10，2025/11/17，2025/12/23，2026/4/17，2026/5/25，2026/6/26</t>
+          <t>2025/03/27，2025/06/08，2025/07/13，2025/07/21，2025/07/24，2025/07/28，2025/08/01，2025/08/16，2025/09/26，2025/10/28，2025/11/10，2025/11/17，2025/12/23，2026/04/17，2026/05/25，2026/06/26</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/22，2025/04/28，2025/06/30，2026/3/6</t>
+          <t>2025/03/27，2025/04/22，2025/04/28，2025/06/30，2026/03/06</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/15，2025/05/08，2025/06/10，2025/07/07，2025/08/04，2025/09/04，2025/10/01，2025/11/26，2026/1/10，2026/3/22，2026/6/20</t>
+          <t>2025/03/27，2025/04/15，2025/05/08，2025/06/10，2025/07/07，2025/08/04，2025/09/04，2025/10/01，2025/11/26，2026/01/10，2026/03/22，2026/06/20，2026/07/20</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/09，2025/05/29，2025/07/24，2025/09/04，2025/10/24，2025/11/19，2026/3/25，2026/4/9，2026/5/10，2026/6/10</t>
+          <t>2025/03/27，2025/05/09，2025/05/29，2025/07/24，2025/09/04，2025/10/24，2025/11/19，2026/03/25，2026/04/09，2026/05/10，2026/06/10</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2025/3/27</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/1/16，2026/2/2，2026/2/7，2026/3/31，2026/4/17，2026/4/29，2026/5/15，2026/5/19，2026/6/12</t>
+          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/22，2025/05/20，2025/06/27，2025/09/12，2025/11/9，2025/11/14，2025/12/9，2026/1/31</t>
+          <t>2025/03/28，2025/04/22，2025/05/20，2025/06/27，2025/09/12，2025/11/09，2025/11/14，2025/12/09，2026/01/31</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/1/16，2026/6/6</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/29，2025/06/09，2025/07/24，2025/08/01，2025/08/03，2025/08/16，2025/09/08，2025/09/12，2025/10/03，2025/10/30，2026/1/10，2026/3/1，2026/3/12，2026/4/1，2026/5/1，2026/6/10</t>
+          <t>2025/03/28，2025/04/29，2025/06/09，2025/07/24，2025/08/01，2025/08/03，2025/08/16，2025/09/08，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/01，2026/03/12，2026/04/01，2026/05/01，2026/06/10</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/23，2025/06/13，2025/06/26，2025/07/11，2025/09/18，2025/11/3，2025/12/23，2025/12/26，2026/1/24，2026/6/3</t>
+          <t>2025/03/28，2025/05/23，2025/06/13，2025/06/26，2025/07/11，2025/09/18，2025/11/03，2025/12/23，2025/12/26，2026/01/24，2026/06/03，2026/07/18</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/25，2026/3/8，2026/3/13</t>
+          <t>2025/03/28，2025/05/25，2026/03/08，2026/03/13</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/03，2025/07/24，2025/09/28，2025/10/31，2025/11/13，2026/1/14</t>
+          <t>2025/03/28，2025/05/03，2025/07/24，2025/09/28，2025/10/31，2025/11/13，2026/01/14</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/9，2026/1/9，2026/2/19，2026/5/10</t>
+          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2025/3/28</t>
+          <t>2025/03/28</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/05，2025/05/08，2025/05/15，2025/05/30，2025/06/13，2025/06/23，2025/07/10，2025/07/24，2025/08/04，2025/09/03，2025/09/21，2025/11/9，2025/11/26，2026/1/16，2026/1/29，2026/4/19</t>
+          <t>2025/03/28，2025/05/05，2025/05/08，2025/05/15，2025/05/30，2025/06/13，2025/06/23，2025/07/10，2025/07/24，2025/08/04，2025/09/03，2025/09/21，2025/11/09，2025/11/26，2026/01/16，2026/01/29，2026/04/19，2026/07/27</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/08/28，2025/09/18，2025/11/21，2025/12/4，2026/3/21，2026/6/27</t>
+          <t>2025/03/28，2025/04/04，2025/08/28，2025/09/18，2025/11/21，2025/12/04，2026/03/21，2026/06/27</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/03，2025/05/26，2025/11/9，2026/5/6，2026/6/10</t>
+          <t>2025/03/28，2025/05/03，2025/05/26，2025/11/09，2026/05/06，2026/06/10</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/7，2025/11/24，2025/12/5，2026/1/23，2026/3/9，2026/3/25，2026/6/20</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/09，2025/06/07，2025/07/31，2025/08/13，2025/08/21，2025/12/16，2026/1/19，2026/5/4</t>
+          <t>2025/03/28，2025/05/09，2025/06/07，2025/07/31，2025/08/13，2025/08/21，2025/12/16，2026/01/19，2026/05/04</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/2</t>
+          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/05/08，2025/05/20，2025/05/26，2025/06/05，2025/06/22，2025/07/10，2025/07/11，2025/07/22，2025/08/07，2025/09/17，2025/09/24，2025/10/23，2025/11/1，2025/11/13</t>
+          <t>2025/03/29，2025/05/08，2025/05/20，2025/05/26，2025/06/05，2025/06/22，2025/07/10，2025/07/11，2025/07/22，2025/08/07，2025/09/17，2025/09/24，2025/10/23，2025/11/01，2025/11/13，2026/07/16，2026/07/25</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/01，2025/04/12，2025/04/14，2025/04/17，2025/04/18，2025/04/20，2025/04/29，2025/05/08，2025/05/20，2025/05/25，2025/06/03，2025/06/08，2025/06/14，2025/06/20，2025/07/05，2025/07/08，2025/07/17，2025/07/28，2025/08/07，2025/08/19，2025/08/28，2025/09/03，2025/09/20，2025/10/03，2025/10/26，2025/12/8，2025/12/12，2026/1/28，2026/3/7，2026/3/28，2026/4/19，2026/5/15</t>
+          <t>2025/03/29，2025/04/01，2025/04/12，2025/04/14，2025/04/17，2025/04/18，2025/04/20，2025/04/29，2025/05/08，2025/05/20，2025/05/25，2025/06/03，2025/06/08，2025/06/14，2025/06/20，2025/07/05，2025/07/08，2025/07/17，2025/07/28，2025/08/07，2025/08/19，2025/08/28，2025/09/03，2025/09/20，2025/10/03，2025/10/26，2025/12/08，2025/12/12，2026/01/28，2026/03/07，2026/03/28，2026/04/19，2026/05/15，2026/07/27</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/05/29，2025/06/17，2025/07/24，2025/08/16，2025/09/21，2025/10/30，2026/2/9</t>
+          <t>2025/03/29，2025/05/29，2025/06/17，2025/07/24，2025/08/16，2025/09/21，2025/10/30，2026/02/09</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -9955,7 +9955,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/3，2025/11/9，2025/12/23，2026/4/8，2026/4/24，2026/5/21，2026/6/10</t>
+          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/7，2025/11/13，2025/12/2，2026/1/14，2026/1/24，2026/3/7，2026/3/15，2026/4/24，2026/6/6，2026/6/23</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/6/28</t>
+          <t>2025/03/29，2025/04/25，2025/05/03，2025/06/23，2025/09/28，2025/11/28，2025/12/26，2026/06/28</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/08/22，2025/09/21，2025/10/20，2025/12/2，2026/2/9，2026/6/3</t>
+          <t>2025/03/29，2025/08/22，2025/09/21，2025/10/20，2025/12/02，2026/02/09，2026/06/03</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/08/12，2025/10/20，2025/11/14，2025/12/2，2026/1/10，2026/2/9，2026/4/18，2026/6/20</t>
+          <t>2025/03/29，2025/08/12，2025/10/20，2025/11/14，2025/12/02，2026/01/10，2026/02/09，2026/04/18，2026/06/20</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/06/17，2025/09/28，2025/10/20，2025/10/31，2026/1/16，2026/6/14，2026/6/17</t>
+          <t>2025/03/30，2025/06/17，2025/09/28，2025/10/20，2025/10/31，2026/01/16，2026/06/14，2026/06/17</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/1/16，2026/3/25，2026/5/23</t>
+          <t>2025/03/30，2025/04/14，2025/05/26，2025/06/15，2025/07/09，2025/10/25，2025/11/24，2025/12/30，2026/01/16，2026/03/25，2026/05/23，2026/07/17</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/1/19</t>
+          <t>2025/03/30，2025/05/22，2025/06/29，2025/09/30，2025/10/23，2026/01/19</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/24，2025/05/15，2025/05/29，2025/09/21，2025/09/27，2025/10/24，2026/1/5，2026/2/9，2026/3/15，2026/5/1</t>
+          <t>2025/03/30，2025/04/24，2025/05/15，2025/05/29，2025/09/21，2025/09/27，2025/10/24，2026/01/05，2026/02/09，2026/03/15，2026/05/01</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/1/9，2026/3/7，2026/4/19，2026/5/23</t>
+          <t>2025/03/30，2025/05/10，2025/06/01，2025/06/10，2025/06/13，2025/07/21，2025/07/22，2025/08/03，2025/09/24，2025/10/05，2026/01/09，2026/03/07，2026/04/19，2026/05/23，2026/07/16</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/4/22</t>
+          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/1，2026/2/14，2026/4/9</t>
+          <t>2025/03/30，2025/04/04，2025/04/26，2025/05/06，2025/05/18，2025/06/10，2025/07/03，2025/07/10，2025/07/24，2025/08/16，2025/09/18，2025/10/03，2025/11/01，2026/02/14，2026/04/09，2026/07/09</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/1/1，2026/1/25，2026/3/8，2026/4/27，2026/6/13</t>
+          <t>2025/03/30，2025/04/15，2025/05/09，2025/06/13，2025/06/27，2025/07/11，2025/08/29，2025/09/12，2025/11/27，2026/01/01，2026/01/25，2026/03/08，2026/04/27，2026/06/13，2026/07/28</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2025/3/30</t>
+          <t>2025/03/30</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/2/7</t>
+          <t>2025/03/30，2025/04/19，2025/06/23，2025/07/08，2025/09/21，2025/10/23，2025/11/14，2025/12/17，2026/02/07</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/2/12，2026/4/16，2026/5/20，2026/6/20</t>
+          <t>2025/04/01，2025/04/11，2025/04/18，2025/04/29，2025/05/08，2025/07/22，2025/07/29，2025/08/04，2025/08/21，2025/09/06，2025/10/09，2025/12/12，2026/02/12，2026/04/16，2026/05/20，2026/06/20</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/05/15，2025/06/09，2025/09/03，2025/09/24，2026/1/5</t>
+          <t>2025/04/01，2025/05/15，2025/06/09，2025/09/03，2025/09/24，2026/01/05</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/06/19，2026/4/25，2026/5/1</t>
+          <t>2025/04/01，2025/06/19，2026/04/25，2026/05/01</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/2/7，2026/6/28</t>
+          <t>2025/04/01，2025/06/23，2025/07/08，2025/09/30，2025/10/23，2026/02/07，2026/06/28</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/1/21，2026/2/25，2026/2/27，2026/3/1，2026/3/8，2026/3/13，2026/3/25，2026/4/1，2026/5/1，2026/5/7，2026/5/8，2026/5/23，2026/6/13</t>
+          <t>2025/04/01，2025/04/28，2025/05/22，2025/06/08，2025/06/27，2025/07/08，2025/08/01，2025/09/03，2025/09/28，2025/10/16，2025/10/23，2025/10/31，2025/12/19，2025/12/31，2026/01/21，2026/02/25，2026/02/27，2026/03/01，2026/03/08，2026/03/13，2026/03/25，2026/04/01，2026/05/01，2026/05/07，2026/05/08，2026/05/23，2026/06/13</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/2，2026/4/8，2026/5/1，2026/6/10，2026/6/20</t>
+          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/05/10，2025/09/04，2025/09/10，2025/09/28，2025/11/26，2026/1/19，2026/5/10</t>
+          <t>2025/04/01，2025/05/10，2025/09/04，2025/09/10，2025/09/28，2025/11/26，2026/01/19，2026/05/10</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/2/8，2026/3/17，2026/5/5，2026/5/21，2026/6/25</t>
+          <t>2025/04/01，2025/04/24，2025/05/12，2025/05/26，2025/06/23，2025/06/27，2025/07/20，2025/08/30，2025/09/15，2025/09/22，2025/10/07，2025/10/28，2025/11/26，2025/12/28，2026/02/08，2026/03/17，2026/05/05，2026/05/21，2026/06/25，2026/07/16</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/1/2，2026/1/5，2026/2/2，2026/2/9，2026/2/19，2026/3/25，2026/5/10，2026/5/21</t>
+          <t>2025/04/01，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/11，2026/01/02，2026/01/05，2026/02/02，2026/02/09，2026/02/19，2026/03/25，2026/05/10，2026/05/21，2026/07/16</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/12，2025/05/26，2025/08/26，2025/08/16，2025/10/05，2026/5/4</t>
+          <t>2025/04/02，2025/05/12，2025/05/26，2025/08/26，2025/08/16，2025/10/05，2026/05/04</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/18，2025/05/26，2025/09/21，2025/10/07，2026/1/15</t>
+          <t>2025/04/02，2025/04/18，2025/05/26，2025/09/21，2025/10/07，2026/01/15</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/22，2025/08/22，2025/09/12，2026/4/20，2026/6/26</t>
+          <t>2025/04/02，2025/05/22，2025/08/22，2025/09/12，2026/04/20，2026/06/26，2026/07/19</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/27，2025/07/24，2026/1/1，2026/6/14</t>
+          <t>2025/04/02，2025/05/27，2025/07/24，2026/01/01，2026/06/14</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/04，2025/05/20，2025/06/23，2025/07/24，2025/09/12，2025/10/17，2025/12/9，2026/2/14，2026/3/25，2026/6/13</t>
+          <t>2025/04/02，2025/05/04，2025/05/20，2025/06/23，2025/07/24，2025/09/12，2025/10/17，2025/12/09，2026/02/14，2026/03/25，2026/06/13，2026/07/28</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/13，2025/05/29，2025/09/04，2025/09/21，2025/10/22，2026/1/1，2026/1/15，2026/5/5</t>
+          <t>2025/04/02，2025/05/13，2025/05/29，2025/09/04，2025/09/21，2025/10/22，2026/01/01，2026/01/15，2026/05/05</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/9，2025/12/6，2025/12/24，2026/4/13，2026/5/4</t>
+          <t>2025/04/02，2025/04/12，2025/05/23，2025/06/08，2025/07/29，2025/08/13，2025/08/28，2025/09/28，2025/09/29，2025/11/09，2025/12/06，2025/12/24，2026/04/13，2026/05/04，2026/07/27</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/13，2025/05/10，2025/05/26，2025/06/02，2025/06/05，2025/06/17，2025/08/04，2025/09/10，2025/09/30，2025/10/16，2025/11/17，2025/12/6，2025/12/31，2026/4/26</t>
+          <t>2025/04/02，2025/04/13，2025/05/10，2025/05/26，2025/06/02，2025/06/05，2025/06/17，2025/08/04，2025/09/10，2025/09/30，2025/10/16，2025/11/17，2025/12/06，2025/12/31，2026/04/26，2026/07/22</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/08，2025/05/04，2025/05/08，2025/07/31，2026/4/9</t>
+          <t>2025/04/02，2025/04/08，2025/05/04，2025/05/08，2025/07/31，2026/04/09</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/19，2025/05/09，2025/05/20，2025/06/26，2025/07/15，2025/09/30，2025/12/5，2026/5/20</t>
+          <t>2025/04/02，2025/04/19，2025/05/09，2025/05/20，2025/06/26，2025/07/15，2025/09/30，2025/12/05，2026/05/20</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/04/03，2025/04/08，2025/05/26，2025/07/18，2025/08/16，2025/09/30，2025/11/26，2026/1/23，2026/2/18，2026/3/12，2026/6/10</t>
+          <t>2025/04/02，2025/04/03，2025/04/08，2025/05/26，2025/07/18，2025/08/16，2025/09/30，2025/11/26，2026/01/23，2026/02/18，2026/03/12，2026/06/10</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/1/25，2026/2/14，2026/4/9，2026/6/20</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/06/20，2025/09/19，2025/10/12，2026/3/9，2026/3/13，2026/3/17，2026/5/1，2026/6/18</t>
+          <t>2025/04/03，2025/06/20，2025/09/19，2025/10/12，2026/03/09，2026/03/13，2026/03/17，2026/05/01，2026/06/18</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/05/03，2025/05/22，2025/09/10，2026/2/7</t>
+          <t>2025/04/03，2025/05/03，2025/05/22，2025/09/10，2026/02/07</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/05/17，2025/05/29，2025/06/16，2025/07/10，2025/08/24，2025/10/16，2025/11/26，2026/4/26</t>
+          <t>2025/04/03，2025/05/17，2025/05/29，2025/06/16，2025/07/10，2025/08/24，2025/10/16，2025/11/26，2026/04/26</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/3，2025/12/12，2025/12/26，2026/4/8</t>
+          <t>2025/04/03，2025/04/14，2025/04/24，2025/06/01，2025/07/06，2025/09/21，2025/11/03，2025/12/12，2025/12/26，2026/04/08，2026/07/20</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/6，2026/1/9，2026/1/29，2026/3/25，2026/4/24，2026/5/23，2026/6/15</t>
+          <t>2025/04/03，2025/04/15，2025/05/22，2025/05/29，2025/06/02，2025/06/07，2025/06/12，2025/06/21，2025/06/23，2025/07/08，2025/07/13，2025/07/21，2025/08/01，2025/08/03，2025/09/02，2025/09/19，2025/10/10，2025/11/12，2025/11/26，2025/12/06，2026/01/09，2026/01/29，2026/03/25，2026/04/24，2026/05/23，2026/06/15，2026/07/09，2026/07/22</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/24，2025/09/12，2026/1/10，2026/6/3</t>
+          <t>2025/04/03，2025/04/24，2025/09/12，2026/01/10，2026/06/03</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/05/12，2025/05/18，2025/06/20，2025/07/05，2025/07/14，2025/12/23，2026/1/30，2026/4/9</t>
+          <t>2025/04/04，2025/05/12，2025/05/18，2025/06/20，2025/07/05，2025/07/14，2025/12/23，2026/01/30，2026/04/09</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/06/02，2025/06/29，2025/07/24，2025/07/26，2025/08/21，2025/11/9，2025/12/16</t>
+          <t>2025/04/04，2025/06/02，2025/06/29，2025/07/24，2025/07/26，2025/08/21，2025/11/09，2025/12/16</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2025/04/04，2026/1/29</t>
+          <t>2025/04/04，2026/01/29</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/06/26，2026/3/13</t>
+          <t>2025/04/04，2025/06/26，2026/03/13</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/04/11，2025/05/18，2025/09/12，2025/10/12，2026/1/16</t>
+          <t>2025/04/04，2025/04/11，2025/05/18，2025/09/12，2025/10/12，2026/01/16</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/04/18，2025/06/06，2025/07/07，2025/08/04，2025/08/12，2025/09/17，2026/4/9</t>
+          <t>2025/04/04，2025/04/18，2025/06/06，2025/07/07，2025/08/04，2025/08/12，2025/09/17，2026/04/09</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/20，2025/12/5，2026/1/22</t>
+          <t>2025/04/04，2025/07/20，2025/12/05，2026/01/22，2026/07/28</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/3，2025/11/28</t>
+          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2025/4/4，2026/6/15</t>
+          <t>2025/04/04，2026/06/15</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2025/4/4，2026/4/20</t>
+          <t>2025/04/04，2026/04/20</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -12315,7 +12315,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/2/14，2026/3/5，2026/4/2，2026/5/20</t>
+          <t>2025/04/05，2025/04/11，2025/04/19，2025/05/04，2025/05/09，2025/05/23，2025/05/30，2025/06/27，2025/08/16，2025/09/30，2026/02/14，2026/03/05，2026/04/02，2026/05/20</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/9，2025/12/16，2026/2/27，2026/6/13</t>
+          <t>2025/04/05，2025/04/19，2025/05/20，2025/07/11，2025/09/12，2025/12/09，2025/12/16，2026/02/27，2026/06/13</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/10，2025/06/20，2025/12/23，2026/4/9</t>
+          <t>2025/04/06，2025/04/10，2025/06/20，2025/12/23，2026/04/09</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/17，2025/05/04，2025/05/24，2025/05/30，2025/09/19，2025/10/22，2025/11/13，2026/6/28</t>
+          <t>2025/04/06，2025/04/17，2025/05/04，2025/05/24，2025/05/30，2025/09/19，2025/10/22，2025/11/13，2026/06/28</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/25，2025/07/25，2025/08/28，2025/09/12，2026/2/20</t>
+          <t>2025/04/06，2025/04/25，2025/07/25，2025/08/28，2025/09/12，2026/02/20</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/19，2025/05/03，2025/08/01，2025/10/31，2025/12/15，2026/2/22，2026/2/23，2026/4/17</t>
+          <t>2025/04/06，2025/04/19，2025/05/03，2025/08/01，2025/10/31，2025/12/15，2026/02/22，2026/02/23，2026/04/17</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/05/23，2025/06/10，2025/10/03，2025/11/1</t>
+          <t>2025/04/06，2025/05/23，2025/06/10，2025/10/03，2025/11/01</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/3/9</t>
+          <t>2025/04/07，2025/05/09，2025/06/19，2025/07/22，2026/03/09</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/19，2025/10/11，2025/12/6</t>
+          <t>2025/04/07，2025/05/19，2025/10/11，2025/12/06</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/1/29，2026/3/20，2026/4/22</t>
+          <t>2025/04/07，2025/04/24，2025/05/03，2025/05/23，2025/06/07，2025/06/12，2025/06/23，2025/06/29，2025/07/15，2025/07/25，2025/09/24，2025/10/18，2025/11/12，2025/11/24，2025/12/23，2026/01/29，2026/03/20，2026/04/22，2026/07/09</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/1/5，2026/3/25，2026/3/25</t>
+          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/1/3，2026/1/22，2026/2/14，2026/5/20</t>
+          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/05/08，2025/05/20，2025/05/30，2025/06/16，2025/08/29，2025/09/12，2025/10/09，2025/10/16，2025/11/18，2026/2/4，2026/2/14，2026/4/15，2026/6/13</t>
+          <t>2025/04/07，2025/04/17，2025/05/08，2025/05/20，2025/05/30，2025/06/16，2025/08/29，2025/09/12，2025/10/09，2025/10/16，2025/11/18，2026/02/04，2026/02/14，2026/04/15，2026/06/13，2026/07/07，2026/07/28</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/3，2025/11/9，2025/11/26，2025/12/9，2026/1/23，2026/3/13，2026/3/25，2026/4/8，2026/5/23，2026/6/20</t>
+          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/9，2026/1/24，2026/3/31，2026/4/2，2026/6/15</t>
+          <t>2025/04/08，2025/04/18，2025/04/19，2025/04/26，2025/05/04，2025/05/08，2025/05/19，2025/05/29，2025/06/07，2025/06/23，2025/07/05，2025/07/13，2025/08/21，2025/09/21，2025/10/25，2025/10/26，2025/11/19，2025/12/09，2026/01/24，2026/03/31，2026/04/02，2026/06/15，2026/07/27</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2025/4/8</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/05/12，2025/08/22，2025/10/01，2025/10/17，2026/2/23，2026/3/6，2026/4/22，2026/6/10</t>
+          <t>2025/04/08，2025/05/12，2025/08/22，2025/10/01，2025/10/17，2026/02/23，2026/03/06，2026/04/22，2026/06/10</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/9，2025/12/5，2025/12/19，2025/12/26，2026/1/10，2026/1/19，2026/2/10，2026/3/24，2026/4/18，2026/6/6</t>
+          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2025/04/10，2025/04/24，2025/05/13，2025/06/13，2025/09/03，2025/09/19，2025/10/13，2025/11/21，2026/3/4，2026/3/24</t>
+          <t>2025/04/10，2025/04/24，2025/05/13，2025/06/13，2025/09/03，2025/09/19，2025/10/13，2025/11/21，2026/03/04，2026/03/24</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2025/04/10，2025/05/19，2025/06/27，2025/08/21，2025/08/29，2025/09/17，2025/10/17，2025/10/30，2026/3/1，2026/3/29</t>
+          <t>2025/04/10，2025/05/19，2025/06/27，2025/08/21，2025/08/29，2025/09/17，2025/10/17，2025/10/30，2026/03/01，2026/03/29</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/9，2025/11/13，2025/12/4，2025/12/13，2026/3/4，2026/5/7，2026/6/20</t>
+          <t>2025/04/11，2025/06/29，2025/08/01，2025/09/04，2025/09/21，2025/10/17，2025/11/09，2025/11/13，2025/12/04，2025/12/13，2026/03/04，2026/05/07，2026/06/20</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2025/4/11</t>
+          <t>2025/04/11</t>
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/18，2025/06/09，2025/07/07，2025/08/26，2025/09/03，2025/09/13，2025/10/17，2025/10/30，2025/11/21，2025/12/17，2026/4/19</t>
+          <t>2025/04/11，2025/05/18，2025/06/09，2025/07/07，2025/08/26，2025/09/03，2025/09/13，2025/10/17，2025/10/30，2025/11/21，2025/12/17，2026/04/19</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/9，2025/12/8，2026/1/5，2026/2/14，2026/5/23，2026/6/20</t>
+          <t>2025/04/11，2025/04/28，2025/05/26，2025/06/17，2025/07/15，2025/07/26，2025/08/13，2025/09/03，2025/09/12，2025/10/07，2025/11/09，2025/12/08，2026/01/05，2026/02/14，2026/05/23，2026/06/20，2026/07/18</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/12，2025/09/11，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/1/29，2026/2/10，2026/3/9，2026/3/24，2026/4/19，2026/5/21，2026/6/15</t>
+          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/12，2025/09/11，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2025/4/11</t>
+          <t>2025/04/11</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2025/4/11</t>
+          <t>2025/04/11</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/04/18，2025/04/25，2025/04/29，2025/05/30，2025/06/09，2025/06/13，2025/06/26，2025/07/05，2025/07/14，2025/08/21，2025/09/10，2025/10/09，2025/11/21，2026/1/22</t>
+          <t>2025/04/11，2025/04/18，2025/04/25，2025/04/29，2025/05/30，2025/06/09，2025/06/13，2025/06/26，2025/07/05，2025/07/14，2025/08/21，2025/09/10，2025/10/09，2025/11/21，2026/01/22</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/18，2025/09/08，2025/12/5，2026/1/28，2026/4/19</t>
+          <t>2025/04/11，2025/05/18，2025/09/08，2025/12/05，2026/01/28，2026/04/19</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/08/04，2025/09/12，2025/09/12，2026/4/9</t>
+          <t>2025/04/11，2025/08/04，2025/09/12，2025/09/12，2026/04/09</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/06/02，2025/06/12，2025/09/27，2025/11/9，2025/12/19，2026/1/1，2026/2/17</t>
+          <t>2025/04/11，2025/06/02，2025/06/12，2025/09/27，2025/11/09，2025/12/19，2026/01/01，2026/02/17，2026/07/09，2026/07/27</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2025/04/12，2025/07/14，2025/09/24，2025/09/28，2025/11/9，2026/4/24</t>
+          <t>2025/04/12，2025/07/14，2025/09/24，2025/09/28，2025/11/09，2026/04/24</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2025/4/12</t>
+          <t>2025/04/12</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/1/9，2026/2/8，2026/3/1，2026/3/9，2026/3/24，2026/4/17，2026/5/1，2026/5/21，2026/6/10，2026/6/25</t>
+          <t>2025/04/13，2025/05/26，2025/06/07，2025/06/21，2025/07/05，2025/08/21，2025/09/15，2025/10/23，2025/11/24，2025/12/23，2026/01/09，2026/02/08，2026/03/01，2026/03/09，2026/03/24，2026/04/17，2026/05/01，2026/05/21，2026/06/10，2026/06/25，2026/07/27</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/21，2025/04/22，2025/04/25，2025/04/26，2025/04/29，2025/05/08，2025/05/12，2025/05/22，2025/05/30，2025/06/06，2025/06/08，2025/06/28，2025/07/13，2025/08/12，2025/08/24，2025/09/07，2025/09/30，2025/10/05，2025/11/21，2025/12/17，2026/1/14，2026/1/23，2026/2/12，2026/3/31，2026/6/18</t>
+          <t>2025/04/13，2025/04/21，2025/04/22，2025/04/25，2025/04/26，2025/04/29，2025/05/08，2025/05/12，2025/05/22，2025/05/30，2025/06/06，2025/06/08，2025/06/28，2025/07/13，2025/08/12，2025/08/24，2025/09/07，2025/09/30，2025/10/05，2025/11/21，2025/12/17，2026/01/14，2026/01/23，2026/02/12，2026/03/31，2026/06/18，2026/07/17</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -14014,7 +14014,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/15，2025/04/27，2025/05/22，2025/05/29，2025/06/03，2025/06/13，2025/06/28，2025/08/22，2025/09/19，2025/10/12，2025/12/5，2025/12/9，2026/1/15，2026/1/24，2026/3/19，2026/5/1，2026/5/21，2026/6/15</t>
+          <t>2025/04/13，2025/04/15，2025/04/27，2025/05/22，2025/05/29，2025/06/03，2025/06/13，2025/06/28，2025/08/22，2025/09/19，2025/10/12，2025/12/05，2025/12/09，2026/01/15，2026/01/24，2026/03/19，2026/05/01，2026/05/21，2026/06/15，2026/07/16</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -14062,7 +14062,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/04/18，2025/08/28，2026/1/16，2026/5/1</t>
+          <t>2025/04/13，2025/04/18，2025/08/28，2026/01/16，2026/05/01</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/1/22，2026/2/23</t>
+          <t>2025/04/13，2025/07/13，2025/07/18，2025/08/02，2025/09/04，2025/09/12，2025/10/17，2025/11/28，2026/01/22，2026/02/23</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2025/04/13，2025/05/23，2025/06/06，2025/08/28，2025/09/05，2025/12/6，2026/3/17</t>
+          <t>2025/04/13，2025/05/23，2025/06/06，2025/08/28，2025/09/05，2025/12/06，2026/03/17</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/6/20</t>
+          <t>2025/04/14，2025/05/24，2025/06/15，2025/06/19，2025/07/21，2025/08/22，2025/09/20，2025/10/09，2025/10/28，2025/12/22，2026/06/20</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/1/1，2026/1/9，2026/2/20，2026/4/18，2026/5/10</t>
+          <t>2025/04/15，2025/05/13，2025/07/14，2025/09/18，2026/01/01，2026/01/09，2026/02/20，2026/04/18，2026/05/10，2026/07/16</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/1/16，2026/3/25，2026/4/24，2026/5/23</t>
+          <t>2025/04/15，2025/04/18，2025/05/12，2025/06/17，2025/09/03，2025/10/07，2025/11/24，2026/01/16，2026/03/25，2026/04/24，2026/05/23，2026/07/17</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/3，2025/12/23，2026/4/9</t>
+          <t>2025/04/15，2025/04/25，2025/05/30，2025/06/17，2025/09/26，2025/10/03，2025/11/03，2025/12/23，2026/04/09</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -14499,7 +14499,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2025/04/15，2025/04/18，2025/04/20，2025/05/18，2025/05/20，2025/05/25，2025/06/28，2025/06/30，2025/08/24，2025/09/26，2026/1/9，2026/4/17</t>
+          <t>2025/04/15，2025/04/18，2025/04/20，2025/05/18，2025/05/20，2025/05/25，2025/06/28，2025/06/30，2025/08/24，2025/09/26，2026/01/09，2026/04/17</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/26，2025/06/23，2025/09/29，2026/4/19</t>
+          <t>2025/04/17，2025/05/26，2025/06/23，2025/09/29，2026/04/19</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/21，2025/05/08，2025/06/10，2025/06/28，2025/07/08，2025/08/22，2025/09/11，2025/10/25，2026/3/13，2026/4/18</t>
+          <t>2025/04/17，2025/04/21，2025/05/08，2025/06/10，2025/06/28，2025/07/08，2025/08/22，2025/09/11，2025/10/25，2026/03/13，2026/04/18，2026/07/22</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/18，2025/07/03，2025/10/17，2025/10/30，2026/1/9</t>
+          <t>2025/04/17，2025/04/18，2025/07/03，2025/10/17，2025/10/30，2026/01/09</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/06/01，2025/08/18，2026/3/6，2026/3/17</t>
+          <t>2025/04/17，2025/06/01，2025/08/18，2026/03/06，2026/03/17</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/01，2025/05/26，2025/07/03，2025/07/27，2025/09/18，2025/10/17，2025/11/21，2026/1/12，2026/1/24，2026/2/19，2026/2/23，2026/3/24，2026/5/4</t>
+          <t>2025/04/17，2025/05/01，2025/05/26，2025/07/03，2025/07/27，2025/09/18，2025/10/17，2025/11/21，2026/01/12，2026/01/24，2026/02/19，2026/02/23，2026/03/24，2026/05/04，2026/07/07</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -14758,7 +14758,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/2/18，2026/5/20，2026/7/5</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/05/31，2025/06/03，2025/06/14，2025/09/10，2026/3/28</t>
+          <t>2025/04/17，2025/05/31，2025/06/03，2025/06/14，2025/09/10，2026/03/28</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2025/4/18</t>
+          <t>2025/04/18</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/06/05，2025/08/22，2025/09/05，2025/10/10，2025/11/3</t>
+          <t>2025/04/18，2025/06/05，2025/08/22，2025/09/05，2025/10/10，2025/11/03</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/10/01，2026/1/23</t>
+          <t>2025/04/18，2025/10/01，2026/01/23</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2025/4/18</t>
+          <t>2025/04/18</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2025/4/18</t>
+          <t>2025/04/18</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/05/29，2025/06/23，2025/09/21，2025/10/07，2026/1/10，2026/4/29</t>
+          <t>2025/04/18，2025/05/29，2025/06/23，2025/09/21，2025/10/07，2026/01/10，2026/04/29</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/05/18，2025/06/19，2025/07/15，2025/08/01，2025/09/17，2025/10/28，2025/11/13，2025/11/14，2026/2/10，2026/2/27</t>
+          <t>2025/04/18，2025/05/18，2025/06/19，2025/07/15，2025/08/01，2025/09/17，2025/10/28，2025/11/13，2025/11/14，2026/02/10，2026/02/27</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/1/10，2026/3/22，2026/4/24，2026/5/25</t>
+          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/04/25，2025/05/22，2025/07/03，2025/07/11，2025/07/26，2025/09/08，2025/10/03，2025/12/2，2026/1/25，2026/6/6</t>
+          <t>2025/04/19，2025/04/25，2025/05/22，2025/07/03，2025/07/11，2025/07/26，2025/09/08，2025/10/03，2025/12/02，2026/01/25，2026/06/06</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/2，2026/1/26，2026/6/28</t>
+          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/02，2026/01/26，2026/06/28</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/9，2025/11/26，2025/12/5，2025/12/6，2026/1/1，2026/1/29，2026/3/1，2026/4/9，2026/5/20</t>
+          <t>2025/04/20，2025/04/27，2025/05/05，2025/05/09，2025/05/18，2025/06/07，2025/06/13，2025/06/21，2025/07/05，2025/07/15，2025/07/25，2025/08/08，2025/08/26，2025/08/28，2025/09/14，2025/09/30，2025/10/03，2025/10/24，2025/10/31，2025/11/09，2025/11/26，2025/12/05，2025/12/06，2026/01/01，2026/01/29，2026/03/01，2026/04/09，2026/05/20，2026/07/27</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2025/04/20，2025/05/15，2025/06/23，2025/09/21</t>
+          <t>2025/04/20，2025/05/15，2025/06/23，2025/09/21，2026/07/27</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2025/04/20，2026/2/2</t>
+          <t>2025/04/20，2026/02/02</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/09/15，2025/10/11，2026/1/5，2026/6/3</t>
+          <t>2025/04/21，2025/09/15，2025/10/11，2026/01/05，2026/06/03，2026/07/26</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/2，2025/12/17，2026/5/6</t>
+          <t>2025/04/21，2025/05/23，2025/06/29，2025/07/26，2025/09/28，2025/12/02，2025/12/17，2026/05/06</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2025/04/21，2025/05/19，2025/07/25，2025/08/07，2025/09/15，2025/09/29，2026/1/5，2026/2/14，2026/4/9，2026/6/20</t>
+          <t>2025/04/21，2025/05/19，2025/07/25，2025/08/07，2025/09/15，2025/09/29，2026/01/05，2026/02/14，2026/04/09，2026/06/20</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2025/04/22，2025/04/29，2025/05/03，2025/05/03，2025/06/03，2025/09/02，2025/10/10，2025/10/20，2025/10/31，2026/2/7，2026/3/13</t>
+          <t>2025/04/22，2025/04/29，2025/05/03，2025/05/03，2025/06/03，2025/09/02，2025/10/10，2025/10/20，2025/10/31，2026/02/07，2026/03/13</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/11/9</t>
+          <t>2025/04/24，2025/11/09</t>
         </is>
       </c>
       <c r="F379" t="inlineStr"/>
@@ -15747,7 +15747,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/05/12，2025/12/11，2026/1/24，2026/3/14</t>
+          <t>2025/04/24，2025/05/12，2025/12/11，2026/01/24，2026/03/14</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
@@ -15787,7 +15787,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2025/4/24</t>
+          <t>2025/04/24</t>
         </is>
       </c>
       <c r="F381" t="inlineStr"/>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/09/22，2026/3/29，2026/6/10</t>
+          <t>2025/04/24，2025/09/22，2026/03/29，2026/06/10</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/05/25，2025/12/2，2025/12/31，2026/4/24，2026/6/3</t>
+          <t>2025/04/24，2025/05/25，2025/12/02，2025/12/31，2026/04/24，2026/06/03</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2025/04/24，2025/11/9</t>
+          <t>2025/04/24，2025/11/09</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2025/4/24</t>
+          <t>2025/04/24</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -15975,7 +15975,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2025/4/25</t>
+          <t>2025/04/25</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/09/08，2025/09/15，2025/12/30，2026/3/31，2026/4/24，2026/6/6，2026/6/14</t>
+          <t>2025/04/25，2025/09/08，2025/09/15，2025/12/30，2026/03/31，2026/04/24，2026/06/06，2026/06/14</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2025/4/25</t>
+          <t>2025/04/25，2026/07/22</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/23，2025/12/5，2026/2/14，2026/4/9，2026/4/24</t>
+          <t>2025/04/25，2025/06/23，2025/12/05，2026/02/14，2026/04/09，2026/04/24</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2025/4/25</t>
+          <t>2025/04/25</t>
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2025/4/25</t>
+          <t>2025/04/25</t>
         </is>
       </c>
       <c r="F394" t="inlineStr"/>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/3，2025/12/30，2026/1/9，2026/4/1，2026/5/23</t>
+          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -16359,7 +16359,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/05/18，2026/4/20</t>
+          <t>2025/04/25，2025/05/18，2026/04/20</t>
         </is>
       </c>
       <c r="F396" t="inlineStr"/>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/07/23，2025/09/19</t>
+          <t>2025/04/25，2025/07/23，2025/09/19，2026/07/22</t>
         </is>
       </c>
       <c r="F397" t="inlineStr"/>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
@@ -16435,7 +16435,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/23，2025/10/09，2026/1/22，2026/3/9</t>
+          <t>2025/04/25，2025/06/23，2025/10/09，2026/01/22，2026/03/09</t>
         </is>
       </c>
       <c r="F398" t="inlineStr"/>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2025/04/26，2025/05/02，2025/07/23，2025/09/19，2025/11/21，2026/2/2</t>
+          <t>2025/04/26，2025/05/02，2025/07/23，2025/09/19，2025/11/21，2026/02/02</t>
         </is>
       </c>
       <c r="F399" t="inlineStr"/>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/1/9，2026/4/9</t>
+          <t>2025/04/27，2025/06/02，2025/06/09，2025/07/09，2025/07/14，2025/08/26，2025/11/21，2025/12/17，2026/01/09，2026/04/09</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -16555,7 +16555,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/04，2025/05/26，2025/06/08，2025/08/28，2025/10/18，2025/11/18，2025/12/24，2026/1/29，2026/2/27，2026/4/9，2026/4/20</t>
+          <t>2025/04/27，2025/05/04，2025/05/26，2025/06/08，2025/08/28，2025/10/18，2025/11/18，2025/12/24，2026/01/29，2026/02/27，2026/04/09，2026/04/20</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/29，2025/06/17，2025/07/11，2025/08/03，2025/09/22，2026/4/9，2026/6/23</t>
+          <t>2025/04/27，2025/05/29，2025/06/17，2025/07/11，2025/08/03，2025/09/22，2026/04/09，2026/06/23</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/07/13，2025/09/12，2025/10/09，2026/1/22，2026/2/2</t>
+          <t>2025/04/27，2025/07/13，2025/09/12，2025/10/09，2026/01/22，2026/02/02</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2025/04/27，2025/05/20，2025/06/08，2025/08/18，2025/09/11，2025/11/03</t>
+          <t>2025/04/27，2025/05/20，2025/06/08，2025/08/18，2025/09/11，2025/11/03，2026/07/09</t>
         </is>
       </c>
       <c r="F405" t="inlineStr"/>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/05/06，2025/07/27，2025/09/17，2025/10/16，2025/11/9，2026/2/12</t>
+          <t>2025/04/28，2025/05/06，2025/07/27，2025/09/17，2025/10/16，2025/11/09，2026/02/12，2026/07/10，2026/07/15</t>
         </is>
       </c>
       <c r="F406" t="inlineStr"/>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/11/18，2026/2/14，2026/4/9，2026/5/16，2026/6/14</t>
+          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/1/19</t>
+          <t>2025/04/28，2025/05/12，2025/05/23，2025/07/20，2025/10/18，2026/01/19，2026/07/27</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2025/4/28</t>
+          <t>2025/04/28</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2025/04/29，2025/05/03，2026/4/20</t>
+          <t>2025/04/29，2025/05/03，2026/04/20</t>
         </is>
       </c>
       <c r="F411" t="inlineStr"/>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2025/05/01，2025/08/12，2025/08/26，2025/11/24，2026/6/20</t>
+          <t>2025/05/01，2025/08/12，2025/08/26，2025/11/24，2026/06/20</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2025/05/02，2025/05/15，2025/06/14，2026/2/19，2026/4/26</t>
+          <t>2025/05/02，2025/05/15，2025/06/14，2026/02/19，2026/04/26</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2025/5/3</t>
+          <t>2025/05/03</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/9</t>
+          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/07/18，2025/08/02，2025/10/16，2026/5/1</t>
+          <t>2025/05/03，2025/07/18，2025/08/02，2025/10/16，2026/05/01</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/06/13，2025/09/08，2026/4/25</t>
+          <t>2025/05/03，2025/06/13，2025/09/08，2026/04/25</t>
         </is>
       </c>
       <c r="F418" t="inlineStr"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/07/13，2025/10/23，2026/6/23</t>
+          <t>2025/05/03，2025/07/13，2025/10/23，2026/06/23</t>
         </is>
       </c>
       <c r="F419" t="inlineStr"/>
@@ -17299,7 +17299,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2025/5/3</t>
+          <t>2025/05/03</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>2025/5/3</t>
+          <t>2025/05/03</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/10/31，2026/4/14</t>
+          <t>2025/05/03，2025/10/31，2026/04/14</t>
         </is>
       </c>
       <c r="F422" t="inlineStr"/>
@@ -17499,7 +17499,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/4/20，2026/5/23</t>
+          <t>2025/05/08，2025/06/16，2025/06/21，2025/07/05，2025/07/14，2025/09/12，2025/11/26，2026/04/20，2026/05/23</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>2025/5/9</t>
+          <t>2025/05/09</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
@@ -17655,7 +17655,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>2025/05/09，2026/1/19</t>
+          <t>2025/05/09，2026/01/19</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/20，2025/06/24，2025/07/07，2025/09/30，2026/5/20，2026/6/12</t>
+          <t>2025/05/10，2025/06/20，2025/06/24，2025/07/07，2025/09/30，2026/05/20，2026/06/12</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/05/13，2025/06/22，2025/07/05，2025/12/4</t>
+          <t>2025/05/10，2025/05/13，2025/06/22，2025/07/05，2025/12/04</t>
         </is>
       </c>
       <c r="F431" t="inlineStr"/>
@@ -17771,7 +17771,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/4/29</t>
+          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>2025/05/12，2025/06/27，2025/07/11，2025/07/11，2025/07/13，2025/08/08，2025/09/06，2026/4/14</t>
+          <t>2025/05/12，2025/06/27，2025/07/11，2025/07/11，2025/07/13，2025/08/08，2025/09/06，2026/04/14</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -17851,7 +17851,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2025/05/12，2025/05/31，2025/06/05，2025/06/15，2025/06/21，2025/06/27，2025/07/23，2025/08/24，2025/09/22，2025/12/19，2026/3/4，2026/6/3</t>
+          <t>2025/05/12，2025/05/31，2025/06/05，2025/06/15，2025/06/21，2025/06/27，2025/07/23，2025/08/24，2025/09/22，2025/12/19，2026/03/04，2026/06/03，2026/07/26</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>2025/05/12，2025/05/22，2025/05/25，2025/07/20，2025/09/12，2026/1/15，2026/1/24，2026/1/30，2026/4/8，2026/5/4，2026/5/23</t>
+          <t>2025/05/12，2025/05/22，2025/05/25，2025/07/20，2025/09/12，2026/01/15，2026/01/24，2026/01/30，2026/04/08，2026/05/04，2026/05/23</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -17971,7 +17971,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>2025/05/15，2025/10/31，2026/4/9</t>
+          <t>2025/05/15，2025/10/31，2026/04/09</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -18011,7 +18011,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2025/05/15，2025/09/03，2025/09/13，2026/4/20</t>
+          <t>2025/05/15，2025/09/03，2025/09/13，2026/04/20</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>2025/05/15，2025/06/13，2025/06/23，2025/07/18，2025/08/02，2025/09/04，2025/09/15，2025/10/03，2025/10/28，2025/11/9，2025/11/14，2025/12/5，2026/2/2，2026/5/4</t>
+          <t>2025/05/15，2025/06/13，2025/06/23，2025/07/18，2025/08/02，2025/09/04，2025/09/15，2025/10/03，2025/10/28，2025/11/09，2025/11/14，2025/12/05，2026/02/02，2026/05/04</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/1/1，2026/2/10，2026/2/22，2026/3/12，2026/4/5，2026/5/3，2026/5/24，2026/7/3</t>
+          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/27，2025/07/10，2026/3/9，2026/4/9，2026/6/10</t>
+          <t>2025/05/18，2025/06/27，2025/07/10，2026/03/09，2026/04/09，2026/06/10</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -18211,7 +18211,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>2025/5/18</t>
+          <t>2025/05/18</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/09/03，2026/3/4</t>
+          <t>2025/05/18，2025/09/03，2026/03/04</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -18327,7 +18327,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/11/28，2026/4/1</t>
+          <t>2025/05/18，2025/11/28，2026/04/01</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -18367,7 +18367,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/1/2，2026/3/17，2026/4/29，2026/5/10</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2025/05/18，2026/2/25</t>
+          <t>2025/05/18，2026/02/25</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/5/23</t>
+          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2025/5/19</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/07/13，2025/10/30，2025/10/31，2025/12/24，2026/1/9，2026/4/9，2026/5/7</t>
+          <t>2025/05/19，2025/07/13，2025/10/30，2025/10/31，2025/12/24，2026/01/09，2026/04/09，2026/05/07</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -18607,7 +18607,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/31，2025/06/07，2025/06/10，2025/08/02，2025/10/07，2025/12/6，2026/3/22，2026/5/1</t>
+          <t>2025/05/22，2025/05/31，2025/06/07，2025/06/10，2025/08/02，2025/10/07，2025/12/06，2026/03/22，2026/05/01</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/06/17，2025/06/23，2025/07/06，2025/07/15，2025/09/10，2025/10/18，2025/11/13，2026/5/4</t>
+          <t>2025/05/22，2025/06/17，2025/06/23，2025/07/06，2025/07/15，2025/09/10，2025/10/18，2025/11/13，2026/05/04，2026/07/09</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/12，2025/09/02，2025/12/5，2026/4/9，2026/5/10</t>
+          <t>2025/05/22，2025/09/12，2025/09/02，2025/12/05，2026/04/09，2026/05/10</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -18771,7 +18771,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/07/21，2026/4/14，2026/6/19</t>
+          <t>2025/05/22，2025/07/21，2026/04/14，2026/06/19</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>2025/5/22</t>
+          <t>2025/05/22</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/1/5，2026/2/2，2026/3/17，2026/5/10，2026/6/14，2026/6/15</t>
+          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -18895,7 +18895,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/09/12，2025/10/03，2025/10/11，2026/1/15，2026/4/29，2026/6/18</t>
+          <t>2025/05/22，2025/09/12，2025/10/03，2025/10/11，2026/01/15，2026/04/29，2026/06/18</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/06/17，2025/07/21，2025/08/16，2025/10/16，2025/12/2，2026/4/22，2026/6/23，2026/7/5</t>
+          <t>2025/05/22，2025/06/17，2025/07/21，2025/08/16，2025/10/16，2025/12/02，2026/04/22，2026/06/23，2026/07/05</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/05/29，2025/09/17，2025/09/02，2025/09/26，2025/10/09，2025/10/24，2026/4/29，2026/5/23</t>
+          <t>2025/05/23，2025/05/29，2025/09/17，2025/09/02，2025/09/26，2025/10/09，2025/10/24，2026/04/29，2026/05/23，2026/07/07</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -18990,7 +18990,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2025/5/23</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -19055,7 +19055,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/07/10，2026/1/19</t>
+          <t>2025/05/23，2025/07/10，2026/01/19</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>2025/05/23，2025/06/26，2025/07/21，2025/08/12，2025/09/10，2025/09/19，2025/11/1，2025/12/9，2025/12/13，2026/2/14，2026/4/24，2026/6/16</t>
+          <t>2025/05/23，2025/06/26，2025/07/21，2025/08/12，2025/09/10，2025/09/19，2025/11/01，2025/12/09，2025/12/13，2026/02/14，2026/04/24，2026/06/16</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/1/28，2026/4/8</t>
+          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2025/5/25</t>
+          <t>2025/05/25</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/7，2025/12/7，2025/12/23，2026/1/9，2026/1/24，2026/2/9，2026/2/25，2026/3/13，2026/3/21，2026/4/18，2026/5/4，2026/5/23，2026/6/14，2026/6/19</t>
+          <t>2025/05/27，2025/05/29，2025/05/30，2025/05/31，2025/06/02，2025/06/03，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/11，2025/07/22，2025/08/21，2025/09/10，2025/09/26，2025/10/03，2025/10/11，2025/10/26，2025/11/07，2025/12/07，2025/12/23，2026/01/09，2026/01/24，2026/02/09，2026/02/25，2026/03/13，2026/03/21，2026/04/18，2026/05/04，2026/05/23，2026/06/14，2026/06/19，2026/07/16</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>2025/5/30</t>
+          <t>2025/05/30</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/07/13，2025/10/31，2026/3/5</t>
+          <t>2025/05/30，2025/07/13，2025/10/31，2026/03/05</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/9，2026/1/1，2026/4/20</t>
+          <t>2025/05/30，2025/09/03，2025/09/11，2025/09/29，2025/11/09，2026/01/01，2026/04/20</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/08/13，2025/08/26，2025/08/26，2025/09/20，2025/09/26，2025/11/21，2026/4/9</t>
+          <t>2025/05/30，2025/08/13，2025/08/26，2025/08/26，2025/09/20，2025/09/26，2025/11/21，2026/04/09</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/1/10，2026/1/22，2026/3/25，2026/6/28</t>
+          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>2025/5/31</t>
+          <t>2025/05/31</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>2025/05/31，2025/12/9</t>
+          <t>2025/05/31，2025/12/09</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>2025/6/1</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>2025/06/01，2025/11/9，2025/11/28，2026/2/17</t>
+          <t>2025/06/01，2025/11/09，2025/11/28，2026/02/17</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>2025/06/01，2025/09/04，2026/3/1</t>
+          <t>2025/06/01，2025/09/04，2026/03/01</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -20039,7 +20039,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>2025/06/01，2025/09/03，2025/11/9</t>
+          <t>2025/06/01，2025/09/03，2025/11/09</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2025/6/1</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2025/6/1</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2025/6/1</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2025/6/1</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -20223,7 +20223,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>2025/6/1，2026/4/1</t>
+          <t>2025/06/01，2026/04/01</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2025/6/1</t>
+          <t>2025/06/01</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2025/06/01，2026/1/23，2026/2/2，2026/2/23，2026/3/5，2026/3/17，2026/4/24，2026/5/16</t>
+          <t>2025/06/01，2026/01/23，2026/02/02，2026/02/23，2026/03/05，2026/03/17，2026/04/24，2026/05/16</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -20339,7 +20339,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/07/03，2025/10/09，2026/1/16，2026/3/6，2026/3/14，2026/4/20</t>
+          <t>2025/06/02，2025/07/03，2025/10/09，2026/01/16，2026/03/06，2026/03/14，2026/04/20，2026/07/09</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -20350,7 +20350,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>2025/6/2</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>2025/6/2</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/10/20，2025/11/1，2026/3/5，2026/4/14</t>
+          <t>2025/06/02，2025/10/20，2025/11/01，2026/03/05，2026/04/14</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>2025/06/02，2025/11/9</t>
+          <t>2025/06/02，2025/11/09</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>2025/06/03，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2026/2/10</t>
+          <t>2025/06/03，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2026/02/10</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>2025/06/06，2025/07/03，2025/10/30，2025/11/7，2025/12/4，2026/1/28</t>
+          <t>2025/06/06，2025/07/03，2025/10/30，2025/11/07，2025/12/04，2026/01/28</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -20679,7 +20679,7 @@
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>2025/6/6</t>
+          <t>2025/06/06</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>2025/06/08，2025/06/13，2025/06/16，2025/06/28，2025/07/18，2025/07/29，2025/08/18，2025/09/03，2025/09/11，2025/09/30，2025/10/05，2025/10/30，2025/11/17，2025/12/24，2026/2/2，2026/3/25</t>
+          <t>2025/06/08，2025/06/13，2025/06/16，2025/06/28，2025/07/18，2025/07/29，2025/08/18，2025/09/03，2025/09/11，2025/09/30，2025/10/05，2025/10/30，2025/11/17，2025/12/24，2026/02/02，2026/03/25</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -20827,7 +20827,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>2025/06/09，2025/08/26，2025/09/17，2025/10/11，2026/2/12，2026/3/5</t>
+          <t>2025/06/09，2025/08/26，2025/09/17，2025/10/11，2026/02/12，2026/03/05</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>2025/06/09，2025/09/26，2025/10/17，2025/10/25，2026/5/1</t>
+          <t>2025/06/09，2025/09/26，2025/10/17，2025/10/25，2026/05/01</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -20907,7 +20907,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>2025/06/09，2025/09/21，2026/4/20</t>
+          <t>2025/06/09，2025/09/21，2026/04/20</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>2025/06/12，2025/07/13，2025/07/18，2025/09/28，2025/10/20，2026/1/19，2026/4/17，2026/6/15</t>
+          <t>2025/06/12，2025/07/13，2025/07/18，2025/09/28，2025/10/20，2026/01/19，2026/04/17，2026/06/15</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>2025/06/12，2025/06/27，2025/07/07，2026/1/1，2026/1/15</t>
+          <t>2025/06/12，2025/06/27，2025/07/07，2026/01/01，2026/01/15</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>2025/06/13，2025/07/25，2026/5/5</t>
+          <t>2025/06/13，2025/07/25，2026/05/05</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -21151,7 +21151,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/2，2025/12/9，2025/12/16，2025/12/26，2026/1/5，2026/1/15，2026/1/28，2026/3/6，2026/4/22，2026/5/10，2026/5/15，2026/6/19</t>
+          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>2025/6/16</t>
+          <t>2025/06/16</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>2025/06/16，2025/07/09，2026/1/22</t>
+          <t>2025/06/16，2025/07/09，2026/01/22</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>2025/6/17，2026/6/26</t>
+          <t>2025/06/17，2026/06/26</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -21383,7 +21383,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>2025/06/17，2025/09/12，2026/3/8</t>
+          <t>2025/06/17，2025/09/12，2026/03/08</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -21427,7 +21427,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>2025/6/19</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/09/05，2025/11/17，2026/1/9，2026/3/1，2026/6/17</t>
+          <t>2025/06/19，2025/09/05，2025/11/17，2026/01/09，2026/03/01，2026/06/17</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/09/02，2026/3/8，2026/3/17，2026/4/14，2026/6/17</t>
+          <t>2025/06/19，2025/09/02，2026/03/08，2026/03/17，2026/04/14，2026/06/17</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -21543,7 +21543,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>2025/6/19，2026/6/10</t>
+          <t>2025/06/19，2026/06/10</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -21583,7 +21583,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>2025/6/19</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -21619,7 +21619,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/7，2025/11/21，2025/12/2，2025/12/17，2026/1/1，2026/1/5，2026/1/14，2026/1/22，2026/1/24，2026/2/2，2026/3/5，2026/3/15，2026/4/1，2026/5/4，2026/5/25，2026/6/20，2026/7/5</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21630,7 +21630,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/09/12，2025/12/2</t>
+          <t>2025/06/20，2025/09/12，2025/12/02</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -21779,7 +21779,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/23，2025/09/29，2026/1/9，2026/2/10</t>
+          <t>2025/06/20，2025/06/23，2025/09/29，2026/01/09，2026/02/10</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -21823,7 +21823,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/2/18，2026/3/9，2026/4/16，2026/4/24，2026/5/15，2026/5/23，2026/6/12</t>
+          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>2025/6/20</t>
+          <t>2025/06/20</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/23</t>
+          <t>2025/06/23，2025/10/23，2026/07/09</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -21914,7 +21914,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I537" t="inlineStr"/>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>2025/6/23</t>
+          <t>2025/06/23</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -21975,7 +21975,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>2025/6/23</t>
+          <t>2025/06/23</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -22011,7 +22011,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/19，2026/1/19</t>
+          <t>2025/06/23，2025/10/19，2026/01/19</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -22051,7 +22051,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/12/4，2025/12/5，2026/2/12</t>
+          <t>2025/06/23，2025/12/04，2025/12/05，2026/02/12</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/09/15，2025/09/19，2025/10/20，2025/12/5</t>
+          <t>2025/06/23，2025/09/15，2025/09/19，2025/10/20，2025/12/05，2026/07/22</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>2025/6/26</t>
+          <t>2025/06/26</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -22167,7 +22167,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>2025/6/26</t>
+          <t>2025/06/26</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -22207,7 +22207,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/1/14，2026/1/22，2026/2/19，2026/3/13，2026/4/12，2026/5/10，2026/6/17</t>
+          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/3/8，2026/5/1，2026/5/23</t>
+          <t>2025/06/26，2025/09/21，2025/10/31，2025/11/28，2026/03/08，2026/05/01，2026/05/23，2026/07/17</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>2025/06/27，2025/09/08，2025/10/13，2025/10/16，2026/1/24，2026/2/9，2026/3/6，2026/3/22，2026/4/11，2026/4/30，2026/5/26，2026/6/18</t>
+          <t>2025/06/27，2025/09/08，2025/10/13，2025/10/16，2026/01/24，2026/02/09，2026/03/06，2026/03/22，2026/04/11，2026/04/30，2026/05/26，2026/06/18</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>2025/06/27，2025/07/21，2025/08/18，2025/08/21，2025/09/17，2025/09/22，2025/10/16，2025/11/26，2026/1/19，2026/5/20</t>
+          <t>2025/06/27，2025/07/21，2025/08/18，2025/08/21，2025/09/17，2025/09/22，2025/10/16，2025/11/26，2026/01/19，2026/05/20</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>2025/06/27，2026/3/7</t>
+          <t>2025/06/27，2026/03/07</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/09/19，2025/11/22</t>
+          <t>2025/06/29，2025/09/19，2025/11/22，2026/07/22</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -22506,7 +22506,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/5/26</t>
+          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>2025/6/29</t>
+          <t>2025/06/29</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -22647,7 +22647,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2025/6/29</t>
+          <t>2025/06/29</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>2025/6/29</t>
+          <t>2025/06/29</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>2025/6/29</t>
+          <t>2025/06/29</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>2025/6/29</t>
+          <t>2025/06/29</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -22791,7 +22791,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/11/9，2025/12/5</t>
+          <t>2025/06/29，2025/11/09，2025/12/05</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>2025/6/30</t>
+          <t>2025/06/30</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -22943,7 +22943,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>2025/7/3</t>
+          <t>2025/07/03</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -22979,7 +22979,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/9，2026/1/9，2026/1/23，2026/2/12，2026/2/25，2026/3/9，2026/3/28，2026/5/10，2026/6/6</t>
+          <t>2025/07/03，2025/07/07，2025/07/26，2025/08/28，2025/09/14，2025/10/11，2025/11/26，2025/12/09，2026/01/09，2026/01/23，2026/02/12，2026/02/25，2026/03/09，2026/03/28，2026/05/10，2026/06/06</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -22990,7 +22990,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>2025/07/05，2025/10/23，2026/1/19</t>
+          <t>2025/07/05，2025/10/23，2026/01/19</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>2025/07/06，2025/07/18，2025/12/31，2026/4/9</t>
+          <t>2025/07/06，2025/07/18，2025/12/31，2026/04/09</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -23095,7 +23095,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>2025/7/7，2026/4/9</t>
+          <t>2025/07/07，2026/04/09</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -23135,7 +23135,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/11/17，2025/12/5，2025/12/16</t>
+          <t>2025/07/07，2025/11/17，2025/12/05，2025/12/16</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -23175,7 +23175,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/09/30，2026/4/9，2026/6/26</t>
+          <t>2025/07/07，2025/09/30，2026/04/09，2026/06/26</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -23215,7 +23215,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/7，2025/11/12，2025/12/9，2026/1/14，2026/1/30，2026/4/9</t>
+          <t>2025/07/07，2025/07/31，2025/09/11，2025/10/11，2025/11/07，2025/11/12，2025/12/09，2026/01/14，2026/01/30，2026/04/09</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -23255,7 +23255,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>2025/07/07，2026/2/14</t>
+          <t>2025/07/07，2026/02/14</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>2025/07/07，2025/07/21，2025/07/27，2025/08/12，2025/08/22，2025/09/06，2025/09/13，2025/12/5</t>
+          <t>2025/07/07，2025/07/21，2025/07/27，2025/08/12，2025/08/22，2025/09/06，2025/09/13，2025/12/05</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -23455,7 +23455,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>2025/7/10</t>
+          <t>2025/07/10</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>2025/07/11，2025/07/15，2025/07/15，2025/08/04，2025/09/28，2025/10/05，2026/1/9，2026/3/7，2026/3/8，2026/6/14</t>
+          <t>2025/07/11，2025/07/15，2025/07/15，2025/08/04，2025/09/28，2025/10/05，2026/01/09，2026/03/07，2026/03/08，2026/06/14</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -23531,7 +23531,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>2025/07/11，2025/09/30，2025/10/31，2025/12/4，2026/1/23，2026/2/12，2026/3/17，2026/4/9，2026/6/28</t>
+          <t>2025/07/11，2025/09/30，2025/10/31，2025/12/04，2026/01/23，2026/02/12，2026/03/17，2026/04/09，2026/06/28</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>2025/07/11，2025/09/21</t>
+          <t>2025/07/11，2025/09/21，2026/07/26</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
@@ -23607,7 +23607,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>2025/7/11</t>
+          <t>2025/07/11</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -23683,7 +23683,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/6/3</t>
+          <t>2025/07/14，2025/07/18，2025/07/28，2025/08/07，2025/08/10，2025/09/04，2025/09/18，2025/10/16，2025/10/22，2026/06/03，2026/07/26</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/09/05，2025/11/9，2026/3/8</t>
+          <t>2025/07/14，2025/09/05，2025/11/09，2026/03/08</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -23763,7 +23763,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/3，2025/11/22，2026/1/5，2026/2/18，2026/2/23，2026/4/19，2026/6/6，2026/6/19</t>
+          <t>2025/07/14，2025/07/17，2025/07/18，2025/07/24，2025/07/28，2025/08/02，2025/08/03，2025/08/21，2025/09/05，2025/09/18，2025/09/30，2025/10/19，2025/11/03，2025/11/22，2026/01/05，2026/02/18，2026/02/23，2026/04/19，2026/06/06，2026/06/19，2026/07/28</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -23774,7 +23774,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>2025/7/15</t>
+          <t>2025/07/15</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>2025/07/15，2026/1/5，2026/1/10，2026/1/25，2026/2/10，2026/2/27，2026/3/7，2026/3/15，2026/3/29，2026/6/23</t>
+          <t>2025/07/15，2026/01/05，2026/01/10，2026/01/25，2026/02/10，2026/02/27，2026/03/07，2026/03/15，2026/03/29，2026/06/23</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/1/9，2026/4/2，2026/4/24，2026/5/22，2026/6/12，2026/6/17</t>
+          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -23919,7 +23919,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/09/06，2026/2/17</t>
+          <t>2025/07/17，2025/09/06，2026/02/17</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/24，2025/07/28，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/26，2025/08/29，2025/09/19，2025/09/29，2025/10/11，2025/10/22，2025/10/28，2025/11/10，2025/11/28，2025/12/16，2026/2/19，2026/3/6，2026/3/28，2026/4/19，2026/6/14</t>
+          <t>2025/07/17，2025/07/24，2025/07/28，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/26，2025/08/29，2025/09/19，2025/09/29，2025/10/11，2025/10/22，2025/10/28，2025/11/10，2025/11/28，2025/12/16，2026/02/19，2026/03/06，2026/03/28，2026/04/19，2026/06/14，2026/07/22</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -23966,7 +23966,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>2025/7/20</t>
+          <t>2025/07/20</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -24031,7 +24031,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>2025/7/21</t>
+          <t>2025/07/21</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -24067,7 +24067,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>2025/7/21</t>
+          <t>2025/07/21</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -24139,7 +24139,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>2025/7/21</t>
+          <t>2025/07/21</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -24175,7 +24175,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>2025/07/23，2025/12/12，2026/2/25，2026/4/9，2026/4/14</t>
+          <t>2025/07/23，2025/12/12，2026/02/25，2026/04/09，2026/04/14</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -24215,7 +24215,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/17，2025/09/11，2025/10/07，2025/11/12，2026/1/14，2026/2/7，2026/6/3</t>
+          <t>2025/07/24，2025/07/26，2025/07/28，2025/07/31，2025/08/04，2025/08/07，2025/08/12，2025/08/22，2025/09/17，2025/09/11，2025/10/07，2025/11/12，2026/01/14，2026/02/07，2026/06/03，2026/07/26</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -24226,7 +24226,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/07/28，2025/08/26，2025/09/10，2026/2/19</t>
+          <t>2025/07/26，2025/07/28，2025/08/26，2025/09/10，2026/02/19</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>2025/7/26</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -24335,7 +24335,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/09/24，2025/10/28，2025/11/12，2025/12/16，2026/1/14，2026/1/30，2026/6/10</t>
+          <t>2025/07/26，2025/09/24，2025/10/28，2025/11/12，2025/12/16，2026/01/14，2026/01/30，2026/06/10，2026/07/26</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>2025/7/26</t>
+          <t>2025/07/26，2026/07/17</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -24386,7 +24386,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
@@ -24411,7 +24411,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>2025/07/26，2025/08/08</t>
+          <t>2025/07/26，2025/08/08，2026/07/22</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
@@ -24447,7 +24447,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>2025/7/28</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/1/19，2026/2/12，2026/2/14，2026/4/8，2026/4/19，2026/5/20，2026/6/6</t>
+          <t>2025/07/31，2025/08/01，2025/08/04，2025/08/09，2025/08/13，2025/08/21，2025/08/29，2025/09/10，2025/09/30，2025/10/30，2025/11/14，2025/12/24，2026/01/19，2026/02/12，2026/02/14，2026/04/08，2026/04/19，2026/05/20，2026/06/06，2026/07/22</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>2025/8/1</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -24595,7 +24595,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>2025/08/02，2025/12/2，2026/3/14</t>
+          <t>2025/08/02，2025/12/02，2026/03/14</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -24635,7 +24635,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>2025/08/02，2025/10/12，2025/12/4，2026/1/9，2026/2/9</t>
+          <t>2025/08/02，2025/10/12，2025/12/04，2026/01/09，2026/02/09</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -24715,7 +24715,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>2025/8/4</t>
+          <t>2025/08/04</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/2，2025/12/17，2026/1/14，2026/2/2，2026/3/22，2026/4/1，2026/4/8，2026/5/15，2026/6/10</t>
+          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -24791,7 +24791,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>2025/08/09，2026/3/13，2026/3/27</t>
+          <t>2025/08/09，2026/03/13，2026/03/27</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>2025/8/9</t>
+          <t>2025/08/09</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -24871,7 +24871,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/1，2025/11/26，2025/12/30，2026/1/10，2026/2/18，2026/4/10，2026/4/23，2026/5/23，2026/6/18</t>
+          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -24882,7 +24882,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>2025/08/21，2026/1/16，2026/2/2，2026/3/17，2026/4/8，2026/6/14</t>
+          <t>2025/08/21，2026/01/16，2026/02/02，2026/03/17，2026/04/08，2026/06/14</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -25035,7 +25035,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>2025/08/24，2025/09/20，2025/10/07，2025/11/9，2025/11/21，2026/2/25，2026/3/31</t>
+          <t>2025/08/24，2025/09/20，2025/10/07，2025/11/09，2025/11/21，2026/02/25，2026/03/31</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -25075,7 +25075,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>2025/8/26</t>
+          <t>2025/08/26</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -25111,7 +25111,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>2025/08/26，2025/08/16，2025/11/13，2025/12/9，2026/1/29，2026/2/19，2026/3/31</t>
+          <t>2025/08/26，2025/08/16，2025/11/13，2025/12/09，2026/01/29，2026/02/19，2026/03/31</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -25151,7 +25151,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>2025/08/29，2025/09/08，2025/11/24，2026/6/14</t>
+          <t>2025/08/29，2025/09/08，2025/11/24，2026/06/14</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>2025/9/3，2026/4/20</t>
+          <t>2025/09/03，2026/04/20</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>2025/9/3</t>
+          <t>2025/09/03</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -25267,7 +25267,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>2025/09/04，2026/3/13</t>
+          <t>2025/09/04，2026/03/13</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -25307,7 +25307,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>2025/9/5</t>
+          <t>2025/09/05</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -25383,7 +25383,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>2025/09/10，2026/1/28</t>
+          <t>2025/09/10，2026/01/28</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -25423,7 +25423,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>2025/09/10，2025/09/22，2025/09/24，2025/10/23，2025/12/6，2026/1/24，2026/2/5，2026/2/23，2026/5/5，2026/5/23</t>
+          <t>2025/09/10，2025/09/22，2025/09/24，2025/10/23，2025/12/06，2026/01/24，2026/02/05，2026/02/23，2026/05/05，2026/05/23，2026/07/09</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -25434,7 +25434,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>2025/09/10，2025/09/13，2025/09/29，2025/10/10，2025/10/17，2025/11/27，2025/12/19，2026/1/16</t>
+          <t>2025/09/10，2025/09/13，2025/09/29，2025/10/10，2025/10/17，2025/11/27，2025/12/19，2026/01/16</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -25503,7 +25503,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -25579,7 +25579,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>2025/9/12，2026/4/24</t>
+          <t>2025/09/12，2026/04/24</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -25619,7 +25619,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -25655,7 +25655,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -25691,7 +25691,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -25727,7 +25727,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -25763,7 +25763,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -25879,7 +25879,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>2025/09/12，2026/3/4</t>
+          <t>2025/09/12，2026/03/04</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>2025/9/12</t>
+          <t>2025/09/12</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -25999,7 +25999,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>2025/09/12，2026/2/7</t>
+          <t>2025/09/12，2026/02/07</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -26039,7 +26039,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/3，2025/11/13，2025/11/24，2025/12/5，2025/12/12，2025/12/17，2026/1/6，2026/1/15，2026/1/24，2026/2/27，2026/4/19，2026/6/6</t>
+          <t>2025/09/13，2025/09/13，2025/09/13，2025/09/17，2025/09/18，2025/09/20，2025/09/21，2025/09/24，2025/09/29，2025/10/10，2025/10/13，2025/10/22，2025/10/30，2025/11/03，2025/11/13，2025/11/24，2025/12/05，2025/12/12，2025/12/17，2026/01/06，2026/01/15，2026/01/24，2026/02/27，2026/04/19，2026/06/06，2026/07/17，2026/07/28</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -26050,7 +26050,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -26079,7 +26079,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>2025/9/17</t>
+          <t>2025/09/17</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -26115,7 +26115,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>2025/09/17，2025/09/15，2025/09/22，2025/09/29，2025/09/29，2025/10/10，2025/10/28，2025/12/2，2026/1/5，2026/3/13，2026/6/23</t>
+          <t>2025/09/17，2025/09/15，2025/09/22，2025/09/29，2025/09/29，2025/10/10，2025/10/28，2025/12/02，2026/01/05，2026/03/13，2026/06/23</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>2025/09/17，2025/10/11，2025/10/13，2025/10/20，2025/10/25，2025/11/21，2025/12/17，2026/2/23，2026/3/17，2026/3/25，2026/5/23</t>
+          <t>2025/09/17，2025/10/11，2025/10/13，2025/10/20，2025/10/25，2025/11/21，2025/12/17，2026/02/23，2026/03/17，2026/03/25，2026/05/23</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -26195,7 +26195,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>2025/9/2</t>
+          <t>2025/09/02</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>2025/09/02，2025/09/22，2026/4/2</t>
+          <t>2025/09/02，2025/09/22，2026/04/02</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -26271,7 +26271,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>2025/09/15，2025/10/19，2025/10/20，2025/10/26，2025/11/1，2025/11/14，2026/1/15，2026/1/23，2026/4/19，2026/4/24，2026/7/5</t>
+          <t>2025/09/15，2025/10/19，2025/10/20，2025/10/26，2025/11/01，2025/11/14，2026/01/15，2026/01/23，2026/04/19，2026/04/24，2026/07/05</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -26311,7 +26311,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>2025/09/15，2026/3/13</t>
+          <t>2025/09/15，2026/03/13</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -26351,7 +26351,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>2025/9/15</t>
+          <t>2025/09/15</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -26387,7 +26387,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>2025/9/18</t>
+          <t>2025/09/18</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -26422,12 +26422,12 @@
       <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>VirtuaReal</t>
+          <t>艾因Eine/羽音Hanon/琉绮Ruki/七海Nana7mi/无理Muri/一果Ichigo/中单光一/弥希Miki/星弥Hoshimi/蜜球兔/罗伊Roi/阿萨Aza</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>2025/09/19，2025/09/26，2025/10/16，2025/11/26，2026/2/12，2026/4/10，2026/6/12</t>
+          <t>2025/09/19，2025/09/26，2025/10/16，2025/11/26，2026/02/12，2026/04/10，2026/06/12</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -26467,7 +26467,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>2025/9/19，2026/6/14</t>
+          <t>2025/09/19，2026/06/14</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -26543,7 +26543,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>2025/9/19</t>
+          <t>2025/09/19</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -26583,7 +26583,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>2025/09/20，2025/09/21，2025/09/22，2025/09/24，2025/09/27，2025/10/05，2025/10/12，2025/10/22，2025/11/1，2025/12/6，2025/12/12，2026/1/19，2026/4/8，2026/5/20，2026/6/6，2026/6/28</t>
+          <t>2025/09/20，2025/09/21，2025/09/22，2025/09/24，2025/09/27，2025/10/05，2025/10/12，2025/10/22，2025/11/01，2025/12/06，2025/12/12，2026/01/19，2026/04/08，2026/05/20，2026/06/06，2026/06/28，2026/07/22</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -26594,7 +26594,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/1，2025/11/9，2025/11/19，2025/11/22，2025/11/28，2025/12/8，2025/12/22，2026/1/5，2026/1/14，2026/1/22，2026/2/7，2026/2/10，2026/3/8，2026/3/22，2026/4/18，2026/5/1，2026/5/20，2026/6/10，2026/6/25，2026/7/5</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>2025/09/22，2025/10/09，2025/12/5，2026/1/25，2026/3/8</t>
+          <t>2025/09/22，2025/10/09，2025/12/05，2026/01/25，2026/03/08</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -26703,7 +26703,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>2025/9/22</t>
+          <t>2025/09/22</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>2025/9/22</t>
+          <t>2025/09/22</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>2025/9/22</t>
+          <t>2025/09/22</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -26811,7 +26811,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>2025/09/22，2025/10/09，2025/12/5</t>
+          <t>2025/09/22，2025/10/09，2025/12/05</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -26847,7 +26847,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>2025/9/24</t>
+          <t>2025/09/24</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -26883,7 +26883,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/7，2025/11/26，2025/12/6，2025/12/12，2025/12/24，2026/1/5，2026/1/19，2026/2/18，2026/3/14，2026/3/24，2026/6/10</t>
+          <t>2025/09/24，2025/09/29，2025/10/13，2025/10/17，2025/10/19，2025/10/20，2025/10/25，2025/10/28，2025/11/07，2025/11/26，2025/12/06，2025/12/12，2025/12/24，2026/01/05，2026/01/19，2026/02/18，2026/03/14，2026/03/24，2026/06/10，2026/07/22</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -26923,7 +26923,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2026/3/14</t>
+          <t>2025/09/24，2025/09/26，2026/03/14</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -26959,7 +26959,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>2025/9/24</t>
+          <t>2025/09/24</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -26995,7 +26995,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/2/5</t>
+          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -27006,7 +27006,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -27035,7 +27035,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>2025/09/26，2025/12/12，2026/3/5</t>
+          <t>2025/09/26，2025/12/12，2026/03/05</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -27075,7 +27075,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>2025/09/26，2025/11/18，2026/1/9，2026/2/25，2026/3/29</t>
+          <t>2025/09/26，2025/11/18，2026/01/09，2026/02/25，2026/03/29</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -27115,7 +27115,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>2025/9/27，2025/10/24</t>
+          <t>2025/09/27，2025/10/24</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>2025/9/27</t>
+          <t>2025/09/27</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -27191,7 +27191,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>2025/7/26，2025/9/28</t>
+          <t>2025/07/26，2025/09/28</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>2025/9/28</t>
+          <t>2025/09/28</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -27267,7 +27267,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>2025/09/29，2025/09/30，2025/10/05，2025/10/07，2025/10/11，2025/10/16，2025/10/19，2025/10/22，2025/10/25，2025/11/19，2025/12/2，2025/12/11，2026/1/9，2026/1/14，2026/2/7，2026/3/22，2026/4/27，2026/5/25，2026/6/20</t>
+          <t>2025/09/29，2025/09/30，2025/10/05，2025/10/07，2025/10/11，2025/10/16，2025/10/19，2025/10/22，2025/10/25，2025/11/19，2025/12/02，2025/12/11，2026/01/09，2026/01/14，2026/02/07，2026/03/22，2026/04/27，2026/05/25，2026/06/20，2026/07/09，2026/07/26</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -27307,7 +27307,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>2025/09/29，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/6，2026/1/15，2026/1/19，2026/3/7，2026/5/5</t>
+          <t>2025/09/29，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/22，2025/10/25，2025/11/21，2025/12/06，2026/01/15，2026/01/19，2026/03/07，2026/05/05</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -27347,7 +27347,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2025/9/30</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2025/09/30，2025/10/16，2026/3/9</t>
+          <t>2025/09/30，2025/10/16，2026/03/09</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -27459,7 +27459,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2025/10/1</t>
+          <t>2025/10/01</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -27495,7 +27495,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2025/10/1</t>
+          <t>2025/10/01</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>2025/10/01，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/20，2025/11/3，2025/11/27</t>
+          <t>2025/10/01，2025/10/07，2025/10/10，2025/10/13，2025/10/17，2025/10/20，2025/11/03，2025/11/27</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>2025/10/3</t>
+          <t>2025/10/03</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -27607,7 +27607,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2025/10/5</t>
+          <t>2025/10/05</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -27643,7 +27643,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2025/10/5</t>
+          <t>2025/10/05</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>2025/10/07，2025/10/12，2025/10/22，2026/3/24，2026/4/2</t>
+          <t>2025/10/07，2025/10/12，2025/10/22，2026/03/24，2026/04/02</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>2025/10/09，2025/11/9，2025/11/14</t>
+          <t>2025/10/09，2025/11/09，2025/11/14</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -27847,7 +27847,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>2025/10/13，2026/3/4，2026/3/24，2026/3/25，2026/4/1，2026/4/25，2026/6/23</t>
+          <t>2025/10/13，2026/03/04，2026/03/24，2026/03/25，2026/04/01，2026/04/25，2026/06/23</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
@@ -27931,7 +27931,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>2025/10/13，2025/10/18，2026/3/15</t>
+          <t>2025/10/13，2025/10/18，2026/03/15</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>2025/10/17，2025/10/18，2025/10/23，2025/12/30，2026/1/12，2026/3/29</t>
+          <t>2025/10/17，2025/10/18，2025/10/23，2025/12/30，2026/01/12，2026/03/29</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -28015,7 +28015,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>2025/10/17，2025/10/18，2025/10/23，2025/10/28，2025/12/5，2025/12/12，2025/12/30</t>
+          <t>2025/10/17，2025/10/18，2025/10/23，2025/10/28，2025/12/05，2025/12/12，2025/12/30</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -28055,7 +28055,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>2025/10/17，2025/10/24，2025/10/30，2025/11/14，2025/11/28，2025/12/12，2025/12/26，2026/1/29，2026/2/9，2026/3/4</t>
+          <t>2025/10/17，2025/10/24，2025/10/30，2025/11/14，2025/11/28，2025/12/12，2025/12/26，2026/01/29，2026/02/09，2026/03/04</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -28215,7 +28215,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>2025/10/19，2025/10/20，2025/11/18，2025/12/8，2025/12/16，2026/1/10，2026/6/17</t>
+          <t>2025/10/19，2025/10/20，2025/11/18，2025/12/08，2025/12/16，2026/01/10，2026/06/17</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>2025/10/23，2025/10/25，2025/12/12，2026/1/19，2026/3/28</t>
+          <t>2025/10/23，2025/10/25，2025/12/12，2026/01/19，2026/03/28</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -28583,7 +28583,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>2025/10/23，2025/10/28，2026/4/2，2026/6/13</t>
+          <t>2025/10/23，2025/10/28，2026/04/02，2026/06/13</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/1，2025/11/12，2025/11/26，2025/12/8，2026/1/2，2026/1/5，2026/1/9，2026/2/23，2026/3/14，2026/3/29，2026/4/24</t>
+          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>2025/10/25，2025/12/2，2026/2/23</t>
+          <t>2025/10/25，2025/12/02，2026/02/23</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -28743,7 +28743,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025/10/28，2025/11/1，2025/11/12，2025/12/19，2026/2/8，2026/2/10，2026/5/10</t>
+          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -28819,7 +28819,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>2025/10/30，2025/11/3，2025/11/7，2025/11/13，2025/11/22，2025/12/5，2026/1/2，2026/4/15</t>
+          <t>2025/10/30，2025/11/03，2025/11/07，2025/11/13，2025/11/22，2025/12/05，2026/01/02，2026/04/15</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2025/11/3，2026/4/24</t>
+          <t>2025/11/03，2026/04/24</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -28939,7 +28939,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>2025/11/3</t>
+          <t>2025/11/03</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>2025/11/9</t>
+          <t>2025/11/09</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -29011,7 +29011,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>2025/11/9</t>
+          <t>2025/11/09</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -29047,7 +29047,7 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>2025/11/9</t>
+          <t>2025/11/09</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>2025/11/9</t>
+          <t>2025/11/09</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -29119,7 +29119,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>2025/11/9，2025/11/14</t>
+          <t>2025/11/09，2025/11/14</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -29159,7 +29159,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/6，2025/12/12，2025/12/26，2026/1/5，2026/1/30，2026/2/9，2026/3/25，2026/5/1，2026/6/17</t>
+          <t>2025/11/12，2025/11/14，2025/11/24，2025/12/06，2025/12/12，2025/12/26，2026/01/05，2026/01/30，2026/02/09，2026/03/25，2026/05/01，2026/06/17，2026/07/25</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -29170,7 +29170,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -29447,7 +29447,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2025/11/19，2025/12/26，2026/3/6</t>
+          <t>2025/11/19，2025/12/26，2026/03/06</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2025/11/24，2026/4/14</t>
+          <t>2025/11/24，2026/04/14</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -29679,7 +29679,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>2025/11/26，2026/3/7</t>
+          <t>2025/11/26，2026/03/07</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/6，2025/12/13，2026/1/10，2026/1/24，2026/2/14，2026/3/14，2026/4/1，2026/4/8，2026/5/1，2026/5/6，2026/5/23，2026/6/20</t>
+          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>2025/12/2，2026/4/20</t>
+          <t>2025/12/02，2026/04/20</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -29907,7 +29907,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>2025/12/4</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>2025/12/4</t>
+          <t>2025/12/04</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -29983,7 +29983,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>2025/12/5</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -30023,7 +30023,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>2025/12/9，2026/2/2，2026/4/14</t>
+          <t>2025/12/09，2026/02/02，2026/04/14</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -30067,7 +30067,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025/12/9，2025/12/17，2026/1/14，2026/1/23，2026/2/5，2026/2/10，2026/2/25，2026/4/8，2026/5/1，2026/6/16</t>
+          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -30107,7 +30107,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>2025/12/11，2025/12/12，2025/12/17，2026/1/2，2026/1/5，2026/1/11，2026/1/17，2026/1/29，2026/2/9，2026/3/28，2026/4/29，2026/7/5</t>
+          <t>2025/12/11，2025/12/12，2025/12/17，2026/01/02，2026/01/05，2026/01/11，2026/01/17，2026/01/29，2026/02/09，2026/03/28，2026/04/29，2026/07/05，2026/07/26</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -30118,7 +30118,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/24，2025/12/26，2026/1/2，2026/1/9，2026/1/23，2026/1/29，2026/3/22，2026/4/29，2026/6/20</t>
+          <t>2025/12/19，2025/12/24，2025/12/26，2026/01/02，2026/01/09，2026/01/23，2026/01/29，2026/03/22，2026/04/29，2026/06/20</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -30439,7 +30439,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>2025/12/19，2026/2/8，2026/5/1，2026/5/25</t>
+          <t>2025/12/19，2026/02/08，2026/05/01，2026/05/25</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -30515,7 +30515,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/23，2025/12/26，2026/1/2，2026/1/5，2026/1/11，2026/1/25，2026/2/9，2026/2/23，2026/3/20，2026/4/2，2026/4/16，2026/4/29，2026/5/10，2026/6/6，2026/6/14，2026/6/20</t>
+          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -30555,7 +30555,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/1/2，2026/1/10，2026/3/13，2026/6/6</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -30595,7 +30595,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/1/5，2026/1/19，2026/1/21，2026/1/22，2026/1/24，2026/2/7，2026/2/19，2026/2/24，2026/2/24，2026/2/25，2026/3/6，2026/3/25，2026/4/11，2026/4/20，2026/5/15，2026/6/19</t>
+          <t>2025/12/26，2026/01/05，2026/01/19，2026/01/21，2026/01/22，2026/01/24，2026/02/07，2026/02/19，2026/02/24，2026/02/24，2026/02/25，2026/03/06，2026/03/25，2026/04/11，2026/04/20，2026/05/15，2026/06/19，2026/07/18</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
@@ -30606,7 +30606,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/1/19，2026/2/9</t>
+          <t>2025/12/26，2026/01/19，2026/02/09</t>
         </is>
       </c>
       <c r="F764" t="inlineStr"/>
@@ -30679,7 +30679,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/1/10，2026/1/22，2026/1/23，2026/1/31，2026/2/10，2026/2/23，2026/3/9，2026/3/12，2026/3/14，2026/3/17，2026/3/27，2026/4/24，2026/5/1，2026/6/14</t>
+          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -30755,7 +30755,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>2026/1/5</t>
+          <t>2026/01/05</t>
         </is>
       </c>
       <c r="F767" t="inlineStr"/>
@@ -30791,7 +30791,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>2025/12/27，2026/1/5，2026/1/6，2026/1/14，2026/1/23，2026/2/9</t>
+          <t>2025/12/27，2026/01/05，2026/01/06，2026/01/14，2026/01/23，2026/02/09，2026/07/27</t>
         </is>
       </c>
       <c r="F768" t="inlineStr"/>
@@ -30802,7 +30802,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>2026/1/14，2026/3/9</t>
+          <t>2026/01/14，2026/03/09</t>
         </is>
       </c>
       <c r="F769" t="inlineStr"/>
@@ -30866,15 +30866,19 @@
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr">
         <is>
-          <t>龙奔</t>
+          <t>三理Mit3uri</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>2026/1/15，2026/1/29</t>
-        </is>
-      </c>
-      <c r="F770" t="inlineStr"/>
+          <t>2026/01/15，2026/01/29</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>原词曲：龙奔</t>
+        </is>
+      </c>
       <c r="G770" t="inlineStr">
         <is>
           <t>华语</t>
@@ -30911,7 +30915,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>2026/1/19</t>
+          <t>2026/01/19</t>
         </is>
       </c>
       <c r="F771" t="inlineStr"/>
@@ -30947,7 +30951,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>2026/1/21</t>
+          <t>2026/01/21</t>
         </is>
       </c>
       <c r="F772" t="inlineStr"/>
@@ -30983,7 +30987,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>2026/1/23，2026/6/28</t>
+          <t>2026/01/23，2026/06/28</t>
         </is>
       </c>
       <c r="F773" t="inlineStr"/>
@@ -31023,7 +31027,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>2026/1/23，2026/1/25，2026/2/5，2026/2/9</t>
+          <t>2026/01/23，2026/01/25，2026/02/05，2026/02/09</t>
         </is>
       </c>
       <c r="F774" t="inlineStr"/>
@@ -31059,7 +31063,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>2026/1/23，2026/3/29</t>
+          <t>2026/01/23，2026/03/29，2026/07/26，2026/07/27</t>
         </is>
       </c>
       <c r="F775" t="inlineStr"/>
@@ -31070,7 +31074,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -31099,7 +31103,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2026/1/24，2026/1/25，2026/1/26，2026/2/2，2026/2/7，2026/2/10，2026/2/14，2026/2/19，2026/3/4，2026/3/12，2026/3/31，2026/4/1，2026/4/14，2026/4/18，2026/5/10，2026/5/23，2026/6/12，2026/7/3</t>
+          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
@@ -31110,7 +31114,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -31139,7 +31143,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>2026/1/24，2026/2/8，2026/6/20</t>
+          <t>2026/01/24，2026/02/08，2026/06/20</t>
         </is>
       </c>
       <c r="F777" t="inlineStr"/>
@@ -31183,7 +31187,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>2026/1/25</t>
+          <t>2026/01/25</t>
         </is>
       </c>
       <c r="F778" t="inlineStr"/>
@@ -31223,7 +31227,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>2026/1/25，2026/2/10</t>
+          <t>2026/01/25，2026/02/10</t>
         </is>
       </c>
       <c r="F779" t="inlineStr"/>
@@ -31263,7 +31267,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>2026/1/25，2026/1/30，2026/2/2，2026/2/8，2026/2/19，2026/2/23，2026/2/25，2026/3/12，2026/3/28，2026/4/12，2026/4/20，2026/6/26</t>
+          <t>2026/01/25，2026/01/30，2026/02/02，2026/02/08，2026/02/19，2026/02/23，2026/02/25，2026/03/12，2026/03/28，2026/04/12，2026/04/20，2026/06/26，2026/07/22</t>
         </is>
       </c>
       <c r="F780" t="inlineStr"/>
@@ -31274,7 +31278,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -31307,7 +31311,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>2026/1/29</t>
+          <t>2026/01/29</t>
         </is>
       </c>
       <c r="F781" t="inlineStr"/>
@@ -31347,7 +31351,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>2026/1/30</t>
+          <t>2026/01/30</t>
         </is>
       </c>
       <c r="F782" t="inlineStr"/>
@@ -31383,7 +31387,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>2026/2/2，2026/2/5，2026/2/9，2026/2/22</t>
+          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27</t>
         </is>
       </c>
       <c r="F783" t="inlineStr"/>
@@ -31394,7 +31398,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -31423,7 +31427,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>2026/2/7，2026/4/19</t>
+          <t>2026/02/07，2026/04/19</t>
         </is>
       </c>
       <c r="F784" t="inlineStr"/>
@@ -31463,7 +31467,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>2026/2/7</t>
+          <t>2026/02/07</t>
         </is>
       </c>
       <c r="F785" t="inlineStr"/>
@@ -31503,7 +31507,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>2026/2/8</t>
+          <t>2026/02/08</t>
         </is>
       </c>
       <c r="F786" t="inlineStr"/>
@@ -31543,7 +31547,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/2/8，2026/2/9，2026/2/14，2026/2/20，2026/2/28，2026/5/25，2026/6/13，2026/7/5</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31554,7 +31558,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -31583,7 +31587,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2026/2/8，2026/2/9，2026/2/12，2026/2/14，2026/2/19，2026/2/23，2026/2/24，2026/2/25，2026/3/1，2026/3/5，2026/3/12，2026/3/17，2026/3/19，2026/3/31，2026/4/20，2026/5/2，2026/5/21，2026/6/20</t>
+          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16</t>
         </is>
       </c>
       <c r="F788" t="inlineStr"/>
@@ -31594,7 +31598,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -31627,7 +31631,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>2026/2/9，2026/2/27，2026/3/9，2026/4/14，2026/5/25</t>
+          <t>2026/02/09，2026/02/27，2026/03/09，2026/04/14，2026/05/25，2026/07/25</t>
         </is>
       </c>
       <c r="F789" t="inlineStr"/>
@@ -31638,7 +31642,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -31667,7 +31671,7 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>2026/2/12</t>
+          <t>2026/02/12</t>
         </is>
       </c>
       <c r="F790" t="inlineStr"/>
@@ -31711,7 +31715,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>2026/2/14，2026/2/24，2026/3/7，2026/3/13，2026/5/26，2026/6/19</t>
+          <t>2026/02/14，2026/02/24，2026/03/07，2026/03/13，2026/05/26，2026/06/19</t>
         </is>
       </c>
       <c r="F791" t="inlineStr"/>
@@ -31755,7 +31759,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>2026/2/17，2026/2/19</t>
+          <t>2026/02/17，2026/02/19</t>
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
@@ -31795,7 +31799,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>2026/2/17</t>
+          <t>2026/02/17</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
@@ -31831,7 +31835,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>2026/2/19</t>
+          <t>2026/02/19</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
@@ -31871,7 +31875,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>2026/2/19</t>
+          <t>2026/02/19</t>
         </is>
       </c>
       <c r="F795" t="inlineStr"/>
@@ -31911,7 +31915,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>2026/2/20</t>
+          <t>2026/02/20</t>
         </is>
       </c>
       <c r="F796" t="inlineStr"/>
@@ -31951,7 +31955,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>2026/2/20</t>
+          <t>2026/02/20</t>
         </is>
       </c>
       <c r="F797" t="inlineStr"/>
@@ -31991,7 +31995,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2026/2/22，2026/2/23，2026/2/24，2026/2/25，2026/3/14，2026/4/20，2026/6/16</t>
+          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
@@ -32035,7 +32039,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>2026/2/23</t>
+          <t>2026/02/23</t>
         </is>
       </c>
       <c r="F799" t="inlineStr"/>
@@ -32075,7 +32079,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>2026/2/23</t>
+          <t>2026/02/23</t>
         </is>
       </c>
       <c r="F800" t="inlineStr"/>
@@ -32115,7 +32119,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>2026/2/25，2026/2/28，2026/3/1，2026/4/20</t>
+          <t>2026/02/25，2026/02/28，2026/03/01，2026/04/20</t>
         </is>
       </c>
       <c r="F801" t="inlineStr"/>
@@ -32159,7 +32163,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>2026/2/27</t>
+          <t>2026/02/27</t>
         </is>
       </c>
       <c r="F802" t="inlineStr"/>
@@ -32199,7 +32203,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>2026/3/1，2026/3/1，2026/3/1，2026/3/1，2026/3/1，2026/3/4，2026/3/5，2026/3/5，2026/3/6，2026/3/12，2026/3/21，2026/3/31，2026/4/20，2026/5/2，2026/5/6，2026/5/21，2026/5/26，2026/6/14</t>
+          <t>2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/01，2026/03/04，2026/03/05，2026/03/05，2026/03/06，2026/03/12，2026/03/21，2026/03/31，2026/04/20，2026/05/02，2026/05/06，2026/05/21，2026/05/26，2026/06/14，2026/07/16</t>
         </is>
       </c>
       <c r="F803" t="inlineStr"/>
@@ -32210,7 +32214,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -32247,7 +32251,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>2026/3/4</t>
+          <t>2026/03/04</t>
         </is>
       </c>
       <c r="F804" t="inlineStr"/>
@@ -32283,7 +32287,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>2026/3/4</t>
+          <t>2026/03/04</t>
         </is>
       </c>
       <c r="F805" t="inlineStr"/>
@@ -32327,7 +32331,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>2026/3/4</t>
+          <t>2026/03/04</t>
         </is>
       </c>
       <c r="F806" t="inlineStr"/>
@@ -32367,7 +32371,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>2025/12/8，2026/1/9，2026/3/4，2026/7/5</t>
+          <t>2025/12/08，2026/01/09，2026/03/04，2026/07/05</t>
         </is>
       </c>
       <c r="F807" t="inlineStr"/>
@@ -32411,7 +32415,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>2025/12/8</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="F808" t="inlineStr"/>
@@ -32451,7 +32455,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>2026/3/7</t>
+          <t>2026/03/07</t>
         </is>
       </c>
       <c r="F809" t="inlineStr"/>
@@ -32491,7 +32495,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>2026/3/7，2026/3/29</t>
+          <t>2026/03/07，2026/03/29</t>
         </is>
       </c>
       <c r="F810" t="inlineStr"/>
@@ -32531,7 +32535,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>2026/3/9</t>
+          <t>2026/03/09</t>
         </is>
       </c>
       <c r="F811" t="inlineStr"/>
@@ -32571,7 +32575,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>2026/3/13，2026/3/25，2026/3/28，2026/4/11，2026/4/20，2026/5/26，2026/7/5</t>
+          <t>2026/03/13，2026/03/25，2026/03/28，2026/04/11，2026/04/20，2026/05/26，2026/07/05，2026/07/22</t>
         </is>
       </c>
       <c r="F812" t="inlineStr"/>
@@ -32582,7 +32586,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -32619,7 +32623,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>2026/3/13，2026/5/1</t>
+          <t>2026/03/13，2026/05/01</t>
         </is>
       </c>
       <c r="F813" t="inlineStr"/>
@@ -32659,7 +32663,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/3/13，2026/3/14，2026/3/28，2026/4/29，2026/5/25，2026/6/3，2026/6/13，2026/7/2</t>
+          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -32670,7 +32674,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -32699,7 +32703,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>2026/3/14，2026/3/17</t>
+          <t>2026/03/14，2026/03/17</t>
         </is>
       </c>
       <c r="F815" t="inlineStr"/>
@@ -32735,7 +32739,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>2026/3/14</t>
+          <t>2026/03/14</t>
         </is>
       </c>
       <c r="F816" t="inlineStr"/>
@@ -32775,7 +32779,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>2026/3/15，2026/3/17</t>
+          <t>2026/03/15，2026/03/17</t>
         </is>
       </c>
       <c r="F817" t="inlineStr"/>
@@ -32819,7 +32823,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>2026/3/15</t>
+          <t>2026/03/15</t>
         </is>
       </c>
       <c r="F818" t="inlineStr"/>
@@ -32855,7 +32859,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>2026/3/17</t>
+          <t>2026/03/17</t>
         </is>
       </c>
       <c r="F819" t="inlineStr"/>
@@ -32891,7 +32895,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>2026/3/17</t>
+          <t>2026/03/17</t>
         </is>
       </c>
       <c r="F820" t="inlineStr"/>
@@ -32931,7 +32935,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>2026/3/17，2026/6/17</t>
+          <t>2026/03/17，2026/06/17</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
@@ -32971,7 +32975,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>2026/3/17，2026/3/29</t>
+          <t>2026/03/17，2026/03/29</t>
         </is>
       </c>
       <c r="F822" t="inlineStr"/>
@@ -33011,7 +33015,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026/3/17，2026/3/17，2026/3/25，2026/3/27，2026/3/29，2026/4/2，2026/4/8，2026/4/16，2026/4/20，2026/5/2，2026/5/6，2026/5/26，2026/6/14</t>
+          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -33022,7 +33026,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -33059,7 +33063,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>2026/3/25，2026/5/26</t>
+          <t>2026/03/25，2026/05/26</t>
         </is>
       </c>
       <c r="F824" t="inlineStr"/>
@@ -33107,7 +33111,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>2026/3/25，2026/4/14，2026/5/25，2026/5/25，2026/6/25，2026/6/25，2026/6/25，2026/6/26</t>
+          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07</t>
         </is>
       </c>
       <c r="F825" t="inlineStr"/>
@@ -33118,7 +33122,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -33147,7 +33151,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>2026/3/28，2026/4/14，2026/5/10，2026/6/12</t>
+          <t>2026/03/28，2026/04/14，2026/05/10，2026/06/12</t>
         </is>
       </c>
       <c r="F826" t="inlineStr"/>
@@ -33187,7 +33191,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>2026/3/29</t>
+          <t>2026/03/29</t>
         </is>
       </c>
       <c r="F827" t="inlineStr"/>
@@ -33227,7 +33231,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/25，2026/4/1</t>
+          <t>2025/12/24，2025/12/25，2026/04/01</t>
         </is>
       </c>
       <c r="F828" t="inlineStr"/>
@@ -33267,7 +33271,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>2026/4/1，2026/6/10</t>
+          <t>2026/04/01，2026/06/10</t>
         </is>
       </c>
       <c r="F829" t="inlineStr"/>
@@ -33307,7 +33311,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>2026/4/1</t>
+          <t>2026/04/01</t>
         </is>
       </c>
       <c r="F830" t="inlineStr"/>
@@ -33351,7 +33355,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>2026/4/2</t>
+          <t>2026/04/02</t>
         </is>
       </c>
       <c r="F831" t="inlineStr"/>
@@ -33395,7 +33399,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>2026/4/9</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F832" t="inlineStr"/>
@@ -33435,7 +33439,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>2026/4/9</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F833" t="inlineStr"/>
@@ -33475,7 +33479,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>2026/4/9</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F834" t="inlineStr"/>
@@ -33515,7 +33519,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>2026/4/9</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F835" t="inlineStr"/>
@@ -33555,7 +33559,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>2026/4/9，2026/6/20</t>
+          <t>2026/04/09，2026/06/20</t>
         </is>
       </c>
       <c r="F836" t="inlineStr"/>
@@ -33595,7 +33599,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>2026/4/9</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F837" t="inlineStr"/>
@@ -33635,7 +33639,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>2026/4/9</t>
+          <t>2026/04/09</t>
         </is>
       </c>
       <c r="F838" t="inlineStr"/>
@@ -33675,7 +33679,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>2026/4/14</t>
+          <t>2026/04/14</t>
         </is>
       </c>
       <c r="F839" t="inlineStr"/>
@@ -33715,7 +33719,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>2026/4/14，2026/6/14</t>
+          <t>2026/04/14，2026/06/14</t>
         </is>
       </c>
       <c r="F840" t="inlineStr"/>
@@ -33755,7 +33759,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>2026/4/14</t>
+          <t>2026/04/14</t>
         </is>
       </c>
       <c r="F841" t="inlineStr"/>
@@ -33795,7 +33799,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>2026/4/14</t>
+          <t>2026/04/14</t>
         </is>
       </c>
       <c r="F842" t="inlineStr"/>
@@ -33831,7 +33835,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>2026/4/14，2026/4/14</t>
+          <t>2026/04/14，2026/04/14，2026/07/22</t>
         </is>
       </c>
       <c r="F843" t="inlineStr"/>
@@ -33842,7 +33846,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -33871,7 +33875,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>2026/4/16，2026/4/29，2026/5/15，2026/5/25</t>
+          <t>2026/04/16，2026/04/29，2026/05/15，2026/05/25</t>
         </is>
       </c>
       <c r="F844" t="inlineStr"/>
@@ -33911,7 +33915,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>2026/4/17，2026/5/25，2026/5/25，2026/5/26</t>
+          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26</t>
         </is>
       </c>
       <c r="F845" t="inlineStr"/>
@@ -33955,7 +33959,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>2026/4/19</t>
+          <t>2026/04/19，2026/07/21</t>
         </is>
       </c>
       <c r="F846" t="inlineStr"/>
@@ -33966,7 +33970,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -33999,7 +34003,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>2026/4/20</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="F847" t="inlineStr"/>
@@ -34035,7 +34039,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>2026/4/20</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="F848" t="inlineStr"/>
@@ -34079,7 +34083,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>2026/4/24</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="F849" t="inlineStr"/>
@@ -34108,10 +34112,14 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Komm,susser Tod</t>
-        </is>
-      </c>
-      <c r="C850" t="inlineStr"/>
+          <t>Komm, süsser Tod</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>来吧，甜蜜的死亡</t>
+        </is>
+      </c>
       <c r="D850" t="inlineStr">
         <is>
           <t>ARIANNE</t>
@@ -34119,7 +34127,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>2026/4/24</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="F850" t="inlineStr"/>
@@ -34163,7 +34171,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>2026/4/24，2026/5/1</t>
+          <t>2026/04/24，2026/05/01</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>
@@ -34203,7 +34211,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>2026/5/1</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -34243,7 +34251,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>2026/5/1</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F853" t="inlineStr"/>
@@ -34283,7 +34291,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2026/5/1</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -34323,7 +34331,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>2026/5/1</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F855" t="inlineStr"/>
@@ -34362,12 +34370,12 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>樱高轻音部</t>
+          <t>放課後ティータイム</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>2026/5/1</t>
+          <t>2026/05/01</t>
         </is>
       </c>
       <c r="F856" t="inlineStr"/>
@@ -34411,7 +34419,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>2026/5/10</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="F857" t="inlineStr"/>
@@ -34455,7 +34463,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>2026/5/15</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="F858" t="inlineStr"/>
@@ -34499,7 +34507,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>2026/5/25，2026/5/25，2026/5/25，2026/5/26，2026/5/26，2026/6/25，2026/6/26</t>
+          <t>2026/05/25，2026/05/25，2026/05/25，2026/05/26，2026/05/26，2026/06/25，2026/06/26，2026/07/09，2026/07/16</t>
         </is>
       </c>
       <c r="F859" t="inlineStr"/>
@@ -34510,7 +34518,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -34543,7 +34551,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2026/5/25，2026/5/26，2026/6/15</t>
+          <t>2026/05/25，2026/05/26，2026/06/15</t>
         </is>
       </c>
       <c r="F860" t="inlineStr"/>
@@ -34578,12 +34586,12 @@
       <c r="C861" t="inlineStr"/>
       <c r="D861" t="inlineStr">
         <is>
-          <t>VirtuaReal</t>
+          <t>艾因Eine/七海Nana7mi/中单光一/星弥Hoshimi/弥希Miki/阿萨Aza/千春Chiharu/小可学妹/阿梓从小就很可爱/勾檀Mayumi/舒三妈Susam/诺莺Nox/桃星Tocci/瑞娅_Rhea/尤格Yog/希侑Kiyuu/雾深Girimi</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>2026/6/6</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="F861" t="inlineStr"/>
@@ -34618,12 +34626,12 @@
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr">
         <is>
-          <t>VirtuaReal</t>
+          <t>瑞娅_Rhea/岁己SUI/栞栞Shiori/米汀Nagisa/花礼Harei/泽音Melody/三理Mit3uri</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>2026/6/6</t>
+          <t>2026/06/06</t>
         </is>
       </c>
       <c r="F862" t="inlineStr"/>
@@ -34663,7 +34671,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>2026/6/10</t>
+          <t>2026/06/10</t>
         </is>
       </c>
       <c r="F863" t="inlineStr"/>
@@ -34698,12 +34706,12 @@
       <c r="C864" t="inlineStr"/>
       <c r="D864" t="inlineStr">
         <is>
-          <t>VirtuaReal</t>
+          <t>艾因Eine/七海Nana7mi/中单光一/弥希Miki/阿萨Aza/雪绘Yukie/阿梓从小就很可爱/小可学妹/诺莺Nox/舒三妈Susam/桃星Tocci/瑞娅_Rhea/尤格Yog/雾深Girimi/莱恩Leo</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>2026/6/14，2026/6/14</t>
+          <t>2026/06/14，2026/06/14</t>
         </is>
       </c>
       <c r="F864" t="inlineStr"/>
@@ -34743,7 +34751,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>2026/6/14</t>
+          <t>2026/06/14，2026/07/10，2026/07/15，2026/07/27</t>
         </is>
       </c>
       <c r="F865" t="inlineStr"/>
@@ -34754,7 +34762,7 @@
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
@@ -34783,7 +34791,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>2026/6/14，2026/6/14</t>
+          <t>2026/06/14，2026/06/14</t>
         </is>
       </c>
       <c r="F866" t="inlineStr"/>
@@ -34827,7 +34835,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>2026/6/15</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="F867" t="inlineStr"/>
@@ -34867,7 +34875,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>2026/6/16，2026/6/17，2026/6/25</t>
+          <t>2026/06/16，2026/06/17，2026/06/25</t>
         </is>
       </c>
       <c r="F868" t="inlineStr"/>
@@ -34907,7 +34915,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>2026/6/18</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="F869" t="inlineStr"/>
@@ -34947,7 +34955,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>2026/6/20</t>
+          <t>2026/06/20</t>
         </is>
       </c>
       <c r="F870" t="inlineStr"/>
@@ -34991,7 +34999,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>2026/6/20</t>
+          <t>2026/06/20</t>
         </is>
       </c>
       <c r="F871" t="inlineStr"/>
@@ -35027,7 +35035,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>2026/6/20，2026/6/30</t>
+          <t>2026/06/20，2026/06/30</t>
         </is>
       </c>
       <c r="F872" t="inlineStr"/>
@@ -35067,7 +35075,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>2026/6/25</t>
+          <t>2026/06/25，2026/07/09，2026/07/18</t>
         </is>
       </c>
       <c r="F873" t="inlineStr"/>
@@ -35078,7 +35086,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -35107,7 +35115,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>2026/6/25</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="F874" t="inlineStr"/>
@@ -35151,7 +35159,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>2026/6/29</t>
+          <t>2026/06/29，2026/07/28</t>
         </is>
       </c>
       <c r="F875" t="inlineStr"/>
@@ -35162,7 +35170,7 @@
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -35191,7 +35199,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>2026/7/5</t>
+          <t>2026/07/05，2026/07/07，2026/07/17</t>
         </is>
       </c>
       <c r="F876" t="inlineStr"/>
@@ -35202,15 +35210,267 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>BV1ZoTC6BELe</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>辞职信</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr"/>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>ChiliChill</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr"/>
+      <c r="J877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>定玄</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>鸣潮先约电台/黄霄雲/杨秉音</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>2026/07/17，2026/07/18，2026/07/27</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr"/>
+      <c r="J878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>红日</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr"/>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>李克勤</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>粤语</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I876" t="inlineStr">
-        <is>
-          <t>BV1ZoTC6BELe</t>
-        </is>
-      </c>
-      <c r="J876" t="inlineStr"/>
+      <c r="I879" t="inlineStr"/>
+      <c r="J879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>醉后喜欢我</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr"/>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>icyball 冰球乐团</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>2026/07/26，2026/07/27，2026/07/28</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr"/>
+      <c r="J880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>NIGHT DANCER</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr"/>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>imase</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>日语</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr"/>
+      <c r="J881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>我们没有在一起</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>刘若英</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr"/>
+      <c r="J882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>圈住你</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr"/>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>一口甜</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr"/>
+      <c r="J883" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -16145,7 +16145,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>BV1HYgy6REZM</t>
+        </is>
+      </c>
       <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
@@ -16413,7 +16417,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>BV1pagy6xEgX</t>
+        </is>
+      </c>
       <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
@@ -23469,7 +23477,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I577" t="inlineStr"/>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>BV1zzuKzpEc5</t>
+        </is>
+      </c>
       <c r="J577" t="inlineStr"/>
     </row>
     <row r="578">
@@ -23585,7 +23597,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I580" t="inlineStr"/>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>BV1GbgX68EMy</t>
+        </is>
+      </c>
       <c r="J580" t="inlineStr"/>
     </row>
     <row r="581">
@@ -24389,7 +24405,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I601" t="inlineStr"/>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>BV1Qx3w6pEUx</t>
+        </is>
+      </c>
       <c r="J601" t="inlineStr"/>
     </row>
     <row r="602">
@@ -24425,7 +24445,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I602" t="inlineStr"/>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>BV1DDgk6eEWB</t>
+        </is>
+      </c>
       <c r="J602" t="inlineStr"/>
     </row>
     <row r="603">
@@ -35253,7 +35277,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I877" t="inlineStr"/>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>BV19x3P6cEPV</t>
+        </is>
+      </c>
       <c r="J877" t="inlineStr"/>
     </row>
     <row r="878">
@@ -35289,7 +35317,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I878" t="inlineStr"/>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>BV1Xx3P6cEfK</t>
+        </is>
+      </c>
       <c r="J878" t="inlineStr"/>
     </row>
     <row r="879">
@@ -35325,7 +35357,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I879" t="inlineStr"/>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>BV1D43w6QE1L</t>
+        </is>
+      </c>
       <c r="J879" t="inlineStr"/>
     </row>
     <row r="880">
@@ -35361,7 +35397,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I880" t="inlineStr"/>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>BV1CU3B6VEPC</t>
+        </is>
+      </c>
       <c r="J880" t="inlineStr"/>
     </row>
     <row r="881">
@@ -35397,7 +35437,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I881" t="inlineStr"/>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>BV19x3P6cENj</t>
+        </is>
+      </c>
       <c r="J881" t="inlineStr"/>
     </row>
     <row r="882">
@@ -35433,7 +35477,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I882" t="inlineStr"/>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>BV1g8gX6fEqx</t>
+        </is>
+      </c>
       <c r="J882" t="inlineStr"/>
     </row>
     <row r="883">
@@ -35469,7 +35517,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I883" t="inlineStr"/>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>BV19x3P6cESt</t>
+        </is>
+      </c>
       <c r="J883" t="inlineStr"/>
     </row>
   </sheetData>

--- a/scripts/Book1.xlsx
+++ b/scripts/Book1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J883"/>
+  <dimension ref="A1:J889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/17，2025/09/02，2025/09/07，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22</t>
+          <t>2025/03/01，2025/03/15，2025/04/01，2025/04/15，2025/04/26，2025/05/09，2025/05/30，2025/06/08，2025/07/05，2025/07/11，2025/08/13，2025/09/17，2025/09/02，2025/09/07，2025/09/19，2025/10/01，2025/10/09，2025/10/16，2025/10/24，2025/10/30，2025/11/09，2025/11/14，2025/12/24，2025/12/26，2026/01/16，2026/01/24，2026/01/28，2026/01/30，2026/02/10，2026/02/14，2026/03/09，2026/03/27，2026/04/01，2026/04/14，2026/04/24，2026/06/12，2026/07/22，2026/08/11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23</t>
+          <t>2025/03/02，2025/03/29，2025/05/06，2025/05/30，2025/06/28，2025/09/04，2025/09/18，2025/11/07，2026/01/14，2026/01/24，2026/02/19，2026/03/07，2026/03/15，2026/06/06，2026/06/23，2026/08/05，2026/08/05</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19</t>
+          <t>2025/03/02，2025/03/29，2025/04/11，2025/04/17，2025/04/26，2025/05/04，2025/05/09，2025/05/17，2025/05/24，2025/06/02，2025/06/20，2025/06/27，2025/07/11，2025/07/21，2025/07/26，2025/08/08，2025/08/29，2025/09/02，2025/10/03，2025/10/09，2025/10/22，2025/11/09，2025/12/11，2026/01/15，2026/02/12，2026/04/19，2026/08/08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22</t>
+          <t>2025/03/02，2025/03/14，2025/03/28，2025/04/17，2025/04/25，2025/05/12，2025/05/12，2025/05/18，2025/05/29，2025/06/02，2025/06/05，2025/06/12，2025/06/27，2025/07/10，2025/08/04，2025/08/08，2025/08/21，2025/08/28，2025/09/10，2025/09/22，2025/09/30，2025/10/12，2025/11/01，2025/11/17，2025/12/02，2025/12/31，2026/02/02，2026/02/14，2026/03/06，2026/04/01，2026/04/20，2026/05/15，2026/06/10，2026/07/22，2026/08/09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22</t>
+          <t>2025/03/03，2025/03/21，2025/04/17，2025/04/21，2025/05/12，2025/05/26，2025/05/30，2025/06/26，2025/07/07，2025/07/13，2025/07/26，2025/08/12，2025/08/22，2025/09/19，2025/10/03，2025/10/28，2025/11/09，2025/11/19，2025/12/16，2026/01/16，2026/01/28，2026/02/07，2026/02/10，2026/03/17，2026/04/19，2026/05/23，2026/06/19，2026/07/22，2026/08/08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09</t>
+          <t>2025/03/03，2025/04/04，2025/04/14，2025/04/20，2025/04/24，2025/05/09，2025/05/18，2025/05/29，2025/06/06，2025/08/01，2025/09/21，2025/10/10，2025/11/28，2025/12/08，2025/12/30，2026/04/26，2026/07/09，2026/07/31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25</t>
+          <t>2025/03/03，2025/03/25，2025/04/03，2025/04/07，2025/04/18，2025/04/24，2025/05/04，2025/05/12，2025/05/16，2025/05/19，2025/05/30，2025/06/02，2025/06/09，2025/06/13，2025/07/05，2025/07/14，2025/07/21，2025/07/28，2025/08/29，2025/09/04，2025/09/07，2025/10/05，2025/10/10，2025/10/22，2025/11/10，2025/12/07，2025/12/31，2026/01/14，2026/01/19，2026/03/29，2026/04/12，2026/04/27，2026/05/01，2026/06/03，2026/06/18，2026/06/25，2026/07/31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20</t>
+          <t>2025/03/04，2025/03/30，2025/05/01，2025/05/26，2025/06/17，2025/08/03，2025/09/26，2025/10/26，2026/01/03，2026/03/25，2026/05/10，2026/06/20，2026/8/16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/04/07，2025/05/29，2025/06/06，2025/06/19，2025/06/26，2025/07/10，2025/07/11，2025/07/14，2025/08/02，2025/09/03，2025/09/26，2025/10/03，2025/11/09，2025/11/24，2025/11/26，2026/01/05，2026/01/30，2026/03/04，2026/06/17</t>
+          <t>2025/03/04，2025/04/07，2025/05/29，2025/06/06，2025/06/19，2025/06/26，2025/07/10，2025/07/11，2025/07/14，2025/08/02，2025/09/03，2025/09/26，2025/10/03，2025/11/09，2025/11/24，2025/11/26，2026/01/05，2026/01/30，2026/03/04，2026/06/17，2026/08/05</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04</t>
+          <t>2025/03/04，2025/03/14，2025/04/15，2025/05/03，2025/05/19，2025/07/18，2025/07/28，2025/08/28，2025/09/22，2025/10/19，2025/10/26，2025/11/09，2025/12/30，2026/02/20，2026/02/23，2026/03/04，2026/04/11，2026/04/16，2026/04/23，2026/06/14，2026/07/04，2026/07/31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26</t>
+          <t>2025/03/04，2025/03/13，2025/04/03，2025/05/12，2025/05/19，2025/05/23，2025/05/25，2025/06/12，2025/07/15，2025/07/20，2025/07/23，2025/08/02，2025/08/10，2025/08/29，2025/09/17，2025/09/19，2025/09/27，2025/10/22，2025/11/01，2025/11/09，2025/11/21，2025/12/08，2026/01/15，2026/01/24，2026/03/04，2026/03/14，2026/05/06，2026/05/16，2026/05/20，2026/06/12，2026/07/16，2026/07/26，2026/07/31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15</t>
+          <t>2025/03/04，2025/03/30，2025/04/14，2025/04/25，2025/06/05，2025/06/13，2025/06/26，2025/07/13，2025/07/24，2025/08/12，2025/08/28，2025/09/26，2025/10/07，2025/10/11，2025/11/01，2025/11/28，2025/12/12，2026/01/05，2026/01/22，2026/03/04，2026/03/08，2026/03/22，2026/04/22，2026/04/24，2026/05/10，2026/05/23，2026/06/10，2026/06/15，2026/07/31，2026/08/11</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20</t>
+          <t>2025/03/04，2025/03/14，2025/04/17，2025/05/06，2025/05/25，2025/05/25，2025/05/31，2025/09/03，2025/11/07，2025/12/24，2026/01/01，2026/01/16，2026/03/14，2026/05/01，2026/05/20，2026/08/01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22</t>
+          <t>2025/03/06，2025/03/20，2025/04/02，2025/04/10，2025/04/19，2025/04/27，2025/05/13，2025/05/15，2025/05/18，2025/05/26，2025/06/06，2025/06/12，2025/06/21，2025/07/05，2025/07/10，2025/07/13，2025/07/27，2025/08/29，2025/09/13，2025/09/19，2025/09/28，2025/10/23，2025/10/28，2025/12/23，2026/01/14，2026/02/19，2026/03/14，2026/04/16，2026/06/17，2026/07/16，2026/07/22，2026/08/11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05</t>
+          <t>2025/03/06，2025/03/19，2025/04/11，2025/05/03，2025/07/10，2025/09/05，2025/09/18，2025/10/01，2025/11/07，2025/11/09，2025/12/02，2026/01/21，2026/03/05，2026/04/16，2026/06/23，2026/07/05，2026/08/05，2026/08/05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025/03/06，2025/04/13，2025/05/01，2025/06/15，2025/07/24，2025/08/30，2025/09/05，2025/10/09，2025/11/03，2025/12/12，2026/02/04，2026/04/18，2026/05/20，2026/06/20</t>
+          <t>2025/03/06，2025/04/13，2025/05/01，2025/06/15，2025/07/24，2025/08/30，2025/09/05，2025/10/09，2025/11/03，2025/12/12，2026/02/04，2026/04/18，2026/05/20，2026/06/20，2026/07/30，2026/08/09</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25</t>
+          <t>2025/03/07，2025/03/28，2025/04/24，2025/04/27，2025/05/01，2025/05/23，2025/05/25，2025/06/23，2025/07/03，2025/07/20，2025/07/27，2025/08/19，2025/09/06，2025/09/21，2025/10/17，2025/10/19，2025/11/01，2025/11/10，2025/11/18，2025/11/24，2025/12/23，2026/01/09，2026/01/22，2026/02/14，2026/03/22，2026/04/19，2026/05/01，2026/05/23，2026/06/25，2026/08/07</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20</t>
+          <t>2025/03/07，2025/03/21，2025/04/04，2025/04/18，2025/04/29，2025/05/08，2025/05/22，2025/05/25，2025/06/06，2025/06/08，2025/06/13，2025/06/13，2025/06/26，2025/07/03，2025/07/05，2025/07/11，2025/07/14，2025/07/26，2025/08/02，2025/08/12，2025/08/21，2025/09/17，2025/11/01，2025/11/09，2025/12/04，2025/12/16，2025/12/31，2026/01/09，2026/01/15，2026/01/21，2026/01/23，2026/01/29，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/02/24，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/05，2026/03/07，2026/03/08，2026/03/09，2026/03/12，2026/03/13，2026/03/14，2026/03/15，2026/03/17，2026/03/18，2026/03/19，2026/03/22，2026/03/24，2026/03/27，2026/03/28，2026/03/31，2026/04/08，2026/04/14，2026/04/18，2026/04/25，2026/05/01，2026/05/15，2026/05/25，2026/06/12，2026/06/23，2026/06/26，2026/07/04，2026/07/20，2026/07/30，2026/08/09</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025/03/07，2025/04/11，2025/04/29，2025/08/01，2025/10/26，2026/02/19，2026/02/23，2026/03/06</t>
+          <t>2025/03/07，2025/04/11，2025/04/29，2025/08/01，2025/10/26，2026/02/19，2026/02/23，2026/03/06，2026/08/02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25</t>
+          <t>2025/03/09，2025/03/14，2025/04/07，2025/04/15，2025/04/27，2025/05/12，2025/05/27，2025/06/05，2025/06/08，2025/07/20，2025/08/01，2025/09/21，2025/09/28，2025/10/07，2025/10/18，2025/10/24，2025/11/10，2025/12/01，2026/01/16，2026/02/02，2026/02/23，2026/03/08，2026/03/19，2026/03/21，2026/04/16，2026/05/10，2026/06/14，2026/07/25，2026/08/07</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20</t>
+          <t>2025/03/09，2025/03/30，2025/04/10，2025/04/20，2025/05/04，2025/05/13，2025/05/22，2025/06/05，2025/06/07，2025/08/29，2025/09/07，2025/09/11，2025/10/10，2025/11/09，2026/01/01，2026/06/20，2026/07/30</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23</t>
+          <t>2025/03/10，2025/03/14，2025/05/09，2025/06/03，2025/07/18，2025/07/22，2025/08/28，2025/09/30，2025/11/27，2026/03/27，2026/04/01，2026/06/23，2026/07/31</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07</t>
+          <t>2025/03/12，2025/04/29，2025/06/02，2025/09/21，2025/10/07，2025/10/28，2025/12/13，2026/01/01，2026/02/14，2026/05/06，2026/05/23，2026/07/07，2026/08/02</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19</t>
+          <t>2025/03/12，2025/04/04，2025/04/19，2025/04/26，2025/06/03，2025/06/19，2025/06/26，2025/07/10，2025/07/17，2025/07/31，2025/08/24，2025/08/30，2025/09/13，2025/09/18，2025/09/19，2025/09/22，2025/09/27，2025/10/01，2025/10/24，2025/10/31，2025/11/04，2025/11/07，2025/11/09，2025/12/04，2026/01/09，2026/01/19，2026/01/21，2026/01/25，2026/03/04，2026/03/07，2026/03/14，2026/06/06，2026/06/19，2026/08/05，2026/08/05</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09</t>
+          <t>2025/03/12，2025/04/07，2025/04/18，2025/05/10，2025/05/15，2025/05/29，2025/06/03，2025/06/16，2025/07/08，2025/07/08，2025/08/01，2025/09/04，2025/09/28，2025/10/25，2025/10/28，2025/11/03，2025/12/02，2025/12/04，2025/12/12，2026/01/05，2026/01/14，2026/02/19，2026/03/04，2026/03/31，2026/04/12，2026/04/29，2026/05/15，2026/06/12，2026/06/23，2026/07/09，2026/08/11</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025/03/13，2025/04/13，2025/04/19，2025/05/06，2025/06/03，2025/08/28，2025/09/17，2025/10/10，2025/11/17，2025/11/22，2025/12/24，2026/01/15，2026/01/29，2026/03/19，2026/05/15</t>
+          <t>2025/03/13，2025/04/13，2025/04/19，2025/05/06，2025/06/03，2025/08/28，2025/09/17，2025/10/10，2025/11/17，2025/11/22，2025/12/24，2026/01/15，2026/01/29，2026/03/19，2026/05/15，2026/08/08</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09</t>
+          <t>2025/03/14，2025/05/20，2025/07/23，2025/11/28，2025/12/09，2026/07/31</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20</t>
+          <t>2025/03/14，2025/04/02，2025/05/10，2025/05/18，2025/05/23，2025/06/05，2025/06/08，2025/06/27，2025/09/03，2025/09/21，2025/10/30，2025/11/22，2025/12/09，2026/01/15，2026/02/19，2026/03/13，2026/03/15，2026/03/21，2026/06/14，2026/06/17，2026/07/20，2026/07/31</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09</t>
+          <t>2025/03/14，2025/03/28，2025/04/18，2025/09/20，2025/10/12，2025/10/22，2026/01/02，2026/01/30，2026/04/09，2026/07/31</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23</t>
+          <t>2025/03/14，2025/04/24，2025/05/25，2025/08/21，2025/09/10，2025/11/03，2025/11/24，2026/04/09，2026/04/14，2026/04/24，2026/05/23，2026/08/02</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025/03/14，2025/04/12，2025/05/20，2025/05/30，2025/06/27，2025/08/13，2025/09/11，2025/10/28，2025/12/20，2026/01/16，2026/04/17</t>
+          <t>2025/03/14，2025/04/12，2025/05/20，2025/05/30，2025/06/27，2025/08/13，2025/09/11，2025/10/28，2025/12/20，2026/01/16，2026/04/17，2026/08/08</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2025/03/15，2025/05/22，2025/06/10，2025/11/09，2025/11/14，2026/03/19，2026/06/15</t>
+          <t>2025/03/15，2025/05/22，2025/06/10，2025/11/09，2025/11/14，2026/03/19，2026/06/15，2026/08/02</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21</t>
+          <t>2025/03/17，2025/03/28，2025/04/15，2025/04/19，2025/04/25，2025/05/01，2025/05/18，2025/05/25，2025/05/29，2025/06/05，2025/06/12，2025/06/22，2025/07/03，2025/07/11，2025/07/18，2025/07/22，2025/07/31，2025/08/01，2025/08/02，2025/08/03，2025/08/12，2025/09/03，2025/09/11，2025/09/18，2025/09/26，2025/10/03，2025/10/09，2025/10/20，2025/11/12，2025/12/07，2025/12/23，2026/01/05，2026/01/21，2026/01/29，2026/02/09，2026/02/20，2026/02/23，2026/03/04，2026/03/06，2026/03/07，2026/04/11，2026/04/14，2026/04/29，2026/05/23，2026/07/03，2026/07/21，2026/08/11</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/03/27，2025/04/25，2025/05/01，2025/05/15，2025/06/10，2025/07/03，2025/09/11，2025/12/11，2026/01/09</t>
+          <t>2025/03/17，2025/03/27，2025/04/25，2025/05/01，2025/05/15，2025/06/10，2025/07/03，2025/09/11，2025/12/11，2026/01/09，2026/08/11</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09</t>
+          <t>2025/03/17，2025/04/17，2025/05/13，2025/05/23，2025/07/21，2025/07/29，2025/08/07，2025/09/30，2025/10/31，2025/12/09，2026/01/12，2026/04/26，2026/07/09，2026/08/02</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/05/17，2025/06/01，2025/09/21，2025/10/09，2025/11/26</t>
+          <t>2025/03/17，2025/05/17，2025/06/01，2025/09/21，2025/10/09，2025/11/26，2026/08/02</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26</t>
+          <t>2025/03/17，2025/04/29，2025/06/03，2025/07/24，2025/08/01，2025/08/03，2025/10/10，2025/11/09，2026/04/26，2026/08/02</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/12，2025/09/02，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15</t>
+          <t>2025/03/17，2025/06/05，2025/06/05，2025/06/23，2025/08/12，2025/09/12，2025/09/02，2025/11/09，2025/12/04，2026/01/01，2026/01/29，2026/04/09，2026/06/15，2026/08/05</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09</t>
+          <t>2025/03/18，2025/03/25，2025/04/02，2025/04/17，2025/05/01，2025/05/08，2025/05/10，2025/05/24，2025/05/29，2025/06/23，2025/06/27，2025/07/08，2025/07/28，2025/08/03，2025/09/08，2025/09/22，2025/10/03，2025/10/11，2025/10/16，2025/10/24，2025/11/18，2025/12/02，2025/12/17，2026/01/09，2026/01/15，2026/02/02，2026/02/14，2026/03/13，2026/03/25，2026/04/24，2026/05/23，2026/06/17，2026/07/05，2026/07/09，2026/07/31，2026/08/08</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08</t>
+          <t>2025/03/18，2025/03/25，2025/05/22，2025/07/10，2025/09/08，2025/10/09，2025/11/01，2026/01/15，2026/04/08，2026/8/16</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18</t>
+          <t>2025/03/19，2025/04/07，2025/04/21，2025/05/01，2025/05/10，2025/05/27，2025/06/09，2025/06/23，2025/06/26，2025/07/03，2025/09/15，2025/09/28，2025/10/01，2025/10/17，2026/01/03，2026/01/05，2026/01/30，2026/03/14，2026/03/31，2026/04/20，2026/05/01，2026/06/19，2026/06/30，2026/07/18，2026/08/03</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/07/07，2025/08/12，2025/08/26，2025/09/13，2025/09/17，2025/10/10，2025/11/21，2025/12/11，2026/01/02，2026/01/15，2026/01/28，2026/02/19，2026/03/05，2026/04/09，2026/06/06，2026/06/20</t>
+          <t>2025/03/19，2025/07/07，2025/08/12，2025/08/26，2025/09/13，2025/09/17，2025/10/10，2025/11/21，2025/12/11，2026/01/02，2026/01/15，2026/01/28，2026/02/19，2026/03/05，2026/04/09，2026/06/06，2026/06/20，2026/07/31，2026/07/31</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/04/11，2025/05/19，2025/05/23，2025/06/12，2025/06/23，2025/07/20，2025/08/19，2025/09/21，2025/10/07，2025/10/20，2025/10/28，2025/11/09，2025/11/24，2025/12/16，2025/12/24，2025/12/26，2026/05/23</t>
+          <t>2025/03/19，2025/03/28，2025/04/11，2025/05/19，2025/05/23，2025/06/12，2025/06/23，2025/07/20，2025/08/19，2025/09/21，2025/10/07，2025/10/20，2025/10/28，2025/11/09，2025/11/24，2025/12/16，2025/12/24，2025/12/26，2026/05/23，2026/07/30</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19</t>
+          <t>2025/03/19，2025/03/28，2025/03/29，2025/04/11，2025/05/08，2025/05/22，2025/05/25，2025/05/29，2025/06/15，2025/07/14，2025/08/21，2025/09/26，2025/10/03，2025/11/19，2025/11/26，2026/01/01，2026/01/09，2026/03/22，2026/04/09，2026/04/20，2026/05/25，2026/06/10，2026/06/19，2026/08/11</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/06/03</t>
+          <t>2025/03/20，2025/06/03，2026/8/16</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/04/17，2025/04/21，2025/04/29，2025/05/08，2025/05/30，2025/06/13，2025/06/26，2025/07/08，2025/07/18，2025/08/22，2025/09/05，2025/09/28，2025/10/25，2025/11/10，2025/11/27，2025/12/08，2025/12/24，2026/01/28，2026/04/22，2026/05/05，2026/06/14，2026/07/22</t>
+          <t>2025/03/20，2025/04/04，2025/04/17，2025/04/21，2025/04/29，2025/05/08，2025/05/30，2025/06/13，2025/06/26，2025/07/08，2025/07/18，2025/08/22，2025/09/05，2025/09/28，2025/10/25，2025/11/10，2025/11/27，2025/12/08，2025/12/24，2026/01/28，2026/04/22，2026/05/05，2026/06/14，2026/07/22，2026/07/31</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02</t>
+          <t>2025/03/20，2025/04/04，2025/05/19，2025/06/08，2025/06/12，2025/07/13，2025/08/28，2025/09/26，2025/10/25，2025/11/19，2025/11/27，2026/01/22，2026/01/25，2026/02/19，2026/05/20，2026/07/02，2026/08/02，2026/08/09</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04</t>
+          <t>2025/03/20，2025/04/04，2025/05/03，2025/05/22，2025/06/05，2025/07/25，2025/08/26，2025/08/16，2025/09/21，2025/10/03，2025/11/12，2025/12/08，2026/01/23，2026/01/26，2026/02/07，2026/02/10，2026/02/23，2026/02/25，2026/02/27，2026/03/01，2026/03/04，2026/03/13，2026/03/24，2026/03/28，2026/03/29，2026/04/27，2026/05/02，2026/06/18，2026/07/04，2026/07/31</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/06/26，2026/04/14，2026/06/10</t>
+          <t>2025/03/20，2025/06/26，2026/04/14，2026/06/10，2026/08/02</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28</t>
+          <t>2025/03/20，2025/04/17，2025/05/01，2025/05/03，2025/05/18，2025/05/22，2025/05/29，2025/06/06，2025/06/13，2025/06/30，2025/07/09，2025/07/27，2025/08/23，2025/09/03，2025/09/11，2025/10/11，2025/10/17，2025/12/24，2026/01/16，2026/02/07，2026/03/28，2026/8/16</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2025/03/21，2026/06/12</t>
+          <t>2025/03/21，2026/06/12，2026/08/02</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09</t>
+          <t>2025/03/21，2025/04/06，2025/04/18，2025/04/25，2025/05/27，2025/07/11，2025/07/24，2025/08/09，2025/09/15，2025/09/21，2025/10/11，2025/10/24，2025/11/03，2025/11/22，2026/01/22，2026/02/19，2026/03/15，2026/04/02，2026/05/01，2026/05/23，2026/07/09，2026/08/11</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17</t>
+          <t>2025/03/21，2025/05/09，2025/05/30，2025/07/22，2025/09/28，2025/11/18，2025/12/08，2026/02/18，2026/03/06，2026/03/13，2026/03/14，2026/03/31，2026/05/01，2026/06/28，2026/07/17，2026/08/02</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25</t>
+          <t>2025/03/21，2025/04/28，2025/05/13，2025/06/07，2025/06/21，2025/08/28，2025/09/29，2025/10/24，2025/11/14，2025/12/17，2026/03/25，2026/08/07</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22</t>
+          <t>2025/03/22，2025/04/05，2025/04/17，2025/04/21，2025/04/22，2025/04/25，2025/05/08，2025/05/15，2025/05/25，2025/05/29，2025/06/03，2025/06/13，2025/06/23，2025/07/06，2025/07/15，2025/08/03，2025/08/16，2025/09/03，2025/09/10，2025/09/30，2025/10/16，2025/10/22，2025/10/30，2025/11/18，2025/12/02，2025/12/05，2025/12/30，2026/01/23，2026/01/29，2026/02/23，2026/03/17，2026/03/22，2026/04/19，2026/05/10，2026/06/12，2026/07/22，2026/08/08</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28</t>
+          <t>2025/03/24，2025/04/06，2025/04/15，2025/04/27，2025/05/05，2025/05/22，2025/05/30，2025/06/02，2025/06/06，2025/06/09，2025/06/21，2025/06/27，2025/08/25，2025/09/06，2025/09/10，2025/09/19，2025/10/05，2025/11/21，2025/12/07，2026/01/17，2026/02/14，2026/04/09，2026/05/20，2026/06/19，2026/06/28，2026/07/31</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2025/03/25，2025/04/11，2025/04/20，2025/05/17，2025/05/22，2025/06/07，2025/06/21，2025/07/06，2025/07/28，2025/09/03，2025/09/14，2025/11/09，2026/01/01，2026/02/07，2026/03/25，2026/04/26，2026/06/23</t>
+          <t>2025/03/25，2025/04/11，2025/04/20，2025/05/17，2025/05/22，2025/06/07，2025/06/21，2025/07/06，2025/07/28，2025/09/03，2025/09/14，2025/11/09，2026/01/01，2026/02/07，2026/03/25，2026/04/26，2026/06/23，2026/07/31，2026/07/31</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/28，2025/04/29，2025/05/12，2025/06/06，2025/06/16，2025/07/24，2025/08/01，2025/09/05，2025/09/26，2025/10/28，2025/12/05，2026/01/09，2026/02/19，2026/03/22，2026/04/16</t>
+          <t>2025/03/27，2025/04/03，2025/04/15，2025/04/28，2025/04/29，2025/05/12，2025/06/06，2025/06/16，2025/07/24，2025/08/01，2025/09/05，2025/09/26，2025/10/28，2025/12/05，2026/01/09，2026/02/19，2026/03/22，2026/04/16，2026/08/08</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12</t>
+          <t>2025/03/27，2025/05/06，2025/05/16，2025/06/10，2025/07/03，2025/07/13，2025/08/22，2025/10/05，2025/10/23，2025/11/10，2026/01/16，2026/02/02，2026/02/07，2026/03/31，2026/04/17，2026/04/29，2026/05/15，2026/05/19，2026/06/12，2026/08/07</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09</t>
+          <t>2025/03/28，2025/07/25，2025/07/26，2025/08/16，2025/09/05，2025/09/29，2025/10/31，2025/12/24，2026/01/16，2026/06/06，2026/07/09，2026/08/08</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15</t>
+          <t>2025/03/28，2025/06/07，2025/06/13，2025/06/23，2025/07/20，2025/10/24，2025/11/09，2026/01/09，2026/02/19，2026/05/10，2026/07/10，2026/07/15，2026/07/31</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/03，2025/05/26，2025/11/09，2026/05/06，2026/06/10</t>
+          <t>2025/03/28，2025/05/03，2025/05/26，2025/11/09，2026/05/06，2026/06/10，2026/08/02</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20</t>
+          <t>2025/03/28，2025/04/04，2025/04/22，2025/04/29，2025/05/10，2025/05/18，2025/06/02，2025/07/10，2025/08/19，2025/09/10，2025/09/15，2025/10/07，2025/10/26，2025/10/30，2025/11/07，2025/11/24，2025/12/05，2026/01/23，2026/03/09，2026/03/25，2026/06/20，2026/8/16</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/05/09，2025/06/07，2025/07/31，2025/08/13，2025/08/21，2025/12/16，2026/01/19，2026/05/04</t>
+          <t>2025/03/28，2025/05/09，2025/06/07，2025/07/31，2025/08/13，2025/08/21，2025/12/16，2026/01/19，2026/05/04，2026/07/31</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02</t>
+          <t>2025/03/28，2025/04/24，2025/06/02，2025/06/27，2025/09/21，2025/10/07，2025/11/13，2025/12/02，2026/08/01</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10</t>
+          <t>2025/03/29，2025/04/18，2025/04/24，2025/05/27，2025/06/20，2025/07/03，2025/07/18，2025/08/02，2025/08/24，2025/10/03，2025/10/25，2025/10/28，2025/11/03，2025/11/09，2025/12/23，2026/04/08，2026/04/24，2026/05/21，2026/06/10，2026/08/02</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23</t>
+          <t>2025/03/29，2025/04/05，2025/05/30，2025/06/28，2025/09/17，2025/09/18，2025/11/07，2025/11/13，2025/12/02，2026/01/14，2026/01/24，2026/03/07，2026/03/15，2026/04/24，2026/06/06，2026/06/23，2026/08/05，2026/08/05</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2025/03/29，2025/08/12，2025/10/20，2025/11/14，2025/12/02，2026/01/10，2026/02/09，2026/04/18，2026/06/20</t>
+          <t>2025/03/29，2025/08/12，2025/10/20，2025/11/14，2025/12/02，2026/01/10，2026/02/09，2026/04/18，2026/06/20，2026/08/02</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/07/13，2025/10/20</t>
+          <t>2025/03/30，2025/07/13，2025/10/20，2026/8/16</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22</t>
+          <t>2025/03/30，2025/04/27，2025/05/19，2025/05/31，2025/08/30，2025/09/02，2025/11/18，2026/04/22，2026/07/31</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20</t>
+          <t>2025/04/01，2025/04/17，2025/05/25，2025/07/17，2025/07/21，2025/09/14，2025/10/11，2025/12/02，2026/04/08，2026/05/01，2026/06/10，2026/06/20，2026/08/02</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2025/04/02，2025/05/13，2025/05/29，2025/09/04，2025/09/21，2025/10/22，2026/01/01，2026/01/15，2026/05/05</t>
+          <t>2025/04/02，2025/05/13，2025/05/29，2025/09/04，2025/09/21，2025/10/22，2026/01/01，2026/01/15，2026/05/05，2026/8/16</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22</t>
+          <t>2025/04/03，2025/04/19，2025/06/16，2025/07/13，2025/07/18，2025/09/19，2025/10/01，2026/01/25，2026/02/14，2026/04/09，2026/06/20，2026/07/22，2026/08/08</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2025/04/03，2025/04/27</t>
+          <t>2025/04/03，2025/04/27，2026/8/16</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28</t>
+          <t>2025/04/04，2025/07/13，2025/07/18，2025/11/03，2025/11/28，2026/8/16</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -12529,7 +12529,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>BV1pmh8zDEsy</t>
+        </is>
+      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>动漫</t>
@@ -12595,7 +12599,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2025/04/06，2025/04/19，2025/05/03，2025/08/01，2025/10/31，2025/12/15，2026/02/22，2026/02/23，2026/04/17</t>
+          <t>2025/04/06，2025/04/19，2025/05/03，2025/08/01，2025/10/31，2025/12/15，2026/02/22，2026/02/23，2026/04/17，2026/07/31</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -12606,7 +12610,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -12795,7 +12799,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25</t>
+          <t>2025/04/07，2025/05/19，2025/10/01，2025/10/31，2026/01/05，2026/03/25，2026/03/25，2026/08/02</t>
         </is>
       </c>
       <c r="F306" t="inlineStr"/>
@@ -12806,7 +12810,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -12835,7 +12839,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20</t>
+          <t>2025/04/07，2025/04/17，2025/04/19，2025/04/27，2025/04/29，2025/05/20，2025/06/14，2025/07/23，2025/08/29，2025/10/01，2025/11/18，2026/01/03，2026/01/22，2026/02/14，2026/05/20，2026/08/08</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -12846,7 +12850,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12915,7 +12919,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20</t>
+          <t>2025/04/08，2025/04/21，2025/04/26，2025/05/10，2025/05/13，2025/05/19，2025/05/30，2025/06/05，2025/06/13，2025/07/05，2025/07/08，2025/07/13，2025/07/15，2025/08/30，2025/09/11，2025/09/18，2025/09/24，2025/09/30，2025/10/30，2025/11/03，2025/11/09，2025/11/26，2025/12/09，2026/01/23，2026/03/13，2026/03/25，2026/04/08，2026/05/23，2026/06/20，2026/08/02</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -12926,7 +12930,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -13009,7 +13013,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>BV1KmdUYhEJu</t>
+        </is>
+      </c>
       <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
@@ -13031,7 +13039,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/05/12，2025/08/22，2025/10/01，2025/10/17，2026/02/23，2026/03/06，2026/04/22，2026/06/10</t>
+          <t>2025/04/08，2025/05/12，2025/08/22，2025/10/01，2025/10/17，2026/02/23，2026/03/06，2026/04/22，2026/06/10，2026/08/05</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
@@ -13042,7 +13050,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -13071,7 +13079,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06</t>
+          <t>2025/04/08，2025/04/13，2025/04/22，2025/05/01，2025/05/22，2025/06/08，2025/06/29，2025/08/30，2025/09/15，2025/10/10，2025/11/09，2025/12/05，2025/12/19，2025/12/26，2026/01/10，2026/01/19，2026/02/10，2026/03/24，2026/04/18，2026/06/06，2026/08/07</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -13082,7 +13090,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -13125,7 +13133,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>BV1Wvd4YFEz4</t>
+        </is>
+      </c>
       <c r="J314" t="inlineStr"/>
     </row>
     <row r="315">
@@ -13357,7 +13369,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>BV1JDoNYYE5V</t>
+        </is>
+      </c>
       <c r="J320" t="inlineStr">
         <is>
           <t>动漫</t>
@@ -13459,7 +13475,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/12，2025/09/11，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15</t>
+          <t>2025/04/11，2025/05/25，2025/05/29，2025/06/28，2025/07/03，2025/08/13，2025/08/25，2025/09/12，2025/09/11，2025/09/28，2025/10/11，2025/10/30，2025/11/21，2026/01/29，2026/02/10，2026/03/09，2026/03/24，2026/04/19，2026/05/21，2026/06/15，2026/08/02</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -13470,7 +13486,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13513,7 +13529,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>BV1YmGizgEFL</t>
+        </is>
+      </c>
       <c r="J324" t="inlineStr"/>
     </row>
     <row r="325">
@@ -13585,7 +13605,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>BV1MeGdzDEbU</t>
+        </is>
+      </c>
       <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
@@ -13701,7 +13725,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>BV1V1GizrEjQ</t>
+        </is>
+      </c>
       <c r="J329" t="inlineStr"/>
     </row>
     <row r="330">
@@ -14219,7 +14247,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2025/04/14，2025/10/31</t>
+          <t>2025/04/14，2025/10/31，2026/08/11</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -14230,7 +14258,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -14827,7 +14855,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05</t>
+          <t>2025/04/17，2025/04/29，2025/05/22，2025/05/25，2025/05/31，2025/08/29，2025/09/20，2025/10/09，2025/10/30，2025/12/11，2026/02/18，2026/05/20，2026/07/05，2026/07/31</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -14838,7 +14866,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -14921,7 +14949,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>BV1KWVyzXEEL</t>
+        </is>
+      </c>
       <c r="J359" t="inlineStr"/>
     </row>
     <row r="360">
@@ -15139,7 +15171,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2025/04/18，2025/05/18，2025/06/19，2025/07/15，2025/08/01，2025/09/17，2025/10/28，2025/11/13，2025/11/14，2026/02/10，2026/02/27</t>
+          <t>2025/04/18，2025/05/18，2025/06/19，2025/07/15，2025/08/01，2025/09/17，2025/10/28，2025/11/13，2025/11/14，2026/02/10，2026/02/27，2026/08/02</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -15150,7 +15182,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -15223,7 +15255,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25</t>
+          <t>2025/04/19，2025/07/14，2025/09/12，2025/10/03，2025/10/30，2026/01/10，2026/03/22，2026/04/24，2026/05/25，2026/08/11</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -15234,7 +15266,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -15343,7 +15375,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/02，2026/01/26，2026/06/28</t>
+          <t>2025/04/19，2025/05/30，2025/07/23，2025/08/23，2025/09/11，2025/12/02，2026/01/26，2026/06/28，2026/08/07</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -15354,7 +15386,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -15671,7 +15703,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2025/04/22，2025/04/29，2025/05/03，2025/05/03，2025/06/03，2025/09/02，2025/10/10，2025/10/20，2025/10/31，2026/02/07，2026/03/13</t>
+          <t>2025/04/22，2025/04/29，2025/05/03，2025/05/03，2025/06/03，2025/09/02，2025/10/10，2025/10/20，2025/10/31，2026/02/07，2026/03/13，2026/08/11</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -15682,7 +15714,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -16323,7 +16355,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23</t>
+          <t>2025/04/25，2025/06/19，2025/06/23，2025/08/12，2025/10/09，2025/11/03，2025/12/30，2026/01/09，2026/04/01，2026/05/23，2026/07/31</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -16334,7 +16366,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -16617,7 +16649,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>BV15Bu3zbEcP</t>
+        </is>
+      </c>
       <c r="J402" t="inlineStr"/>
     </row>
     <row r="403">
@@ -16803,7 +16839,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14</t>
+          <t>2025/04/28，2025/11/18，2026/02/14，2026/04/09，2026/05/16，2026/06/14，2026/08/02</t>
         </is>
       </c>
       <c r="F407" t="inlineStr"/>
@@ -16814,7 +16850,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -16933,7 +16969,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>BV1P8GSzFEa7</t>
+        </is>
+      </c>
       <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
@@ -17009,7 +17049,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr"/>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>BV12dEjz9Etf</t>
+        </is>
+      </c>
       <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
@@ -17125,7 +17169,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>BV116Gdz2ELk</t>
+        </is>
+      </c>
       <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
@@ -17147,7 +17195,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09</t>
+          <t>2025/05/03，2025/08/28，2025/09/11，2025/10/20，2025/12/09，2026/8/16</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -17158,7 +17206,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -17601,7 +17649,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>BV1ps55zYEGz</t>
+        </is>
+      </c>
       <c r="J427" t="inlineStr"/>
     </row>
     <row r="428">
@@ -17779,7 +17831,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29</t>
+          <t>2025/05/10，2025/06/10，2025/08/03，2025/09/05，2026/04/29，2026/08/07</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -17790,7 +17842,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -18139,7 +18191,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03</t>
+          <t>2025/05/17，2025/05/31，2025/06/15，2025/07/23，2025/09/11，2026/01/01，2026/02/10，2026/02/22，2026/03/12，2026/04/05，2026/05/03，2026/05/24，2026/07/03，2026/08/07</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -18150,7 +18202,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -18233,7 +18285,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>BV1tMNXzxEwY</t>
+        </is>
+      </c>
       <c r="J443" t="inlineStr"/>
     </row>
     <row r="444">
@@ -18375,7 +18431,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09</t>
+          <t>2025/05/18，2025/06/07，2025/06/10，2025/06/12，2025/06/13，2025/06/17，2025/06/23，2025/07/08，2025/07/13，2025/07/20，2025/07/31，2025/09/17，2025/09/26，2025/10/07，2025/11/13，2025/12/17，2026/01/02，2026/03/17，2026/04/29，2026/05/10，2026/07/09，2026/07/31，2026/08/11</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -18386,7 +18442,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -18455,7 +18511,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/12/16，2025/12/24</t>
+          <t>2025/05/19，2025/12/16，2025/12/24，2026/8/16</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -18466,7 +18522,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -18495,7 +18551,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23</t>
+          <t>2025/05/19，2025/07/13，2025/08/21，2025/12/17，2026/05/23，2026/08/11</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -18506,7 +18562,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -18549,7 +18605,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I451" t="inlineStr"/>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>BV1EdEQzrEyw</t>
+        </is>
+      </c>
       <c r="J451" t="inlineStr"/>
     </row>
     <row r="452">
@@ -18575,7 +18635,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2025/05/19，2025/07/13，2025/10/30，2025/10/31，2025/12/24，2026/01/09，2026/04/09，2026/05/07</t>
+          <t>2025/05/19，2025/07/13，2025/10/30，2025/10/31，2025/12/24，2026/01/09，2026/04/09，2026/05/07，2026/07/31</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -18586,7 +18646,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -18615,7 +18675,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/31，2025/06/07，2025/06/10，2025/08/02，2025/10/07，2025/12/06，2026/03/22，2026/05/01</t>
+          <t>2025/05/22，2025/05/31，2025/06/07，2025/06/10，2025/08/02，2025/10/07，2025/12/06，2026/03/22，2026/05/01，2026/8/16</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -18626,7 +18686,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -18819,7 +18879,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>2025/05/22</t>
+          <t>2025/05/22，2026/07/30</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -18830,7 +18890,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -18863,7 +18923,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15</t>
+          <t>2025/05/22，2025/05/25，2025/05/31，2025/06/03，2025/06/10，2025/06/13，2025/06/23，2025/07/23，2025/07/24，2025/07/27，2025/08/22，2025/09/06，2025/10/28，2025/10/30，2025/11/10，2025/11/19，2026/01/05，2026/02/02，2026/03/17，2026/05/10，2026/06/14，2026/06/15，2026/07/31</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -18874,7 +18934,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -19041,7 +19101,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>BV1ihjpzEEWS</t>
+        </is>
+      </c>
       <c r="J463" t="inlineStr"/>
     </row>
     <row r="464">
@@ -19077,7 +19141,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I464" t="inlineStr"/>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>BV1ofuNzSEmK</t>
+        </is>
+      </c>
       <c r="J464" t="inlineStr"/>
     </row>
     <row r="465">
@@ -19179,7 +19247,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08</t>
+          <t>2025/05/24，2025/07/13，2025/08/23，2025/09/29，2025/12/24，2025/12/30，2026/01/28，2026/04/08，2026/8/16</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -19190,7 +19258,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -19313,7 +19381,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>BV1CZj3zcEhL</t>
+        </is>
+      </c>
       <c r="J470" t="inlineStr"/>
     </row>
     <row r="471">
@@ -19349,7 +19421,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I471" t="inlineStr"/>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>BV1nF33zGE8P</t>
+        </is>
+      </c>
       <c r="J471" t="inlineStr"/>
     </row>
     <row r="472">
@@ -19465,7 +19541,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>BV1CN7pzFEVF</t>
+        </is>
+      </c>
       <c r="J474" t="inlineStr"/>
     </row>
     <row r="475">
@@ -19487,7 +19567,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/08/23，2025/10/11</t>
+          <t>2025/05/30，2025/08/23，2025/10/11，2026/8/16</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -19498,7 +19578,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -19541,7 +19621,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>BV1MF7PzDESp</t>
+        </is>
+      </c>
       <c r="J476" t="inlineStr"/>
     </row>
     <row r="477">
@@ -19563,7 +19647,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/07/13，2025/10/31，2026/03/05</t>
+          <t>2025/05/30，2025/07/13，2025/10/31，2026/03/05，2026/08/08</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -19574,7 +19658,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -19683,7 +19767,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28</t>
+          <t>2025/05/30，2025/05/31，2025/05/31，2025/06/02，2025/06/03，2025/06/05，2025/06/19，2025/06/26，2025/07/03，2025/07/14，2025/08/02，2025/08/24，2025/09/03，2025/09/18，2025/10/07，2025/11/19，2025/12/11，2026/01/10，2026/01/22，2026/03/25，2026/06/28，2026/08/03</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -19694,7 +19778,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -19723,7 +19807,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2025/05/31，2025/06/02，2025/06/23，2025/09/15，2025/09/27，2025/10/17</t>
+          <t>2025/05/31，2025/06/02，2025/06/23，2025/09/15，2025/09/27，2025/10/17，2026/8/16</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -19734,7 +19818,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -19777,7 +19861,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I482" t="inlineStr"/>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>BV1Ey7NzzEcC</t>
+        </is>
+      </c>
       <c r="J482" t="inlineStr"/>
     </row>
     <row r="483">
@@ -19813,7 +19901,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I483" t="inlineStr"/>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>BV1qm7NzqEAT</t>
+        </is>
+      </c>
       <c r="J483" t="inlineStr"/>
     </row>
     <row r="484">
@@ -19853,7 +19945,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I484" t="inlineStr"/>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>BV16WypB3EX6</t>
+        </is>
+      </c>
       <c r="J484" t="inlineStr"/>
     </row>
     <row r="485">
@@ -20101,7 +20197,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I490" t="inlineStr"/>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>BV1ny7rzLE4i</t>
+        </is>
+      </c>
       <c r="J490" t="inlineStr"/>
     </row>
     <row r="491">
@@ -20285,7 +20385,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I495" t="inlineStr"/>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>BV1r37mzwE3A</t>
+        </is>
+      </c>
       <c r="J495" t="inlineStr"/>
     </row>
     <row r="496">
@@ -20401,7 +20505,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>BV1YY7SzREB6</t>
+        </is>
+      </c>
       <c r="J498" t="inlineStr"/>
     </row>
     <row r="499">
@@ -20437,7 +20545,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I499" t="inlineStr"/>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>BV1zp7SzaEq7</t>
+        </is>
+      </c>
       <c r="J499" t="inlineStr"/>
     </row>
     <row r="500">
@@ -20473,7 +20585,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>BV1jV7XzKEk1</t>
+        </is>
+      </c>
       <c r="J500" t="inlineStr"/>
     </row>
     <row r="501">
@@ -20589,7 +20705,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr"/>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>BV16xwozUELq</t>
+        </is>
+      </c>
       <c r="J503" t="inlineStr"/>
     </row>
     <row r="504">
@@ -20701,7 +20821,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I506" t="inlineStr"/>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>BV15gTjzKEAJ</t>
+        </is>
+      </c>
       <c r="J506" t="inlineStr"/>
     </row>
     <row r="507">
@@ -20737,7 +20861,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>BV1FaT2zYEEQ</t>
+        </is>
+      </c>
       <c r="J507" t="inlineStr"/>
     </row>
     <row r="508">
@@ -20773,7 +20901,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>BV1joT1z4E8u</t>
+        </is>
+      </c>
       <c r="J508" t="inlineStr"/>
     </row>
     <row r="509">
@@ -20875,7 +21007,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>2025/06/09，2025/09/26，2025/10/17，2025/10/25，2026/05/01</t>
+          <t>2025/06/09，2025/09/26，2025/10/17，2025/10/25，2026/05/01，2026/08/02</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -20886,7 +21018,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -21159,7 +21291,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09</t>
+          <t>2025/06/15，2025/06/15，2025/06/16，2025/06/17，2025/06/19，2025/06/27，2025/07/03，2025/07/05，2025/07/11，2025/07/25，2025/08/01，2025/08/03，2025/08/13，2025/09/03，2025/09/12，2025/09/24，2025/10/07，2025/10/24，2025/11/13，2025/12/02，2025/12/09，2025/12/16，2025/12/26，2026/01/05，2026/01/15，2026/01/28，2026/03/06，2026/04/22，2026/05/10，2026/05/15，2026/06/19，2026/07/09，2026/07/31</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -21170,7 +21302,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -21213,7 +21345,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I519" t="inlineStr"/>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>BV11DNtzSEY2</t>
+        </is>
+      </c>
       <c r="J519" t="inlineStr"/>
     </row>
     <row r="520">
@@ -21369,7 +21505,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I523" t="inlineStr"/>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>BV1K1N5z2EHA</t>
+        </is>
+      </c>
       <c r="J523" t="inlineStr"/>
     </row>
     <row r="524">
@@ -21605,7 +21745,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I529" t="inlineStr"/>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>BV1tH3FztEpR</t>
+        </is>
+      </c>
       <c r="J529" t="inlineStr"/>
     </row>
     <row r="530">
@@ -21627,7 +21771,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28</t>
+          <t>2025/06/19，2025/07/14，2025/07/17，2025/07/28，2025/08/03，2025/08/08，2025/08/22，2025/09/17，2025/09/26，2025/09/30，2025/10/12，2025/10/16，2025/11/07，2025/11/21，2025/12/02，2025/12/17，2026/01/01，2026/01/05，2026/01/14，2026/01/22，2026/01/24，2026/02/02，2026/03/05，2026/03/15，2026/04/01，2026/05/04，2026/05/25，2026/06/20，2026/07/05，2026/07/18，2026/07/28，2026/08/11</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -21638,7 +21782,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21831,7 +21975,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22</t>
+          <t>2025/06/20，2025/06/21，2025/07/08，2025/07/13，2025/07/18，2025/07/28，2025/08/01，2025/08/03，2025/08/04，2025/08/16，2025/09/03，2025/09/13，2025/09/19，2025/10/23，2025/10/28，2025/11/10，2025/11/13，2025/11/18，2025/12/11，2025/12/16，2026/02/18，2026/03/09，2026/04/16，2026/04/24，2026/05/15，2026/05/23，2026/06/12，2026/07/22，2026/08/11</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -21842,7 +21986,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -21925,7 +22069,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I537" t="inlineStr"/>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>BV1BCMp6DEtt</t>
+        </is>
+      </c>
       <c r="J537" t="inlineStr"/>
     </row>
     <row r="538">
@@ -21961,7 +22109,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I538" t="inlineStr"/>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>BV1ZFKhzLEqz</t>
+        </is>
+      </c>
       <c r="J538" t="inlineStr"/>
     </row>
     <row r="539">
@@ -21997,7 +22149,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I539" t="inlineStr"/>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>BV1XbK8ziE7s</t>
+        </is>
+      </c>
       <c r="J539" t="inlineStr"/>
     </row>
     <row r="540">
@@ -22019,7 +22175,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>2025/06/23，2025/10/19，2026/01/19</t>
+          <t>2025/06/23，2025/10/19，2026/01/19，2026/8/16</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -22030,7 +22186,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -22189,7 +22345,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I544" t="inlineStr"/>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>BV178KfzbEJ6</t>
+        </is>
+      </c>
       <c r="J544" t="inlineStr"/>
     </row>
     <row r="545">
@@ -22215,7 +22375,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17</t>
+          <t>2025/06/26，2025/06/27，2025/07/14，2025/07/17，2025/08/23，2025/09/21，2025/10/28，2025/11/10，2026/01/14，2026/01/22，2026/02/19，2026/03/13，2026/04/12，2026/05/10，2026/06/17，2026/08/08</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -22226,7 +22386,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -22299,7 +22459,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>2025/06/27，2025/09/08，2025/10/13，2025/10/16，2026/01/24，2026/02/09，2026/03/06，2026/03/22，2026/04/11，2026/04/30，2026/05/26，2026/06/18</t>
+          <t>2025/06/27，2025/09/08，2025/10/13，2025/10/16，2026/01/24，2026/02/09，2026/03/06，2026/03/22，2026/04/11，2026/04/30，2026/05/26，2026/06/18，2026/08/03</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -22314,7 +22474,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -22405,7 +22565,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>BV17iK6zkEYv</t>
+        </is>
+      </c>
       <c r="J549" t="inlineStr"/>
     </row>
     <row r="550">
@@ -22481,7 +22645,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I551" t="inlineStr"/>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>BV1Fv3Xz8ETi</t>
+        </is>
+      </c>
       <c r="J551" t="inlineStr"/>
     </row>
     <row r="552">
@@ -22543,7 +22711,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26</t>
+          <t>2025/06/29，2025/07/03，2025/07/14，2025/09/17，2025/11/13，2025/11/27，2025/12/16，2026/05/26，2026/8/16</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -22554,7 +22722,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -22583,7 +22751,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>2025/06/29</t>
+          <t>2025/06/29，2026/08/11</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -22594,10 +22762,14 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I554" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>BV1KBgCzkELn</t>
+        </is>
+      </c>
       <c r="J554" t="inlineStr"/>
     </row>
     <row r="555">
@@ -22633,7 +22805,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I555" t="inlineStr"/>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>BV158yXBUENQ</t>
+        </is>
+      </c>
       <c r="J555" t="inlineStr"/>
     </row>
     <row r="556">
@@ -22669,7 +22845,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr"/>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>BV1MegCzLEbb</t>
+        </is>
+      </c>
       <c r="J556" t="inlineStr"/>
     </row>
     <row r="557">
@@ -22705,7 +22885,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I557" t="inlineStr"/>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>BV14v3PzNEcG</t>
+        </is>
+      </c>
       <c r="J557" t="inlineStr"/>
     </row>
     <row r="558">
@@ -22741,7 +22925,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I558" t="inlineStr"/>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>BV1pHGFzHEHx</t>
+        </is>
+      </c>
       <c r="J558" t="inlineStr"/>
     </row>
     <row r="559">
@@ -22777,7 +22965,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I559" t="inlineStr"/>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>BV1ergkzDEuP</t>
+        </is>
+      </c>
       <c r="J559" t="inlineStr"/>
     </row>
     <row r="560">
@@ -22889,7 +23081,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I562" t="inlineStr"/>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>BV1G8g1zdELq</t>
+        </is>
+      </c>
       <c r="J562" t="inlineStr"/>
     </row>
     <row r="563">
@@ -22965,7 +23161,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr"/>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>BV1Bm3izjEJZ</t>
+        </is>
+      </c>
       <c r="J564" t="inlineStr"/>
     </row>
     <row r="565">
@@ -23637,7 +23837,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I581" t="inlineStr"/>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>BV1mvM9zqELY</t>
+        </is>
+      </c>
       <c r="J581" t="inlineStr"/>
     </row>
     <row r="582">
@@ -23833,7 +24037,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I586" t="inlineStr"/>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>BV1Jkgtz9ELP</t>
+        </is>
+      </c>
       <c r="J586" t="inlineStr"/>
     </row>
     <row r="587">
@@ -23895,7 +24103,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17</t>
+          <t>2025/07/17，2025/07/18，2025/07/24，2025/07/26，2025/07/31，2025/09/26，2025/09/29，2025/10/09，2025/12/26，2026/01/09，2026/04/02，2026/04/24，2026/05/22，2026/06/12，2026/06/17，2026/08/11</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -23906,7 +24114,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -24097,7 +24305,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I593" t="inlineStr"/>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>BV15Whuz2E7Y</t>
+        </is>
+      </c>
       <c r="J593" t="inlineStr"/>
     </row>
     <row r="594">
@@ -24133,7 +24345,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I594" t="inlineStr"/>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>BV1ktaZzwEZT</t>
+        </is>
+      </c>
       <c r="J594" t="inlineStr"/>
     </row>
     <row r="595">
@@ -24169,7 +24385,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I595" t="inlineStr"/>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>BV151gWzKEos</t>
+        </is>
+      </c>
       <c r="J595" t="inlineStr"/>
     </row>
     <row r="596">
@@ -24191,7 +24411,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>2025/07/23，2025/12/12，2026/02/25，2026/04/09，2026/04/14</t>
+          <t>2025/07/23，2025/12/12，2026/02/25，2026/04/09，2026/04/14，2026/08/02</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -24202,7 +24422,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -24329,7 +24549,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I599" t="inlineStr"/>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>BV1d68pzEEd3</t>
+        </is>
+      </c>
       <c r="J599" t="inlineStr"/>
     </row>
     <row r="600">
@@ -24485,7 +24709,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I603" t="inlineStr"/>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>BV12o8nzfEPr</t>
+        </is>
+      </c>
       <c r="J603" t="inlineStr"/>
     </row>
     <row r="604">
@@ -24561,7 +24789,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I605" t="inlineStr"/>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>BV1x6pgzLE5J</t>
+        </is>
+      </c>
       <c r="J605" t="inlineStr"/>
     </row>
     <row r="606">
@@ -24775,7 +25007,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10</t>
+          <t>2025/08/09，2025/08/10，2025/08/13，2025/08/22，2025/08/25，2025/09/03，2025/09/05，2025/09/20，2025/09/29，2025/10/05，2025/10/22，2025/11/14，2025/12/02，2025/12/17，2026/01/14，2026/02/02，2026/03/22，2026/04/01，2026/04/08，2026/05/15，2026/06/10，2026/07/31</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -24786,7 +25018,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -24804,7 +25036,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>原创曲（未命名）</t>
+          <t>优尼瓦思电力</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -24815,7 +25047,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>2025/08/09，2026/03/13，2026/03/27</t>
+          <t>2025/08/09，2026/03/13，2026/03/27，2026/08/02</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -24830,7 +25062,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -24895,7 +25127,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13</t>
+          <t>2025/08/12，2025/09/05，2025/09/05，2025/09/17，2025/09/24，2025/09/28，2025/10/01，2025/10/10，2025/10/17，2025/10/23，2025/11/01，2025/11/26，2025/12/30，2026/01/10，2026/02/18，2026/04/10，2026/04/23，2026/05/23，2026/06/18，2026/07/13，2026/08/07</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -24906,7 +25138,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -24935,7 +25167,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>2025/08/21，2026/01/16，2026/02/02，2026/03/17，2026/04/08，2026/06/14</t>
+          <t>2025/08/21，2026/01/16，2026/02/02，2026/03/17，2026/04/08，2026/06/14，2026/08/02</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -24946,7 +25178,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -25113,7 +25345,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I619" t="inlineStr"/>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>BV11Uerz8E9J</t>
+        </is>
+      </c>
       <c r="J619" t="inlineStr"/>
     </row>
     <row r="620">
@@ -25345,7 +25581,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I625" t="inlineStr"/>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>BV1FQYMz4E82</t>
+        </is>
+      </c>
       <c r="J625" t="inlineStr"/>
     </row>
     <row r="626">
@@ -25581,7 +25821,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr"/>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>BV1WhHrzfEYw</t>
+        </is>
+      </c>
       <c r="J631" t="inlineStr"/>
     </row>
     <row r="632">
@@ -25657,7 +25901,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr"/>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>BV17opgzeE7g</t>
+        </is>
+      </c>
       <c r="J633" t="inlineStr"/>
     </row>
     <row r="634">
@@ -26335,7 +26583,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>2025/09/15，2026/03/13</t>
+          <t>2025/09/15，2026/03/13，2026/08/02</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -26346,7 +26594,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -26647,7 +26895,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05</t>
+          <t>2025/09/21，2025/09/21，2025/09/22，2025/09/22，2025/09/24，2025/09/27，2025/09/29，2025/10/03，2025/10/05，2025/10/09，2025/10/18，2025/10/22，2025/10/26，2025/11/01，2025/11/09，2025/11/19，2025/11/22，2025/11/28，2025/12/08，2025/12/22，2026/01/05，2026/01/14，2026/01/22，2026/02/07，2026/02/10，2026/03/08，2026/03/22，2026/04/18，2026/05/01，2026/05/20，2026/06/10，2026/06/25，2026/07/05，2026/07/31</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -26658,7 +26906,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -26741,7 +26989,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr"/>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>BV1VenwzhEE1</t>
+        </is>
+      </c>
       <c r="J661" t="inlineStr"/>
     </row>
     <row r="662">
@@ -26835,7 +27087,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>2025/09/22，2025/10/09，2025/12/05</t>
+          <t>2025/09/22，2025/10/09，2025/12/05，2026/8/16</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -26846,10 +27098,14 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I664" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>BV1CJnKzxErq</t>
+        </is>
+      </c>
       <c r="J664" t="inlineStr"/>
     </row>
     <row r="665">
@@ -27019,7 +27275,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16</t>
+          <t>2025/09/24，2025/09/26，2025/09/28，2025/09/29，2025/10/01，2025/10/07，2025/10/10，2025/10/11，2025/10/17，2025/10/23，2025/10/28，2025/12/26，2026/02/05，2026/07/16，2026/07/31</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -27030,7 +27286,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -27291,7 +27547,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>2025/09/29，2025/09/30，2025/10/05，2025/10/07，2025/10/11，2025/10/16，2025/10/19，2025/10/22，2025/10/25，2025/11/19，2025/12/02，2025/12/11，2026/01/09，2026/01/14，2026/02/07，2026/03/22，2026/04/27，2026/05/25，2026/06/20，2026/07/09，2026/07/26</t>
+          <t>2025/09/29，2025/09/30，2025/10/05，2025/10/07，2025/10/11，2025/10/16，2025/10/19，2025/10/22，2025/10/25，2025/11/19，2025/12/02，2025/12/11，2026/01/09，2026/01/14，2026/02/07，2026/03/22，2026/04/27，2026/05/25，2026/06/20，2026/07/09，2026/07/26，2026/08/11</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -27302,7 +27558,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -27385,7 +27641,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr"/>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>BV1ZHn1ztEyz</t>
+        </is>
+      </c>
       <c r="J678" t="inlineStr"/>
     </row>
     <row r="679">
@@ -27407,7 +27667,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>2025/09/30，2025/10/01，2025/10/11，2025/10/17，2025/10/26</t>
+          <t>2025/09/30，2025/10/01，2025/10/11，2025/10/17，2025/10/26，2026/8/16</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -27418,10 +27678,14 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I679" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>BV1tksmz4EF8</t>
+        </is>
+      </c>
       <c r="J679" t="inlineStr"/>
     </row>
     <row r="680">
@@ -27497,7 +27761,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I681" t="inlineStr"/>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>BV15ZHpzbEZN</t>
+        </is>
+      </c>
       <c r="J681" t="inlineStr"/>
     </row>
     <row r="682">
@@ -27533,7 +27801,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I682" t="inlineStr"/>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>BV1vdHpzfEJe</t>
+        </is>
+      </c>
       <c r="J682" t="inlineStr"/>
     </row>
     <row r="683">
@@ -27681,7 +27953,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr"/>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>BV1xPxgzDEAv</t>
+        </is>
+      </c>
       <c r="J686" t="inlineStr"/>
     </row>
     <row r="687">
@@ -27703,7 +27979,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>2025/10/07，2025/10/12，2025/10/22，2026/03/24，2026/04/02</t>
+          <t>2025/10/07，2025/10/12，2025/10/22，2026/03/24，2026/04/02，2026/08/07</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -27714,7 +27990,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -27955,7 +28231,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>2025/10/13，2025/10/18，2026/03/15</t>
+          <t>2025/10/13，2025/10/18，2026/03/15，2026/08/09</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -27966,7 +28242,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -28315,7 +28591,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/10/23，2026/8/16</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -28326,10 +28602,14 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I702" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>BV1gabm6ZEH1</t>
+        </is>
+      </c>
       <c r="J702" t="inlineStr"/>
     </row>
     <row r="703">
@@ -28477,7 +28757,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I706" t="inlineStr"/>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>BV1DasVzNEqy</t>
+        </is>
+      </c>
       <c r="J706" t="inlineStr"/>
     </row>
     <row r="707">
@@ -28513,7 +28797,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I707" t="inlineStr"/>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>BV1kUsVzWECP</t>
+        </is>
+      </c>
       <c r="J707" t="inlineStr"/>
     </row>
     <row r="708">
@@ -28549,7 +28837,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I708" t="inlineStr"/>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>BV1s8sjzPEbJ</t>
+        </is>
+      </c>
       <c r="J708" t="inlineStr"/>
     </row>
     <row r="709">
@@ -28683,7 +28975,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09</t>
+          <t>2025/10/24，2025/10/25，2025/10/28，2025/11/01，2025/11/12，2025/11/26，2025/12/08，2026/01/02，2026/01/05，2026/01/09，2026/02/23，2026/03/14，2026/03/29，2026/04/24，2026/07/09，2026/08/11</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -28694,7 +28986,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -28767,7 +29059,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10</t>
+          <t>2025/10/28，2025/11/01，2025/11/12，2025/12/19，2026/02/08，2026/02/10，2026/05/10，2026/8/16</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -28778,7 +29070,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -28897,7 +29189,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I717" t="inlineStr"/>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>BV1sDyXBNENn</t>
+        </is>
+      </c>
       <c r="J717" t="inlineStr"/>
     </row>
     <row r="718">
@@ -28919,7 +29215,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>2025/11/03，2026/04/24</t>
+          <t>2025/11/03，2026/04/24，2026/08/11</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -28930,7 +29226,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -29013,7 +29309,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I720" t="inlineStr"/>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>BV1qAkDBrE7e</t>
+        </is>
+      </c>
       <c r="J720" t="inlineStr"/>
     </row>
     <row r="721">
@@ -29259,7 +29559,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2025/11/14，2026/08/02</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -29270,10 +29570,14 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I727" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>BV1a23Z6jE7P</t>
+        </is>
+      </c>
       <c r="J727" t="inlineStr"/>
     </row>
     <row r="728">
@@ -29309,7 +29613,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I728" t="inlineStr"/>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>BV1mnmmBcEJC</t>
+        </is>
+      </c>
       <c r="J728" t="inlineStr"/>
     </row>
     <row r="729">
@@ -29471,7 +29779,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2025/11/19，2025/12/26，2026/03/06</t>
+          <t>2025/11/19，2025/12/26，2026/03/06，2026/08/11</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -29482,7 +29790,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -29525,7 +29833,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I734" t="inlineStr"/>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>BV1SmBQBdE4b</t>
+        </is>
+      </c>
       <c r="J734" t="inlineStr"/>
     </row>
     <row r="735">
@@ -29623,7 +29935,7 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/11/24，2026/08/02</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -29634,10 +29946,14 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I737" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>BV1HbUhByEXN</t>
+        </is>
+      </c>
       <c r="J737" t="inlineStr"/>
     </row>
     <row r="738">
@@ -29743,7 +30059,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18</t>
+          <t>2025/11/27，2025/11/27，2025/11/28，2025/12/06，2025/12/13，2026/01/10，2026/01/24，2026/02/14，2026/03/14，2026/04/01，2026/04/08，2026/05/01，2026/05/06，2026/05/23，2026/06/20，2026/07/18，2026/08/07</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -29754,7 +30070,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -29833,7 +30149,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I742" t="inlineStr"/>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>BV14eSwBrEQb</t>
+        </is>
+      </c>
       <c r="J742" t="inlineStr"/>
     </row>
     <row r="743">
@@ -30091,7 +30411,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16</t>
+          <t>2025/12/09，2025/12/17，2026/01/14，2026/01/23，2026/02/05，2026/02/10，2026/02/25，2026/04/08，2026/05/01，2026/06/16，2026/8/16</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -30102,7 +30422,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -30185,7 +30505,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I751" t="inlineStr"/>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>BV1k9mUB4EG4</t>
+        </is>
+      </c>
       <c r="J751" t="inlineStr"/>
     </row>
     <row r="752">
@@ -30221,7 +30545,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I752" t="inlineStr"/>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>BV1hNmRBsERE</t>
+        </is>
+      </c>
       <c r="J752" t="inlineStr"/>
     </row>
     <row r="753">
@@ -30257,7 +30585,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I753" t="inlineStr"/>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>BV13NmRBsEJj</t>
+        </is>
+      </c>
       <c r="J753" t="inlineStr"/>
     </row>
     <row r="754">
@@ -30293,7 +30625,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I754" t="inlineStr"/>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>BV13NmRBsEED</t>
+        </is>
+      </c>
       <c r="J754" t="inlineStr"/>
     </row>
     <row r="755">
@@ -30423,7 +30759,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/24，2025/12/26，2026/01/02，2026/01/09，2026/01/23，2026/01/29，2026/03/22，2026/04/29，2026/06/20</t>
+          <t>2025/12/19，2025/12/24，2025/12/26，2026/01/02，2026/01/09，2026/01/23，2026/01/29，2026/03/22，2026/04/29，2026/06/20，2026/08/11</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -30434,7 +30770,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -30539,7 +30875,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16</t>
+          <t>2025/12/19，2025/12/23，2025/12/26，2026/01/02，2026/01/05，2026/01/11，2026/01/25，2026/02/09，2026/02/23，2026/03/20，2026/04/02，2026/04/16，2026/04/29，2026/05/10，2026/06/06，2026/06/14，2026/06/20，2026/07/16，2026/08/02，2026/08/07</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -30550,7 +30886,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -30579,7 +30915,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27</t>
+          <t>2025/12/24，2025/12/24，2025/12/26，2026/01/02，2026/01/10，2026/03/13，2026/06/06，2026/07/09，2026/07/27，2026/08/08</t>
         </is>
       </c>
       <c r="F762" t="inlineStr"/>
@@ -30590,7 +30926,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -30703,7 +31039,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14</t>
+          <t>2025/12/26，2026/01/10，2026/01/22，2026/01/23，2026/01/31，2026/02/10，2026/02/23，2026/03/09，2026/03/12，2026/03/14，2026/03/17，2026/03/27，2026/04/24，2026/05/01，2026/06/14，2026/08/01</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -30714,7 +31050,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -31127,7 +31463,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21</t>
+          <t>2026/01/24，2026/01/25，2026/01/26，2026/02/02，2026/02/07，2026/02/10，2026/02/14，2026/02/19，2026/03/04，2026/03/12，2026/03/31，2026/04/01，2026/04/14，2026/04/18，2026/05/10，2026/05/23，2026/06/12，2026/07/03，2026/07/21，2026/08/07</t>
         </is>
       </c>
       <c r="F776" t="inlineStr"/>
@@ -31138,7 +31474,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -31411,7 +31747,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27</t>
+          <t>2026/02/02，2026/02/05，2026/02/09，2026/02/22，2026/07/25，2026/07/26，2026/07/27，2026/07/31，2026/07/31，2026/08/11</t>
         </is>
       </c>
       <c r="F783" t="inlineStr"/>
@@ -31422,7 +31758,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -31571,7 +31907,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18</t>
+          <t>2026/02/08，2026/02/09，2026/02/14，2026/02/20，2026/02/28，2026/05/25，2026/06/13，2026/07/05，2026/07/18，2026/08/08</t>
         </is>
       </c>
       <c r="F787" t="inlineStr"/>
@@ -31582,7 +31918,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -31611,7 +31947,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16</t>
+          <t>2026/02/08，2026/02/09，2026/02/12，2026/02/14，2026/02/19，2026/02/23，2026/02/24，2026/02/25，2026/03/01，2026/03/05，2026/03/12，2026/03/17，2026/03/19，2026/03/31，2026/04/20，2026/05/02，2026/05/21，2026/06/20，2026/07/16，2026/08/02</t>
         </is>
       </c>
       <c r="F788" t="inlineStr"/>
@@ -31622,7 +31958,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -32019,7 +32355,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16</t>
+          <t>2026/02/22，2026/02/23，2026/02/24，2026/02/25，2026/03/14，2026/04/20，2026/06/16，2026/08/01</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
@@ -32030,7 +32366,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -32453,7 +32789,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I808" t="inlineStr"/>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>BV17UmJBME1o</t>
+        </is>
+      </c>
       <c r="J808" t="inlineStr"/>
     </row>
     <row r="809">
@@ -32687,7 +33027,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27</t>
+          <t>2026/03/13，2026/03/14，2026/03/28，2026/04/29，2026/05/25，2026/06/03，2026/06/13，2026/07/02，2026/07/10，2026/07/15，2026/07/22，2026/07/27，2026/07/31，2026/08/11</t>
         </is>
       </c>
       <c r="F814" t="inlineStr"/>
@@ -32698,7 +33038,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -33039,7 +33379,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18</t>
+          <t>2026/03/17，2026/03/17，2026/03/25，2026/03/27，2026/03/29，2026/04/02，2026/04/08，2026/04/16，2026/04/20，2026/05/02，2026/05/06，2026/05/26，2026/06/14，2026/07/18，2026/08/08</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -33050,7 +33390,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -33135,7 +33475,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07</t>
+          <t>2026/03/25，2026/04/14，2026/05/25，2026/05/25，2026/06/25，2026/06/25，2026/06/25，2026/06/26，2026/07/07，2026/08/09</t>
         </is>
       </c>
       <c r="F825" t="inlineStr"/>
@@ -33146,7 +33486,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -33837,7 +34177,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I842" t="inlineStr"/>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>BV1PEQVBuEKU</t>
+        </is>
+      </c>
       <c r="J842" t="inlineStr"/>
     </row>
     <row r="843">
@@ -33939,7 +34283,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26</t>
+          <t>2026/04/17，2026/05/25，2026/05/25，2026/05/26，2026/08/02</t>
         </is>
       </c>
       <c r="F845" t="inlineStr"/>
@@ -33950,7 +34294,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -34041,7 +34385,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I847" t="inlineStr"/>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>BV1UodkBzE3C</t>
+        </is>
+      </c>
       <c r="J847" t="inlineStr"/>
     </row>
     <row r="848">
@@ -34235,7 +34583,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/01，2026/07/31，2026/08/01，2026/08/08，2026/08/11</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -34246,7 +34594,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -34315,7 +34663,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2026/05/01</t>
+          <t>2026/05/01，2026/08/02</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -34326,7 +34674,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -34575,7 +34923,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2026/05/25，2026/05/26，2026/06/15</t>
+          <t>2026/05/25，2026/05/26，2026/06/15，2026/08/02</t>
         </is>
       </c>
       <c r="F860" t="inlineStr"/>
@@ -34586,7 +34934,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -34815,7 +35163,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>2026/06/14，2026/06/14</t>
+          <t>2026/06/14，2026/06/14，2026/08/02</t>
         </is>
       </c>
       <c r="F866" t="inlineStr"/>
@@ -34826,7 +35174,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -35037,7 +35385,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I871" t="inlineStr"/>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>BV1XGjb6yEbo</t>
+        </is>
+      </c>
       <c r="J871" t="inlineStr"/>
     </row>
     <row r="872">
@@ -35099,7 +35451,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>2026/06/25，2026/07/09，2026/07/18</t>
+          <t>2026/06/25，2026/07/09，2026/07/18，2026/07/31</t>
         </is>
       </c>
       <c r="F873" t="inlineStr"/>
@@ -35110,7 +35462,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -35139,7 +35491,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/06/25，2026/08/01，2026/08/11</t>
         </is>
       </c>
       <c r="F874" t="inlineStr"/>
@@ -35150,7 +35502,7 @@
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -35263,7 +35615,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27</t>
+          <t>2026/07/07，2026/07/09，2026/07/10，2026/07/15，2026/07/16，2026/07/18，2026/07/25，2026/07/27，2026/08/01，2026/08/08，2026/08/11</t>
         </is>
       </c>
       <c r="F877" t="inlineStr"/>
@@ -35274,7 +35626,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -35303,7 +35655,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>2026/07/17，2026/07/18，2026/07/27</t>
+          <t>2026/07/17，2026/07/18，2026/07/27，2026/08/02，2026/08/05</t>
         </is>
       </c>
       <c r="F878" t="inlineStr"/>
@@ -35314,7 +35666,7 @@
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -35383,7 +35735,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>2026/07/26，2026/07/27，2026/07/28</t>
+          <t>2026/07/26，2026/07/27，2026/07/28，2026/07/31，2026/07/31，2026/08/08</t>
         </is>
       </c>
       <c r="F880" t="inlineStr"/>
@@ -35394,7 +35746,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -35423,7 +35775,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/27，2026/07/30，2026/08/01，2026/08/03</t>
         </is>
       </c>
       <c r="F881" t="inlineStr"/>
@@ -35434,7 +35786,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -35503,7 +35855,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/27，2026/07/31</t>
         </is>
       </c>
       <c r="F883" t="inlineStr"/>
@@ -35514,15 +35866,247 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>BV19x3P6cESt</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>蝴蝶泉边</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr"/>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>黄雅莉</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>2026/08/02</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I883" t="inlineStr">
-        <is>
-          <t>BV19x3P6cESt</t>
-        </is>
-      </c>
-      <c r="J883" t="inlineStr"/>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>BV1Qm3Z61Exc</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>麦恩莉</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr"/>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>方大同</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>2026/08/03，2026/08/08，2026/08/09，2026/08/11</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>BV1BTMo6VELH</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>中国人会飞</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr"/>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Chalky Wong/揽佬SKAI ISYOURGOD</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>2026/08/05，2026/08/05</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>BV1cZMy6DE4V</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Imagine Dragons/JID/英雄联盟/双城之战</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>2026/08/05，2025/05/03</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>BV1scGdzVEjo</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>悲伤的五个步骤</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr"/>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>艾薇Ivy</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>2026/08/11，2026/08/11</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr"/>
+      <c r="J888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>讨厌</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>芮恩</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>华语</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr"/>
+      <c r="J889" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
